--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3C80E6-3F48-49A9-9F32-ADFE08465885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D0C602-5D38-4CE2-9D1A-388729735BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2635,6 +2635,36 @@
   </si>
   <si>
     <t>M$2021/PJ</t>
+  </si>
+  <si>
+    <t>IMPELCVN1</t>
+  </si>
+  <si>
+    <t>IMPELCLAO1</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>IMPELCLAO2</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>cost/PJ</t>
+  </si>
+  <si>
+    <t>IMPELCLAO3</t>
   </si>
 </sst>
 </file>
@@ -2648,7 +2678,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2850,8 +2880,13 @@
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2906,6 +2941,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF1FB"/>
         <bgColor rgb="FFEAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3049,7 +3090,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="59">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3117,8 +3158,9 @@
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3273,12 +3315,16 @@
     <xf numFmtId="49" fontId="31" fillId="10" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="59" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="59">
+  <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="calculated" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Calculation 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma" xfId="59" builtinId="3"/>
     <cellStyle name="Comma 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma 11" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Comma 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -7314,12 +7360,12 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
     <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
     <col min="18" max="18" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
     <col min="20" max="16384" width="8.85546875" style="23"/>
@@ -7730,18 +7776,157 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2022</v>
+      </c>
+      <c r="H18" s="82">
+        <v>35.75</v>
+      </c>
+      <c r="I18">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>2026</v>
+      </c>
+      <c r="H19">
+        <v>22.05</v>
+      </c>
+      <c r="I19" s="80">
+        <v>2.6490239999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20">
+        <v>2028</v>
+      </c>
+      <c r="H20">
+        <v>21.39</v>
+      </c>
+      <c r="I20">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21">
+        <v>2029</v>
+      </c>
+      <c r="H21">
+        <v>21.39</v>
+      </c>
+      <c r="I21">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B24" s="44"/>
+      <c r="C24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="44"/>
       <c r="C25" s="2"/>
+      <c r="K25" s="80">
+        <v>168</v>
+      </c>
+      <c r="L25" s="80">
+        <f>K25*24*365*0.5</f>
+        <v>735840</v>
+      </c>
+      <c r="M25" s="80">
+        <f>L25*N25</f>
+        <v>2.6490239999999998</v>
+      </c>
+      <c r="N25" s="2">
+        <v>3.5999999999999998E-6</v>
+      </c>
+      <c r="O25">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="P25" s="81">
+        <f>L25*O25*10^3</f>
+        <v>58425696</v>
+      </c>
+      <c r="Q25" s="80">
+        <f>P25/M25</f>
+        <v>22055555.555555556</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C26" s="2"/>
+      <c r="K26" s="80">
+        <v>900</v>
+      </c>
+      <c r="L26" s="80">
+        <f>K26*24*365*0.5</f>
+        <v>3942000</v>
+      </c>
+      <c r="M26" s="80">
+        <f>L26*N26</f>
+        <v>14.191199999999998</v>
+      </c>
+      <c r="N26" s="2">
+        <v>3.5999999999999998E-6</v>
+      </c>
+      <c r="O26">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="P26" s="81">
+        <f>L26*O26*10^3</f>
+        <v>303534000</v>
+      </c>
+      <c r="Q26" s="80">
+        <f>P26/M26</f>
+        <v>21388888.888888892</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D0C602-5D38-4CE2-9D1A-388729735BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63DDFA4-95E7-49B0-B02D-801505C7AE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="4" r:id="rId1"/>
@@ -3160,7 +3160,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3318,6 +3318,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="59" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -6905,7 +6906,7 @@
       <c r="H14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="83">
         <v>975</v>
       </c>
       <c r="J14"/>
@@ -6956,7 +6957,7 @@
       <c r="H15" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="83">
         <v>750</v>
       </c>
       <c r="J15" s="30"/>
@@ -7007,7 +7008,7 @@
       <c r="H16" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="83">
         <v>2078.7684537684499</v>
       </c>
       <c r="J16" s="30"/>
@@ -7059,7 +7060,7 @@
       <c r="H17" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="83">
         <v>500</v>
       </c>
       <c r="J17"/>
@@ -7110,7 +7111,7 @@
       <c r="H18" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="83">
         <v>1340</v>
       </c>
       <c r="J18"/>
@@ -7163,7 +7164,7 @@
       <c r="H19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="83">
         <v>1700</v>
       </c>
       <c r="J19"/>
@@ -7216,7 +7217,7 @@
       <c r="H20" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="83">
         <v>120</v>
       </c>
       <c r="J20" s="30"/>
@@ -7264,7 +7265,7 @@
       <c r="H21" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="83">
         <v>100</v>
       </c>
       <c r="K21" s="23">
@@ -7311,7 +7312,7 @@
       <c r="H22" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="83">
         <v>100</v>
       </c>
       <c r="K22" s="23">
@@ -8366,14 +8367,14 @@
       <c r="U16" s="63"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" t="str">
+      <c r="B17" s="2" t="str">
         <f>O17</f>
         <v>CSCNSOL1</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>238</v>
       </c>
       <c r="E17" s="30">
@@ -8420,21 +8421,21 @@
       <c r="U17" s="65"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" t="str">
+      <c r="B18" s="2" t="str">
         <f t="shared" ref="B18:B27" si="0">O18</f>
         <v>CSCNELC1</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="55" t="s">
         <v>238</v>
       </c>
       <c r="E18" s="30">
         <v>2022</v>
       </c>
       <c r="F18" s="31">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G18" s="31">
         <v>0.3</v>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63DDFA4-95E7-49B0-B02D-801505C7AE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390300C5-EC26-4C37-8240-08D62FEEDFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="4" r:id="rId1"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2586,9 +2586,6 @@
     <t>PDP Installed Capacity</t>
   </si>
   <si>
-    <t>NCAP_BND</t>
-  </si>
-  <si>
     <t>TRAINHFO1</t>
   </si>
   <si>
@@ -2665,6 +2662,9 @@
   </si>
   <si>
     <t>IMPELCLAO3</t>
+  </si>
+  <si>
+    <t>NCAP_BND (FX)</t>
   </si>
 </sst>
 </file>
@@ -4695,7 +4695,7 @@
     <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
     <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
@@ -4943,7 +4943,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -5112,6 +5112,9 @@
       <c r="D14" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E14" s="26">
+        <v>2023</v>
+      </c>
       <c r="F14" s="26">
         <v>2023</v>
       </c>
@@ -5165,6 +5168,15 @@
       <c r="Y14" s="65"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B15" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E15" s="23">
         <v>2025</v>
       </c>
@@ -5192,6 +5204,15 @@
       <c r="Y15" s="65"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B16" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E16" s="23">
         <v>2030</v>
       </c>
@@ -5219,6 +5240,15 @@
       <c r="Y16" s="65"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B17" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E17" s="23">
         <v>2035</v>
       </c>
@@ -5246,6 +5276,15 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B18" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E18" s="23">
         <v>2040</v>
       </c>
@@ -5283,6 +5322,9 @@
       <c r="D19" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E19" s="23">
+        <v>2023</v>
+      </c>
       <c r="F19" s="23">
         <v>2023</v>
       </c>
@@ -5336,6 +5378,15 @@
       <c r="Y19" s="65"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B20" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E20" s="23">
         <v>2025</v>
       </c>
@@ -5362,6 +5413,15 @@
       <c r="Y20" s="65"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B21" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E21" s="23">
         <v>2030</v>
       </c>
@@ -5388,6 +5448,15 @@
       <c r="Y21" s="65"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B22" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E22" s="23">
         <v>2035</v>
       </c>
@@ -5414,6 +5483,15 @@
       <c r="Y22" s="65"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B23" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E23" s="23">
         <v>2040</v>
       </c>
@@ -5450,6 +5528,9 @@
       <c r="D24" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E24" s="23">
+        <v>2027</v>
+      </c>
       <c r="F24" s="23">
         <v>2027</v>
       </c>
@@ -5505,6 +5586,15 @@
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B25" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E25" s="23">
         <v>2030</v>
       </c>
@@ -5531,6 +5621,15 @@
       <c r="Y25" s="65"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B26" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E26" s="23">
         <v>2035</v>
       </c>
@@ -5569,6 +5668,15 @@
       <c r="Y26" s="65"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B27" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E27" s="23">
         <v>2040</v>
       </c>
@@ -5607,6 +5715,15 @@
       <c r="Y27" s="65"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E28" s="23">
         <v>2045</v>
       </c>
@@ -5646,7 +5763,7 @@
     </row>
     <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
-        <f t="shared" ref="B29" si="0">S26</f>
+        <f>S26</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5654,6 +5771,9 @@
       </c>
       <c r="D29" s="23" t="s">
         <v>49</v>
+      </c>
+      <c r="E29" s="23">
+        <v>2028</v>
       </c>
       <c r="F29" s="23">
         <v>2028</v>
@@ -5708,6 +5828,15 @@
       <c r="Y29" s="65"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E30" s="23">
         <v>2030</v>
       </c>
@@ -5733,6 +5862,15 @@
       <c r="Y30" s="65"/>
     </row>
     <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E31" s="23">
         <v>2035</v>
       </c>
@@ -5758,6 +5896,15 @@
       <c r="Y31" s="65"/>
     </row>
     <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E32" s="23">
         <v>2040</v>
       </c>
@@ -5793,7 +5940,7 @@
       <c r="D33" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F33" s="23">
+      <c r="E33" s="23">
         <v>2023</v>
       </c>
       <c r="G33" s="27">
@@ -5845,6 +5992,15 @@
       <c r="Y33" s="65"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B34" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E34" s="23">
         <v>2025</v>
       </c>
@@ -5868,6 +6024,15 @@
       <c r="Y34" s="65"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B35" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E35" s="23">
         <v>2030</v>
       </c>
@@ -5891,6 +6056,15 @@
       <c r="Y35" s="65"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B36" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E36" s="23">
         <v>2035</v>
       </c>
@@ -5914,6 +6088,15 @@
       <c r="Y36" s="65"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B37" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E37" s="23">
         <v>2040</v>
       </c>
@@ -5947,6 +6130,9 @@
       <c r="D38" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E38" s="23">
+        <v>2026</v>
+      </c>
       <c r="F38" s="23">
         <v>2026</v>
       </c>
@@ -5995,6 +6181,18 @@
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B39" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="23">
+        <v>2030</v>
+      </c>
       <c r="F39" s="23">
         <v>2030</v>
       </c>
@@ -6012,7 +6210,7 @@
         <v>1273</v>
       </c>
       <c r="K39" s="23">
-        <f t="shared" ref="K39:K40" si="1">K38*0.95</f>
+        <f t="shared" ref="K39:K40" si="0">K38*0.95</f>
         <v>25.364999999999998</v>
       </c>
       <c r="O39" s="27"/>
@@ -6024,6 +6222,18 @@
       <c r="W39" s="60"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B40" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="23">
+        <v>2035</v>
+      </c>
       <c r="F40" s="23">
         <v>2035</v>
       </c>
@@ -6041,7 +6251,7 @@
         <v>1209.3499999999999</v>
       </c>
       <c r="K40" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24.096749999999997</v>
       </c>
       <c r="O40" s="27"/>
@@ -6053,6 +6263,18 @@
       <c r="W40" s="60"/>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B41" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="23">
+        <v>2040</v>
+      </c>
       <c r="F41" s="23">
         <v>2040</v>
       </c>
@@ -6084,6 +6306,9 @@
       <c r="D42" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E42" s="23">
+        <v>2022</v>
+      </c>
       <c r="F42" s="23">
         <v>2022</v>
       </c>
@@ -6134,6 +6359,15 @@
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B43" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E43" s="23">
         <v>2025</v>
       </c>
@@ -6156,6 +6390,15 @@
       <c r="W43" s="60"/>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B44" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E44" s="23">
         <v>2030</v>
       </c>
@@ -6178,6 +6421,15 @@
       <c r="W44" s="60"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B45" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E45" s="23">
         <v>2035</v>
       </c>
@@ -6200,6 +6452,15 @@
       <c r="W45" s="60"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B46" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E46" s="23">
         <v>2040</v>
       </c>
@@ -6232,6 +6493,9 @@
       <c r="D47" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E47" s="23">
+        <v>2024</v>
+      </c>
       <c r="F47" s="23">
         <v>2024</v>
       </c>
@@ -6265,6 +6529,15 @@
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B48" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E48" s="23">
         <v>2025</v>
       </c>
@@ -6281,6 +6554,15 @@
       <c r="O48" s="27"/>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B49" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E49" s="23">
         <v>2030</v>
       </c>
@@ -6297,6 +6579,15 @@
       <c r="O49" s="27"/>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B50" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E50" s="23">
         <v>2035</v>
       </c>
@@ -6313,6 +6604,15 @@
       <c r="O50" s="27"/>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B51" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E51" s="23">
         <v>2040</v>
       </c>
@@ -6339,6 +6639,9 @@
       <c r="D52" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E52" s="23">
+        <v>2030</v>
+      </c>
       <c r="F52" s="23">
         <v>2030</v>
       </c>
@@ -6371,6 +6674,15 @@
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B53" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E53" s="23">
         <v>2035</v>
       </c>
@@ -6386,6 +6698,15 @@
       <c r="L53" s="27"/>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B54" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E54" s="23">
         <v>2040</v>
       </c>
@@ -6410,6 +6731,9 @@
       <c r="D55" s="23" t="s">
         <v>49</v>
       </c>
+      <c r="E55" s="23">
+        <v>2025</v>
+      </c>
       <c r="F55" s="23">
         <v>2025</v>
       </c>
@@ -6441,6 +6765,15 @@
       <c r="T55" s="23"/>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B56" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E56" s="23">
         <v>2030</v>
       </c>
@@ -6455,6 +6788,15 @@
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B57" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E57" s="23">
         <v>2035</v>
       </c>
@@ -6469,6 +6811,15 @@
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B58" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="E58" s="23">
         <v>2040</v>
       </c>
@@ -7612,7 +7963,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>52</v>
@@ -7631,11 +7982,11 @@
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E11" s="2">
         <v>2022</v>
@@ -7654,11 +8005,11 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E12" s="2">
         <v>2022</v>
@@ -7676,11 +8027,11 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E13" s="2">
         <v>2022</v>
@@ -7698,11 +8049,11 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E14" s="2">
         <v>2022</v>
@@ -7720,11 +8071,11 @@
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E15" s="2">
         <v>2022</v>
@@ -7741,11 +8092,11 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16" s="2">
         <v>2022</v>
@@ -7762,10 +8113,10 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E17" s="2">
         <v>2022</v>
@@ -7779,7 +8130,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B18" s="60" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D18" t="s">
         <v>49</v>
@@ -7796,7 +8147,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D19" t="s">
         <v>49</v>
@@ -7813,7 +8164,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D20" t="s">
         <v>49</v>
@@ -7831,7 +8182,7 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D21" t="s">
         <v>49</v>
@@ -7850,25 +8201,25 @@
       <c r="B24" s="44"/>
       <c r="C24" s="2"/>
       <c r="K24" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O24" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -10434,7 +10785,7 @@
         <v>90</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q29" t="s">
         <v>226</v>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390300C5-EC26-4C37-8240-08D62FEEDFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD6F12A-4056-40A2-9D85-9F3267687824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ELC" sheetId="4" r:id="rId1"/>
+    <sheet name="ELC" sheetId="10" r:id="rId1"/>
     <sheet name="IND" sheetId="8" r:id="rId2"/>
     <sheet name="PRI" sheetId="7" r:id="rId3"/>
     <sheet name="RCA" sheetId="6" r:id="rId4"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="312">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2583,9 +2583,6 @@
     <t>ELE, STG</t>
   </si>
   <si>
-    <t>PDP Installed Capacity</t>
-  </si>
-  <si>
     <t>TRAINHFO1</t>
   </si>
   <si>
@@ -2662,9 +2659,6 @@
   </si>
   <si>
     <t>IMPELCLAO3</t>
-  </si>
-  <si>
-    <t>NCAP_BND (FX)</t>
   </si>
 </sst>
 </file>
@@ -3401,21 +3395,21 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>21166</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+        <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE448FC7-5FA6-4416-A543-F7B93A5592EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32B77573-8AA6-4A45-9A0E-8369B938F12E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3423,8 +3417,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1311274" y="5296958"/>
-          <a:ext cx="7356475" cy="1423458"/>
+          <a:off x="1314449" y="6016625"/>
+          <a:ext cx="7355417" cy="1452033"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4683,9 +4677,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECAA6EC-6D7D-4104-9FDE-D9F949DD51B1}">
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
@@ -4694,33 +4687,32 @@
     <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" style="23" customWidth="1"/>
-    <col min="13" max="13" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="23" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" style="23" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" style="23" customWidth="1"/>
+    <col min="12" max="12" width="7" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="P2" s="36"/>
       <c r="Q2" s="36"/>
       <c r="R2" s="36"/>
       <c r="S2" s="36"/>
@@ -4729,9 +4721,8 @@
       <c r="V2" s="36"/>
       <c r="W2" s="36"/>
       <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-    </row>
-    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4750,11 +4741,11 @@
       <c r="G3" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="I3" s="22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>49</v>
       </c>
@@ -4773,51 +4764,51 @@
       <c r="G4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="59" t="s">
+      <c r="P4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="60"/>
       <c r="S4" s="60"/>
       <c r="T4" s="60"/>
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q5" s="61" t="s">
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="P5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="62" t="s">
+      <c r="Q5" s="62" t="s">
         <v>55</v>
       </c>
+      <c r="R5" s="61" t="s">
+        <v>6</v>
+      </c>
       <c r="S5" s="61" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T5" s="61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5" s="61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V5" s="61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W5" s="61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X5" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>56</v>
       </c>
@@ -4836,37 +4827,36 @@
       <c r="G6" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="P6" s="63" t="s">
+        <v>61</v>
+      </c>
       <c r="Q6" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R6" s="63" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="S6" s="63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T6" s="63" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="U6" s="63" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="V6" s="63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W6" s="63" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="X6" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>65</v>
       </c>
@@ -4885,45 +4875,43 @@
       <c r="G7" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="32"/>
-      <c r="Q7" s="2"/>
+      <c r="H7" s="32"/>
+      <c r="P7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="5"/>
-      <c r="Q10" s="59" t="s">
+      <c r="L10" s="5"/>
+      <c r="P10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="59"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="60"/>
       <c r="S10" s="60"/>
       <c r="T10" s="60"/>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
       <c r="W10" s="60"/>
       <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4943,59 +4931,56 @@
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11" s="16" t="s">
         <v>36</v>
       </c>
+      <c r="L11" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="M11" s="15" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="O11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="61" t="s">
+      <c r="O11" s="25"/>
+      <c r="P11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="Q11" s="62" t="s">
         <v>55</v>
       </c>
+      <c r="R11" s="61" t="s">
+        <v>1</v>
+      </c>
       <c r="S11" s="61" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" s="61" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="U11" s="61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V11" s="61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W11" s="61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X11" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -5011,58 +4996,55 @@
         <v>37</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="I12" s="18" t="s">
         <v>72</v>
       </c>
+      <c r="I12" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="J12" s="17" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="17" t="s">
         <v>74</v>
       </c>
+      <c r="P12" s="64" t="s">
+        <v>75</v>
+      </c>
       <c r="Q12" s="64" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="R12" s="64" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="S12" s="64" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T12" s="64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U12" s="64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V12" s="64" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="W12" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X12" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>78</v>
       </c>
@@ -5072,26 +5054,26 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
+      <c r="I13" s="19" t="s">
+        <v>199</v>
+      </c>
       <c r="J13" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="O13" s="19"/>
-      <c r="Q13" s="63" t="s">
+      <c r="N13" s="19"/>
+      <c r="P13" s="63" t="s">
         <v>97</v>
       </c>
+      <c r="Q13" s="63"/>
       <c r="R13" s="63"/>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
@@ -5099,11 +5081,10 @@
       <c r="V13" s="63"/>
       <c r="W13" s="63"/>
       <c r="X13" s="63"/>
-      <c r="Y13" s="63"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
-        <f>S14</f>
+        <f>R14</f>
         <v>ELCTNCOA01</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -5112,9 +5093,6 @@
       <c r="D14" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="26">
-        <v>2023</v>
-      </c>
       <c r="F14" s="26">
         <v>2023</v>
       </c>
@@ -5122,1723 +5100,674 @@
         <v>0.42</v>
       </c>
       <c r="H14" s="27">
-        <v>1.32</v>
-      </c>
-      <c r="I14" s="27">
         <v>0.85</v>
       </c>
-      <c r="J14" s="23">
+      <c r="I14" s="23">
         <v>1650</v>
       </c>
+      <c r="J14" s="27">
+        <v>30</v>
+      </c>
       <c r="K14" s="27">
-        <v>30</v>
-      </c>
-      <c r="L14" s="27">
         <v>0.4</v>
       </c>
+      <c r="L14" s="23">
+        <v>40</v>
+      </c>
       <c r="M14" s="23">
-        <v>40</v>
-      </c>
-      <c r="N14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O14" s="27">
+      <c r="N14" s="27">
         <v>1</v>
       </c>
-      <c r="Q14" s="65" t="s">
+      <c r="P14" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65" t="s">
+        <v>151</v>
+      </c>
       <c r="S14" s="65" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="T14" s="65" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="U14" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W14" s="60" t="s">
+      <c r="V14" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="W14" s="65"/>
       <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B15" s="23" t="s">
-        <v>151</v>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="23" t="str">
+        <f>R15</f>
+        <v>ELCTNOIL01</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="23">
-        <v>2025</v>
-      </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="23">
+        <v>2023</v>
+      </c>
       <c r="G15" s="27">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H15" s="27">
-        <v>1.32</v>
-      </c>
-      <c r="I15" s="27">
         <v>0.85</v>
       </c>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="O15" s="27"/>
+      <c r="I15" s="23">
+        <v>250</v>
+      </c>
+      <c r="J15" s="27">
+        <v>20</v>
+      </c>
+      <c r="K15" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="23">
+        <v>40</v>
+      </c>
+      <c r="M15" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N15" s="27">
+        <v>1</v>
+      </c>
+      <c r="P15" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="60"/>
+      <c r="R15" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="S15" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="T15" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U15" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V15" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W15" s="65"/>
       <c r="X15" s="65"/>
-      <c r="Y15" s="65"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B16" s="23" t="s">
-        <v>151</v>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B16" s="23" t="str">
+        <f>R16</f>
+        <v>ELCTNGAS01</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="23">
-        <v>2030</v>
-      </c>
-      <c r="F16" s="26"/>
+        <v>2027</v>
+      </c>
+      <c r="F16" s="23">
+        <v>2027</v>
+      </c>
       <c r="G16" s="27">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="27">
-        <v>1.44</v>
-      </c>
-      <c r="I16" s="27">
         <v>0.85</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="O16" s="27"/>
+      <c r="I16" s="23">
+        <v>1100</v>
+      </c>
+      <c r="J16" s="27">
+        <v>30</v>
+      </c>
+      <c r="K16" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="L16" s="23">
+        <v>40</v>
+      </c>
+      <c r="M16" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N16" s="27">
+        <v>1</v>
+      </c>
+      <c r="P16" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="Q16" s="65"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="65"/>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B17" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>49</v>
-      </c>
+      <c r="R16" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="S16" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="T16" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U16" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V16" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W16" s="65"/>
+      <c r="X16" s="65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
-      <c r="F17" s="26"/>
       <c r="G17" s="27">
-        <v>0.42</v>
-      </c>
-      <c r="H17" s="27">
-        <v>1.44</v>
-      </c>
-      <c r="I17" s="27">
-        <v>0.85</v>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="J17" s="27"/>
       <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="O17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="P17" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="60"/>
+      <c r="R17" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="S17" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="T17" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U17" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V17" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W17" s="65"/>
       <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B18" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
-      <c r="F18" s="26"/>
       <c r="G18" s="27">
-        <v>0.42</v>
-      </c>
-      <c r="H18" s="27">
-        <v>1.44</v>
-      </c>
-      <c r="I18" s="27">
-        <v>0.85</v>
-      </c>
+        <v>0.52</v>
+      </c>
+      <c r="H18" s="27"/>
+      <c r="J18" s="27"/>
       <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="O18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="P18" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="60"/>
+      <c r="R18" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="S18" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="T18" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U18" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V18" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W18" s="65"/>
       <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B19" s="23" t="str">
-        <f>S19</f>
-        <v>ELCTNOIL01</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="19" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="23">
-        <v>2023</v>
-      </c>
-      <c r="F19" s="23">
-        <v>2023</v>
+        <v>2045</v>
       </c>
       <c r="G19" s="27">
-        <v>0.3</v>
-      </c>
-      <c r="H19" s="27">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="I19" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="J19" s="23">
-        <v>250</v>
-      </c>
-      <c r="K19" s="27">
-        <v>20</v>
-      </c>
-      <c r="L19" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="M19" s="23">
-        <v>40</v>
-      </c>
-      <c r="N19" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O19" s="27">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="65" t="s">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="P19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65" t="s">
+        <v>156</v>
+      </c>
       <c r="S19" s="65" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="T19" s="65" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="U19" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V19" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="60" t="s">
+      <c r="V19" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="W19" s="65"/>
       <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B20" s="23" t="s">
-        <v>153</v>
+    </row>
+    <row r="20" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="23" t="str">
+        <f t="shared" ref="B20:B22" si="0">R17</f>
+        <v>ELCRNBIO01</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="23">
-        <v>2025</v>
+      <c r="F20" s="23">
+        <v>2028</v>
       </c>
       <c r="G20" s="27">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H20" s="27">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="I20" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="O20" s="27"/>
+        <v>0.6</v>
+      </c>
+      <c r="I20" s="23">
+        <v>2500</v>
+      </c>
+      <c r="J20" s="23">
+        <v>30</v>
+      </c>
+      <c r="K20" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="L20" s="23">
+        <v>25</v>
+      </c>
+      <c r="M20" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N20" s="27">
+        <v>1</v>
+      </c>
+      <c r="P20" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="60"/>
+      <c r="R20" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="S20" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="T20" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U20" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V20" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W20" s="65"/>
       <c r="X20" s="65"/>
-      <c r="Y20" s="65"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B21" s="23" t="s">
-        <v>153</v>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B21" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCRNHYD01</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="23">
-        <v>2030</v>
+      <c r="F21" s="23">
+        <v>2026</v>
       </c>
       <c r="G21" s="27">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="27">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="I21" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="60"/>
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="23">
+        <v>3000</v>
+      </c>
+      <c r="J21" s="23">
+        <v>35</v>
+      </c>
+      <c r="K21" s="27">
+        <v>2</v>
+      </c>
+      <c r="L21" s="23">
+        <v>50</v>
+      </c>
+      <c r="M21" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N21" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="P21" t="s">
+        <v>285</v>
+      </c>
+      <c r="R21" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="S21" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="T21" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U21" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V21" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="W21" s="65"/>
       <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B22" s="23" t="s">
-        <v>153</v>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B22" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>ELCRNWIN01</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="23">
+      <c r="F22" s="23">
+        <v>2026</v>
+      </c>
+      <c r="G22" s="27">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="I22" s="23">
+        <v>1340</v>
+      </c>
+      <c r="J22" s="23">
+        <v>26.7</v>
+      </c>
+      <c r="K22" s="27"/>
+      <c r="L22" s="23">
+        <v>25</v>
+      </c>
+      <c r="M22" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N22" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="P22" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R22" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="S22" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="T22" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V22" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="F23" s="23">
         <v>2035</v>
       </c>
-      <c r="G22" s="27">
-        <v>0.3</v>
-      </c>
-      <c r="H22" s="27">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="I22" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B23" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="23">
-        <v>2040</v>
-      </c>
       <c r="G23" s="27">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="27">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="I23" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
+        <v>0.35</v>
+      </c>
+      <c r="I23" s="23">
+        <f>I22*0.95</f>
+        <v>1273</v>
+      </c>
+      <c r="J23" s="23">
+        <f t="shared" ref="J23:J24" si="1">J22*0.95</f>
+        <v>25.364999999999998</v>
+      </c>
+      <c r="N23" s="27"/>
+      <c r="P23" s="65"/>
+      <c r="R23" s="23"/>
       <c r="S23" s="65"/>
       <c r="T23" s="65"/>
       <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B24" s="23" t="str">
-        <f>S24</f>
-        <v>ELCTNGAS01</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="23">
-        <v>2027</v>
-      </c>
+      <c r="V23" s="60"/>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F24" s="23">
-        <v>2027</v>
+        <v>2040</v>
       </c>
       <c r="G24" s="27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H24" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I24" s="27">
-        <v>0.85</v>
+        <v>0.35</v>
+      </c>
+      <c r="I24" s="23">
+        <f>I23*0.95</f>
+        <v>1209.3499999999999</v>
       </c>
       <c r="J24" s="23">
-        <v>1100</v>
-      </c>
-      <c r="K24" s="27">
-        <v>30</v>
-      </c>
-      <c r="L24" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="M24" s="23">
-        <v>40</v>
-      </c>
-      <c r="N24" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O24" s="27">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="T24" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="U24" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V24" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W24" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="65" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B25" s="23" t="s">
-        <v>152</v>
+        <f t="shared" si="1"/>
+        <v>24.096749999999997</v>
+      </c>
+      <c r="N24" s="27"/>
+      <c r="P24" s="65"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="60"/>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B25" s="23" t="str">
+        <f>R20</f>
+        <v>ELCRNSOL01</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="23">
-        <v>2030</v>
+      <c r="F25" s="23">
+        <v>2022</v>
       </c>
       <c r="G25" s="27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H25" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I25" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B26" s="23" t="s">
-        <v>152</v>
+        <v>0.25</v>
+      </c>
+      <c r="I25" s="23">
+        <v>550</v>
+      </c>
+      <c r="J25" s="23">
+        <v>7</v>
+      </c>
+      <c r="K25" s="27">
+        <v>0</v>
+      </c>
+      <c r="L25" s="23">
+        <v>25</v>
+      </c>
+      <c r="M25" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N25" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="P25" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="S25" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="T25" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="U25" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="V25" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B26" s="23" t="str">
+        <f>R22</f>
+        <v>ELCRNBSO01</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="23">
-        <v>2035</v>
+      <c r="F26" s="23">
+        <v>2026</v>
       </c>
       <c r="G26" s="27">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="H26" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I26" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="Q26" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="T26" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="U26" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V26" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W26" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B27" s="23" t="s">
-        <v>152</v>
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="23">
+        <v>1090</v>
+      </c>
+      <c r="J26" s="23">
+        <f>I26*0.02</f>
+        <v>21.8</v>
+      </c>
+      <c r="K26" s="27">
+        <v>0</v>
+      </c>
+      <c r="L26" s="23">
+        <v>25</v>
+      </c>
+      <c r="M26" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N26" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B27" s="23" t="str">
+        <f>R25</f>
+        <v>ELCRNPHY01</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="23">
-        <v>2040</v>
+      <c r="F27" s="23">
+        <v>2028</v>
       </c>
       <c r="G27" s="27">
-        <v>0.52</v>
-      </c>
-      <c r="H27" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I27" s="27">
-        <v>0.85</v>
-      </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="Q27" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R27" s="65"/>
-      <c r="S27" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="T27" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="U27" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V27" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W27" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X27" s="65"/>
-      <c r="Y27" s="65"/>
-    </row>
-    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="I27" s="23">
+        <v>1990</v>
+      </c>
+      <c r="J27" s="23">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="K27" s="27">
+        <v>2</v>
+      </c>
+      <c r="L27" s="23">
+        <v>40</v>
+      </c>
+      <c r="M27" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="N27" s="23">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B28" s="23" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="23">
-        <v>2045</v>
-      </c>
-      <c r="G28" s="27">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H28" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I28" s="27">
+      <c r="F28" s="23">
+        <v>2026</v>
+      </c>
+      <c r="G28" s="23">
         <v>0.85</v>
       </c>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="Q28" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="T28" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="U28" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V28" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W28" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
-    </row>
-    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="23" t="str">
-        <f>S26</f>
-        <v>ELCRNBIO01</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="23">
-        <v>2028</v>
-      </c>
-      <c r="F29" s="23">
-        <v>2028</v>
-      </c>
-      <c r="G29" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="H29" s="27">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="I29" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="J29" s="23">
-        <v>2500</v>
-      </c>
-      <c r="K29" s="23">
-        <v>30</v>
-      </c>
-      <c r="L29" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="M29" s="23">
-        <v>25</v>
-      </c>
-      <c r="N29" s="23">
+      <c r="H28" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="I28" s="23">
+        <v>490</v>
+      </c>
+      <c r="J28" s="23">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L28" s="23">
+        <v>15</v>
+      </c>
+      <c r="M28" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O29" s="27">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="T29" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="U29" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V29" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W29" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
-    </row>
-    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G30" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="H30" s="27">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="I30" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="L30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
-    </row>
-    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G31" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="H31" s="27">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="I31" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="L31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-    </row>
-    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G32" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="H32" s="27">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="I32" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="L32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B33" s="23" t="str">
-        <f>S27</f>
-        <v>ELCRNHYD01</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="23">
-        <v>2023</v>
-      </c>
-      <c r="G33" s="27">
-        <v>1</v>
-      </c>
-      <c r="H33" s="27">
-        <v>1.3301000000000001</v>
-      </c>
-      <c r="I33" s="27">
+      <c r="N28" s="23">
         <v>0.5</v>
       </c>
-      <c r="J33" s="23">
-        <v>3000</v>
-      </c>
-      <c r="K33" s="23">
-        <v>35</v>
-      </c>
-      <c r="L33" s="27">
-        <v>2</v>
-      </c>
-      <c r="M33" s="23">
-        <v>50</v>
-      </c>
-      <c r="N33" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O33" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>285</v>
-      </c>
-      <c r="S33" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="T33" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="U33" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V33" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W33" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B34" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="23">
-        <v>2025</v>
-      </c>
-      <c r="G34" s="27">
-        <v>1</v>
-      </c>
-      <c r="H34" s="27">
-        <v>1.3351</v>
-      </c>
-      <c r="I34" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="L34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B35" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G35" s="27">
-        <v>1</v>
-      </c>
-      <c r="H35" s="27">
-        <v>1.9951000000000001</v>
-      </c>
-      <c r="I35" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="L35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B36" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G36" s="27">
-        <v>1</v>
-      </c>
-      <c r="H36" s="27">
-        <v>2.7111000000000001</v>
-      </c>
-      <c r="I36" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="L36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B37" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G37" s="27">
-        <v>1</v>
-      </c>
-      <c r="H37" s="27">
-        <v>2.8811</v>
-      </c>
-      <c r="I37" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="L37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="60"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B38" s="23" t="str">
-        <f>S28</f>
-        <v>ELCRNWIN01</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="23">
-        <v>2026</v>
-      </c>
-      <c r="F38" s="23">
-        <v>2026</v>
-      </c>
-      <c r="G38" s="27">
-        <v>1</v>
-      </c>
-      <c r="H38" s="27">
-        <v>0.15</v>
-      </c>
-      <c r="I38" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="J38" s="23">
-        <v>1340</v>
-      </c>
-      <c r="K38" s="23">
-        <v>26.7</v>
-      </c>
-      <c r="L38" s="27"/>
-      <c r="M38" s="23">
-        <v>25</v>
-      </c>
-      <c r="N38" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O38" s="27">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="S38" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="T38" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="U38" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V38" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W38" s="60" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B39" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="23">
-        <v>2030</v>
-      </c>
-      <c r="F39" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G39" s="27">
-        <v>1</v>
-      </c>
-      <c r="H39" s="27">
-        <v>0.9</v>
-      </c>
-      <c r="I39" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="J39" s="23">
-        <f>J38*0.95</f>
-        <v>1273</v>
-      </c>
-      <c r="K39" s="23">
-        <f t="shared" ref="K39:K40" si="0">K38*0.95</f>
-        <v>25.364999999999998</v>
-      </c>
-      <c r="O39" s="27"/>
-      <c r="Q39" s="65"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="60"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B40" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="23">
-        <v>2035</v>
-      </c>
-      <c r="F40" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G40" s="27">
-        <v>1</v>
-      </c>
-      <c r="H40" s="27">
-        <v>1.05</v>
-      </c>
-      <c r="I40" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="J40" s="23">
-        <f>J39*0.95</f>
-        <v>1209.3499999999999</v>
-      </c>
-      <c r="K40" s="23">
-        <f t="shared" si="0"/>
-        <v>24.096749999999997</v>
-      </c>
-      <c r="O40" s="27"/>
-      <c r="Q40" s="65"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="65"/>
-      <c r="W40" s="60"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B41" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="23">
-        <v>2040</v>
-      </c>
-      <c r="F41" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G41" s="27">
-        <v>1</v>
-      </c>
-      <c r="H41" s="27">
-        <v>2.1</v>
-      </c>
-      <c r="I41" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="O41" s="27"/>
-      <c r="Q41" s="65"/>
-      <c r="S41" s="23"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="65"/>
-      <c r="V41" s="65"/>
-      <c r="W41" s="60"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B42" s="23" t="str">
-        <f>S29</f>
-        <v>ELCRNSOL01</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="23">
-        <v>2022</v>
-      </c>
-      <c r="F42" s="23">
-        <v>2022</v>
-      </c>
-      <c r="G42" s="27">
-        <v>1</v>
-      </c>
-      <c r="H42" s="27">
-        <v>0.44679999999999997</v>
-      </c>
-      <c r="I42" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="J42" s="23">
-        <v>550</v>
-      </c>
-      <c r="K42" s="23">
-        <v>7</v>
-      </c>
-      <c r="L42" s="27">
-        <v>0</v>
-      </c>
-      <c r="M42" s="23">
-        <v>25</v>
-      </c>
-      <c r="N42" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O42" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="S42" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="T42" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="U42" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V42" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W42" s="60" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B43" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" s="23">
-        <v>2025</v>
-      </c>
-      <c r="G43" s="27">
-        <v>1</v>
-      </c>
-      <c r="H43" s="27">
-        <v>0.93679999999999997</v>
-      </c>
-      <c r="I43" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="L43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="Q43" s="65"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="60"/>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B44" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G44" s="27">
-        <v>1</v>
-      </c>
-      <c r="H44" s="27">
-        <v>2.5268000000000002</v>
-      </c>
-      <c r="I44" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="L44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="Q44" s="65"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="60"/>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B45" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G45" s="27">
-        <v>1</v>
-      </c>
-      <c r="H45" s="27">
-        <v>3.0908000000000002</v>
-      </c>
-      <c r="I45" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="L45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="Q45" s="65"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="60"/>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B46" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E46" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G46" s="27">
-        <v>1</v>
-      </c>
-      <c r="H46" s="27">
-        <v>4.2907999999999999</v>
-      </c>
-      <c r="I46" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="L46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="Q46" s="65"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="60"/>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B47" s="23" t="str">
-        <f>S38</f>
-        <v>ELCRNBSO01</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="23">
-        <v>2024</v>
-      </c>
-      <c r="F47" s="23">
-        <v>2024</v>
-      </c>
-      <c r="G47" s="27">
-        <v>1</v>
-      </c>
-      <c r="H47" s="27">
-        <v>0.06</v>
-      </c>
-      <c r="I47" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="J47" s="23">
-        <v>1090</v>
-      </c>
-      <c r="K47" s="23">
-        <f>J47*0.02</f>
-        <v>21.8</v>
-      </c>
-      <c r="L47" s="27">
-        <v>0</v>
-      </c>
-      <c r="M47" s="23">
-        <v>25</v>
-      </c>
-      <c r="N47" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O47" s="27">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B48" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="23">
-        <v>2025</v>
-      </c>
-      <c r="G48" s="27">
-        <v>1</v>
-      </c>
-      <c r="H48" s="27">
-        <v>0.39</v>
-      </c>
-      <c r="I48" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="L48" s="27"/>
-      <c r="O48" s="27"/>
-    </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B49" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G49" s="27">
-        <v>1</v>
-      </c>
-      <c r="H49" s="27">
-        <v>0.54</v>
-      </c>
-      <c r="I49" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="L49" s="27"/>
-      <c r="O49" s="27"/>
-    </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B50" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G50" s="27">
-        <v>1</v>
-      </c>
-      <c r="H50" s="27">
-        <v>0.54</v>
-      </c>
-      <c r="I50" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="L50" s="27"/>
-      <c r="O50" s="27"/>
-    </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B51" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E51" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G51" s="27">
-        <v>1</v>
-      </c>
-      <c r="H51" s="27">
-        <v>0.54</v>
-      </c>
-      <c r="I51" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="L51" s="27"/>
-      <c r="O51" s="27"/>
-    </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B52" s="23" t="str">
-        <f>S42</f>
-        <v>ELCRNPHY01</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" s="23">
-        <v>2030</v>
-      </c>
-      <c r="F52" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G52" s="27">
-        <v>1</v>
-      </c>
-      <c r="H52" s="27">
-        <v>1</v>
-      </c>
-      <c r="I52" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="J52" s="23">
-        <v>1990</v>
-      </c>
-      <c r="K52" s="23">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="L52" s="27">
-        <v>2</v>
-      </c>
-      <c r="M52" s="23">
-        <v>40</v>
-      </c>
-      <c r="N52" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O52" s="23">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B53" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G53" s="27">
-        <v>1</v>
-      </c>
-      <c r="H53" s="27">
-        <v>1</v>
-      </c>
-      <c r="I53" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="L53" s="27"/>
-    </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B54" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E54" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G54" s="27">
-        <v>1</v>
-      </c>
-      <c r="H54" s="27">
-        <v>1.8</v>
-      </c>
-      <c r="I54" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="L54" s="27"/>
-    </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B55" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E55" s="23">
-        <v>2025</v>
-      </c>
-      <c r="F55" s="23">
-        <v>2025</v>
-      </c>
-      <c r="G55" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H55" s="23">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="I55" s="23">
-        <v>0.15</v>
-      </c>
-      <c r="J55" s="23">
-        <v>490</v>
-      </c>
-      <c r="K55" s="23">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="M55" s="23">
-        <v>15</v>
-      </c>
-      <c r="N55" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O55" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="S55" s="23"/>
-      <c r="T55" s="23"/>
-    </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B56" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G56" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H56" s="23">
-        <v>1.754</v>
-      </c>
-      <c r="I56" s="23">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B57" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G57" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H57" s="23">
-        <v>1.754</v>
-      </c>
-      <c r="I57" s="23">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B58" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E58" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G58" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H58" s="23">
-        <v>2.254</v>
-      </c>
-      <c r="I58" s="23">
-        <v>0.15</v>
-      </c>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="0" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7963,7 +6892,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>52</v>
@@ -7982,11 +6911,11 @@
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="2">
         <v>2022</v>
@@ -8005,11 +6934,11 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E12" s="2">
         <v>2022</v>
@@ -8027,11 +6956,11 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E13" s="2">
         <v>2022</v>
@@ -8049,11 +6978,11 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E14" s="2">
         <v>2022</v>
@@ -8071,11 +7000,11 @@
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E15" s="2">
         <v>2022</v>
@@ -8092,11 +7021,11 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E16" s="2">
         <v>2022</v>
@@ -8113,10 +7042,10 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E17" s="2">
         <v>2022</v>
@@ -8130,7 +7059,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B18" s="60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
         <v>49</v>
@@ -8147,7 +7076,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
         <v>49</v>
@@ -8164,7 +7093,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D20" t="s">
         <v>49</v>
@@ -8182,7 +7111,7 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D21" t="s">
         <v>49</v>
@@ -8201,25 +7130,25 @@
       <c r="B24" s="44"/>
       <c r="C24" s="2"/>
       <c r="K24" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="O24" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -10785,7 +9714,7 @@
         <v>90</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q29" t="s">
         <v>226</v>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v02\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD6F12A-4056-40A2-9D85-9F3267687824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C529732-5A78-41E8-BD06-C501E0CFCAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ELC" sheetId="10" r:id="rId1"/>
+    <sheet name="ELC" sheetId="11" r:id="rId1"/>
     <sheet name="IND" sheetId="8" r:id="rId2"/>
     <sheet name="PRI" sheetId="7" r:id="rId3"/>
     <sheet name="RCA" sheetId="6" r:id="rId4"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2659,6 +2659,12 @@
   </si>
   <si>
     <t>IMPELCLAO3</t>
+  </si>
+  <si>
+    <t>PDP Installed Capacity</t>
+  </si>
+  <si>
+    <t>STOCK</t>
   </si>
 </sst>
 </file>
@@ -3395,13 +3401,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>21166</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3409,7 +3415,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32B77573-8AA6-4A45-9A0E-8369B938F12E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E286F4-4061-438E-BF13-395AC8691940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3417,8 +3423,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1314449" y="6016625"/>
-          <a:ext cx="7355417" cy="1452033"/>
+          <a:off x="1314449" y="10741025"/>
+          <a:ext cx="8231717" cy="1452033"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4677,8 +4683,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECAA6EC-6D7D-4104-9FDE-D9F949DD51B1}">
-  <dimension ref="A1:X28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6102E8E0-39ED-424E-B000-52DC9CECD6CF}">
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
@@ -4687,32 +4693,33 @@
     <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="23" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="23" customWidth="1"/>
-    <col min="12" max="12" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="7" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="P2" s="36"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="Q2" s="36"/>
       <c r="R2" s="36"/>
       <c r="S2" s="36"/>
@@ -4721,8 +4728,9 @@
       <c r="V2" s="36"/>
       <c r="W2" s="36"/>
       <c r="X2" s="36"/>
-    </row>
-    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="Y2" s="36"/>
+    </row>
+    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4741,11 +4749,11 @@
       <c r="G3" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="H3" s="22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>49</v>
       </c>
@@ -4764,51 +4772,51 @@
       <c r="G4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="59" t="s">
+      <c r="Q4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="60"/>
+      <c r="R4" s="59"/>
       <c r="S4" s="60"/>
       <c r="T4" s="60"/>
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="P5" s="61" t="s">
+      <c r="Y4" s="60"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Q5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="62" t="s">
+      <c r="R5" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="R5" s="61" t="s">
+      <c r="S5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="T5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="U5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="V5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="V5" s="61" t="s">
+      <c r="W5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="W5" s="61" t="s">
+      <c r="X5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="X5" s="61" t="s">
+      <c r="Y5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>56</v>
       </c>
@@ -4827,36 +4835,37 @@
       <c r="G6" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="H6" s="35"/>
-      <c r="P6" s="63" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="35"/>
+      <c r="Q6" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="Q6" s="63" t="s">
+      <c r="R6" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="S6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="T6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="U6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="V6" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="V6" s="63" t="s">
+      <c r="W6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="63" t="s">
+      <c r="X6" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="X6" s="63" t="s">
+      <c r="Y6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>65</v>
       </c>
@@ -4875,43 +4884,45 @@
       <c r="G7" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="32"/>
-      <c r="P7" s="2"/>
-      <c r="R7" s="2"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="32"/>
+      <c r="Q7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="P9" s="3"/>
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="5"/>
-      <c r="P10" s="59" t="s">
+      <c r="L10" s="7"/>
+      <c r="M10" s="5"/>
+      <c r="Q10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="60"/>
+      <c r="R10" s="59"/>
       <c r="S10" s="60"/>
       <c r="T10" s="60"/>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
       <c r="W10" s="60"/>
       <c r="X10" s="60"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="60"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4931,56 +4942,59 @@
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="J11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="M11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="N11" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="O11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O11" s="25"/>
-      <c r="P11" s="61" t="s">
+      <c r="P11" s="25"/>
+      <c r="Q11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="62" t="s">
+      <c r="R11" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="R11" s="61" t="s">
+      <c r="S11" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="T11" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="U11" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="V11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="V11" s="61" t="s">
+      <c r="W11" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="W11" s="61" t="s">
+      <c r="X11" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="X11" s="61" t="s">
+      <c r="Y11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -4996,55 +5010,58 @@
         <v>37</v>
       </c>
       <c r="H12" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="I12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="J12" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="K12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="L12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="M12" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="N12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="O12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="P12" s="64" t="s">
+      <c r="Q12" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="R12" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="S12" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="T12" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="T12" s="64" t="s">
+      <c r="U12" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="U12" s="64" t="s">
+      <c r="V12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="V12" s="64" t="s">
+      <c r="W12" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="W12" s="64" t="s">
+      <c r="X12" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="X12" s="64" t="s">
+      <c r="Y12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>78</v>
       </c>
@@ -5054,26 +5071,26 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="20"/>
+      <c r="J13" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="K13" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="L13" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="M13" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="N13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="19"/>
-      <c r="P13" s="63" t="s">
+      <c r="O13" s="19"/>
+      <c r="Q13" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="Q13" s="63"/>
       <c r="R13" s="63"/>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
@@ -5081,10 +5098,11 @@
       <c r="V13" s="63"/>
       <c r="W13" s="63"/>
       <c r="X13" s="63"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="63"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
-        <f>R14</f>
+        <f>S14</f>
         <v>ELCTNCOA01</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -5100,674 +5118,1374 @@
         <v>0.42</v>
       </c>
       <c r="H14" s="27">
+        <v>1.32</v>
+      </c>
+      <c r="I14" s="27">
         <v>0.85</v>
       </c>
-      <c r="I14" s="23">
+      <c r="J14" s="23">
         <v>1650</v>
       </c>
-      <c r="J14" s="27">
+      <c r="K14" s="27">
         <v>30</v>
       </c>
-      <c r="K14" s="27">
+      <c r="L14" s="27">
         <v>0.4</v>
       </c>
-      <c r="L14" s="23">
+      <c r="M14" s="23">
         <v>40</v>
       </c>
-      <c r="M14" s="23">
+      <c r="N14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="N14" s="27">
+      <c r="O14" s="27">
         <v>1</v>
       </c>
-      <c r="P14" s="65" t="s">
+      <c r="Q14" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="65"/>
+      <c r="S14" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="S14" s="65" t="s">
+      <c r="T14" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="T14" s="65" t="s">
+      <c r="U14" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="U14" s="65" t="s">
+      <c r="V14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="V14" s="60" t="s">
+      <c r="W14" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="W14" s="65"/>
       <c r="X14" s="65"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B15" s="23" t="str">
-        <f>R15</f>
-        <v>ELCTNOIL01</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="23">
-        <v>2023</v>
-      </c>
+      <c r="Y14" s="65"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="E15" s="23">
+        <v>2025</v>
+      </c>
+      <c r="F15" s="26"/>
       <c r="G15" s="27">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H15" s="27">
+        <v>1.32</v>
+      </c>
+      <c r="I15" s="27">
         <v>0.85</v>
       </c>
-      <c r="I15" s="23">
-        <v>250</v>
-      </c>
-      <c r="J15" s="27">
-        <v>20</v>
-      </c>
-      <c r="K15" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="L15" s="23">
-        <v>40</v>
-      </c>
-      <c r="M15" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N15" s="27">
-        <v>1</v>
-      </c>
-      <c r="P15" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="O15" s="27"/>
       <c r="Q15" s="65"/>
-      <c r="R15" s="65" t="s">
-        <v>153</v>
-      </c>
-      <c r="S15" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="T15" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U15" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V15" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="60"/>
       <c r="X15" s="65"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B16" s="23" t="str">
-        <f>R16</f>
-        <v>ELCTNGAS01</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>49</v>
-      </c>
+      <c r="Y15" s="65"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E16" s="23">
-        <v>2027</v>
-      </c>
-      <c r="F16" s="23">
-        <v>2027</v>
-      </c>
+        <v>2030</v>
+      </c>
+      <c r="F16" s="26"/>
       <c r="G16" s="27">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H16" s="27">
+        <v>1.44</v>
+      </c>
+      <c r="I16" s="27">
         <v>0.85</v>
       </c>
-      <c r="I16" s="23">
-        <v>1100</v>
-      </c>
-      <c r="J16" s="27">
-        <v>30</v>
-      </c>
-      <c r="K16" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="L16" s="23">
-        <v>40</v>
-      </c>
-      <c r="M16" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N16" s="27">
-        <v>1</v>
-      </c>
-      <c r="P16" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="O16" s="27"/>
       <c r="Q16" s="65"/>
-      <c r="R16" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="S16" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="T16" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U16" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V16" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W16" s="65"/>
-      <c r="X16" s="65" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
+      <c r="F17" s="26"/>
       <c r="G17" s="27">
-        <v>0.51</v>
-      </c>
-      <c r="H17" s="27"/>
-      <c r="J17" s="27"/>
+        <v>0.42</v>
+      </c>
+      <c r="H17" s="27">
+        <v>1.44</v>
+      </c>
+      <c r="I17" s="27">
+        <v>0.85</v>
+      </c>
       <c r="K17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="P17" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="L17" s="27"/>
+      <c r="O17" s="27"/>
       <c r="Q17" s="65"/>
-      <c r="R17" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="S17" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="T17" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U17" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V17" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="60"/>
       <c r="X17" s="65"/>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="65"/>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
+      <c r="F18" s="26"/>
       <c r="G18" s="27">
-        <v>0.52</v>
-      </c>
-      <c r="H18" s="27"/>
-      <c r="J18" s="27"/>
+        <v>0.42</v>
+      </c>
+      <c r="H18" s="27">
+        <v>1.44</v>
+      </c>
+      <c r="I18" s="27">
+        <v>0.85</v>
+      </c>
       <c r="K18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="P18" s="65" t="s">
+      <c r="L18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B19" s="23" t="str">
+        <f>S19</f>
+        <v>ELCTNOIL01</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="23">
+        <v>2023</v>
+      </c>
+      <c r="G19" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="H19" s="27">
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="I19" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="J19" s="23">
+        <v>250</v>
+      </c>
+      <c r="K19" s="27">
+        <v>20</v>
+      </c>
+      <c r="L19" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="23">
+        <v>40</v>
+      </c>
+      <c r="N19" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O19" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="S18" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="T18" s="65" t="s">
+      <c r="R19" s="65"/>
+      <c r="S19" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="T19" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="U19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="U18" s="65" t="s">
+      <c r="V19" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="V18" s="60" t="s">
+      <c r="W19" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-    </row>
-    <row r="19" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E19" s="23">
-        <v>2045</v>
-      </c>
-      <c r="G19" s="27">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="P19" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="S19" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="T19" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U19" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V19" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W19" s="65"/>
       <c r="X19" s="65"/>
-    </row>
-    <row r="20" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="23" t="str">
-        <f t="shared" ref="B20:B22" si="0">R17</f>
-        <v>ELCRNBIO01</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="23">
-        <v>2028</v>
+      <c r="Y19" s="65"/>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E20" s="23">
+        <v>2025</v>
       </c>
       <c r="G20" s="27">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H20" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="I20" s="23">
-        <v>2500</v>
-      </c>
-      <c r="J20" s="23">
-        <v>30</v>
-      </c>
-      <c r="K20" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="L20" s="23">
-        <v>25</v>
-      </c>
-      <c r="M20" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N20" s="27">
-        <v>1</v>
-      </c>
-      <c r="P20" s="65" t="s">
-        <v>81</v>
-      </c>
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="I20" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="O20" s="27"/>
       <c r="Q20" s="65"/>
-      <c r="R20" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="S20" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="T20" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U20" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V20" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="65"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="60"/>
       <c r="X20" s="65"/>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B21" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v>ELCRNHYD01</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="23">
-        <v>2026</v>
+      <c r="Y20" s="65"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E21" s="23">
+        <v>2030</v>
       </c>
       <c r="G21" s="27">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="I21" s="23">
-        <v>3000</v>
-      </c>
-      <c r="J21" s="23">
-        <v>35</v>
-      </c>
-      <c r="K21" s="27">
-        <v>2</v>
-      </c>
-      <c r="L21" s="23">
-        <v>50</v>
-      </c>
-      <c r="M21" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N21" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="P21" t="s">
-        <v>285</v>
-      </c>
-      <c r="R21" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="S21" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="T21" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U21" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V21" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="W21" s="65"/>
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="I21" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="60"/>
       <c r="X21" s="65"/>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v>ELCRNWIN01</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="23">
-        <v>2026</v>
+      <c r="Y21" s="65"/>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E22" s="23">
+        <v>2035</v>
       </c>
       <c r="G22" s="27">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H22" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="I22" s="23">
-        <v>1340</v>
-      </c>
-      <c r="J22" s="23">
-        <v>26.7</v>
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="I22" s="27">
+        <v>0.85</v>
       </c>
       <c r="K22" s="27"/>
-      <c r="L22" s="23">
-        <v>25</v>
-      </c>
-      <c r="M22" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N22" s="27">
+      <c r="L22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E23" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G23" s="27">
         <v>0.3</v>
       </c>
-      <c r="P22" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R22" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="S22" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="T22" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U22" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V22" s="60" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="F23" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G23" s="27">
-        <v>1</v>
-      </c>
       <c r="H23" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="I23" s="23">
-        <f>I22*0.95</f>
-        <v>1273</v>
-      </c>
-      <c r="J23" s="23">
-        <f t="shared" ref="J23:J24" si="1">J22*0.95</f>
-        <v>25.364999999999998</v>
-      </c>
-      <c r="N23" s="27"/>
-      <c r="P23" s="65"/>
-      <c r="R23" s="23"/>
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="I23" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
       <c r="S23" s="65"/>
       <c r="T23" s="65"/>
       <c r="U23" s="65"/>
-      <c r="V23" s="60"/>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="V23" s="65"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B24" s="23" t="str">
+        <f>S24</f>
+        <v>ELCTNGAS01</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="F24" s="23">
+        <v>2027</v>
+      </c>
+      <c r="G24" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I24" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="J24" s="23">
+        <v>1100</v>
+      </c>
+      <c r="K24" s="27">
+        <v>30</v>
+      </c>
+      <c r="L24" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="M24" s="23">
+        <v>40</v>
+      </c>
+      <c r="N24" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O24" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="T24" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="U24" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V24" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W24" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E25" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G25" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I25" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E26" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G26" s="27">
+        <v>0.51</v>
+      </c>
+      <c r="H26" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I26" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="Q26" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="T26" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="U26" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V26" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W26" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E27" s="23">
         <v>2040</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G27" s="27">
+        <v>0.52</v>
+      </c>
+      <c r="H27" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I27" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="Q27" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="T27" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="U27" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V27" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W27" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
+    </row>
+    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E28" s="23">
+        <v>2045</v>
+      </c>
+      <c r="G28" s="27">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H28" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I28" s="27">
+        <v>0.85</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="Q28" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="T28" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="U28" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V28" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W28" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+    </row>
+    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="23" t="str">
+        <f t="shared" ref="B29" si="0">S26</f>
+        <v>ELCRNBIO01</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="23">
+        <v>2028</v>
+      </c>
+      <c r="G29" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="H29" s="27">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="I29" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="J29" s="23">
+        <v>2500</v>
+      </c>
+      <c r="K29" s="23">
+        <v>30</v>
+      </c>
+      <c r="L29" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="M29" s="23">
+        <v>25</v>
+      </c>
+      <c r="N29" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O29" s="27">
         <v>1</v>
       </c>
-      <c r="H24" s="27">
+      <c r="Q29" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="T29" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="U29" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V29" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W29" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="65"/>
+    </row>
+    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G30" s="27">
         <v>0.35</v>
       </c>
-      <c r="I24" s="23">
-        <f>I23*0.95</f>
+      <c r="H30" s="27">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I30" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="65"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="65"/>
+    </row>
+    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G31" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="H31" s="27">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I31" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
+    </row>
+    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G32" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="H32" s="27">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I32" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="65"/>
+      <c r="T32" s="65"/>
+      <c r="U32" s="65"/>
+      <c r="V32" s="65"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="65"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B33" s="23" t="str">
+        <f>S27</f>
+        <v>ELCRNHYD01</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="23">
+        <v>2023</v>
+      </c>
+      <c r="G33" s="27">
+        <v>1</v>
+      </c>
+      <c r="H33" s="27">
+        <v>1.3301000000000001</v>
+      </c>
+      <c r="I33" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="23">
+        <v>3000</v>
+      </c>
+      <c r="K33" s="23">
+        <v>35</v>
+      </c>
+      <c r="L33" s="27">
+        <v>2</v>
+      </c>
+      <c r="M33" s="23">
+        <v>50</v>
+      </c>
+      <c r="N33" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O33" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>285</v>
+      </c>
+      <c r="S33" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="T33" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="U33" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V33" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W33" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="65"/>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E34" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1</v>
+      </c>
+      <c r="H34" s="27">
+        <v>1.3351</v>
+      </c>
+      <c r="I34" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="L34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="60"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E35" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G35" s="27">
+        <v>1</v>
+      </c>
+      <c r="H35" s="27">
+        <v>1.9951000000000001</v>
+      </c>
+      <c r="I35" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E36" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G36" s="27">
+        <v>1</v>
+      </c>
+      <c r="H36" s="27">
+        <v>2.7111000000000001</v>
+      </c>
+      <c r="I36" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="L36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E37" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G37" s="27">
+        <v>1</v>
+      </c>
+      <c r="H37" s="27">
+        <v>2.8811</v>
+      </c>
+      <c r="I37" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="L37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="60"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B38" s="23" t="str">
+        <f>S28</f>
+        <v>ELCRNWIN01</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="23">
+        <v>2026</v>
+      </c>
+      <c r="G38" s="27">
+        <v>1</v>
+      </c>
+      <c r="H38" s="27">
+        <v>0.15</v>
+      </c>
+      <c r="I38" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="J38" s="23">
+        <v>1340</v>
+      </c>
+      <c r="K38" s="23">
+        <v>26.7</v>
+      </c>
+      <c r="L38" s="27"/>
+      <c r="M38" s="23">
+        <v>25</v>
+      </c>
+      <c r="N38" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O38" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="S38" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="T38" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="U38" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V38" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="F39" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G39" s="27">
+        <v>1</v>
+      </c>
+      <c r="H39" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="I39" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="J39" s="23">
+        <f>J38*0.95</f>
+        <v>1273</v>
+      </c>
+      <c r="K39" s="23">
+        <f t="shared" ref="K39:K40" si="1">K38*0.95</f>
+        <v>25.364999999999998</v>
+      </c>
+      <c r="O39" s="27"/>
+      <c r="Q39" s="65"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="60"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="F40" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G40" s="27">
+        <v>1</v>
+      </c>
+      <c r="H40" s="27">
+        <v>1.05</v>
+      </c>
+      <c r="I40" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="J40" s="23">
+        <f>J39*0.95</f>
         <v>1209.3499999999999</v>
       </c>
-      <c r="J24" s="23">
+      <c r="K40" s="23">
         <f t="shared" si="1"/>
         <v>24.096749999999997</v>
       </c>
-      <c r="N24" s="27"/>
-      <c r="P24" s="65"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="65"/>
-      <c r="T24" s="65"/>
-      <c r="U24" s="65"/>
-      <c r="V24" s="60"/>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B25" s="23" t="str">
-        <f>R20</f>
+      <c r="O40" s="27"/>
+      <c r="Q40" s="65"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="65"/>
+      <c r="W40" s="60"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="F41" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G41" s="27">
+        <v>1</v>
+      </c>
+      <c r="H41" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="I41" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="O41" s="27"/>
+      <c r="Q41" s="65"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="60"/>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B42" s="23" t="str">
+        <f>S29</f>
         <v>ELCRNSOL01</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D42" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F42" s="23">
         <v>2022</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G42" s="27">
         <v>1</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H42" s="27">
+        <v>0.44679999999999997</v>
+      </c>
+      <c r="I42" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J42" s="23">
+        <v>550</v>
+      </c>
+      <c r="K42" s="23">
+        <v>7</v>
+      </c>
+      <c r="L42" s="27">
+        <v>0</v>
+      </c>
+      <c r="M42" s="23">
+        <v>25</v>
+      </c>
+      <c r="N42" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O42" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="S42" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="T42" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="U42" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="V42" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="W42" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E43" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G43" s="27">
+        <v>1</v>
+      </c>
+      <c r="H43" s="27">
+        <v>0.93679999999999997</v>
+      </c>
+      <c r="I43" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="Q43" s="65"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="60"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E44" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G44" s="27">
+        <v>1</v>
+      </c>
+      <c r="H44" s="27">
+        <v>2.5268000000000002</v>
+      </c>
+      <c r="I44" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="Q44" s="65"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="60"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E45" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G45" s="27">
+        <v>1</v>
+      </c>
+      <c r="H45" s="27">
+        <v>3.0908000000000002</v>
+      </c>
+      <c r="I45" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L45" s="27"/>
+      <c r="O45" s="27"/>
+      <c r="Q45" s="65"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="65"/>
+      <c r="U45" s="65"/>
+      <c r="V45" s="65"/>
+      <c r="W45" s="60"/>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E46" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G46" s="27">
+        <v>1</v>
+      </c>
+      <c r="H46" s="27">
+        <v>4.2907999999999999</v>
+      </c>
+      <c r="I46" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="Q46" s="65"/>
+      <c r="S46" s="23"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="65"/>
+      <c r="V46" s="65"/>
+      <c r="W46" s="60"/>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B47" s="23" t="str">
+        <f>S38</f>
+        <v>ELCRNBSO01</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="23">
+        <v>2024</v>
+      </c>
+      <c r="G47" s="27">
+        <v>1</v>
+      </c>
+      <c r="H47" s="27">
+        <v>0.06</v>
+      </c>
+      <c r="I47" s="27">
         <v>0.25</v>
       </c>
-      <c r="I25" s="23">
-        <v>550</v>
-      </c>
-      <c r="J25" s="23">
-        <v>7</v>
-      </c>
-      <c r="K25" s="27">
+      <c r="J47" s="23">
+        <v>1090</v>
+      </c>
+      <c r="K47" s="23">
+        <f>J47*0.02</f>
+        <v>21.8</v>
+      </c>
+      <c r="L47" s="27">
         <v>0</v>
       </c>
-      <c r="L25" s="23">
+      <c r="M47" s="23">
         <v>25</v>
       </c>
-      <c r="M25" s="23">
+      <c r="N47" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="N25" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="P25" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R25" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="S25" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="T25" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="U25" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="V25" s="60" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B26" s="23" t="str">
-        <f>R22</f>
-        <v>ELCRNBSO01</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" s="23" t="s">
+      <c r="O47" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="E48" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G48" s="27">
+        <v>1</v>
+      </c>
+      <c r="H48" s="27">
+        <v>0.39</v>
+      </c>
+      <c r="I48" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="O48" s="27"/>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E49" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G49" s="27">
+        <v>1</v>
+      </c>
+      <c r="H49" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="I49" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L49" s="27"/>
+      <c r="O49" s="27"/>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E50" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G50" s="27">
+        <v>1</v>
+      </c>
+      <c r="H50" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="I50" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L50" s="27"/>
+      <c r="O50" s="27"/>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E51" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G51" s="27">
+        <v>1</v>
+      </c>
+      <c r="H51" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="I51" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L51" s="27"/>
+      <c r="O51" s="27"/>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B52" s="23" t="str">
+        <f>S42</f>
+        <v>ELCRNPHY01</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="23">
-        <v>2026</v>
-      </c>
-      <c r="G26" s="27">
+      <c r="F52" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G52" s="27">
         <v>1</v>
       </c>
-      <c r="H26" s="27">
-        <v>0.3</v>
-      </c>
-      <c r="I26" s="23">
-        <v>1090</v>
-      </c>
-      <c r="J26" s="23">
-        <f>I26*0.02</f>
-        <v>21.8</v>
-      </c>
-      <c r="K26" s="27">
-        <v>0</v>
-      </c>
-      <c r="L26" s="23">
-        <v>25</v>
-      </c>
-      <c r="M26" s="23">
+      <c r="H52" s="27">
+        <v>1</v>
+      </c>
+      <c r="I52" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="J52" s="23">
+        <v>1990</v>
+      </c>
+      <c r="K52" s="23">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="L52" s="27">
+        <v>2</v>
+      </c>
+      <c r="M52" s="23">
+        <v>40</v>
+      </c>
+      <c r="N52" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="N26" s="27">
+      <c r="O52" s="23">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E53" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G53" s="27">
+        <v>1</v>
+      </c>
+      <c r="H53" s="27">
+        <v>1</v>
+      </c>
+      <c r="I53" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="L53" s="27"/>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E54" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G54" s="27">
+        <v>1</v>
+      </c>
+      <c r="H54" s="27">
+        <v>1.8</v>
+      </c>
+      <c r="I54" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="L54" s="27"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B55" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G55" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H55" s="23">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="I55" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="J55" s="23">
+        <v>490</v>
+      </c>
+      <c r="K55" s="23">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M55" s="23">
+        <v>15</v>
+      </c>
+      <c r="N55" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O55" s="23">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B27" s="23" t="str">
-        <f>R25</f>
-        <v>ELCRNPHY01</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F27" s="23">
-        <v>2028</v>
-      </c>
-      <c r="G27" s="27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="I27" s="23">
-        <v>1990</v>
-      </c>
-      <c r="J27" s="23">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="K27" s="27">
-        <v>2</v>
-      </c>
-      <c r="L27" s="23">
-        <v>40</v>
-      </c>
-      <c r="M27" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N27" s="23">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B28" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="23">
-        <v>2026</v>
-      </c>
-      <c r="G28" s="23">
+      <c r="S55" s="23"/>
+      <c r="T55" s="23"/>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E56" s="23">
+        <v>2030</v>
+      </c>
+      <c r="G56" s="23">
         <v>0.85</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H56" s="23">
+        <v>1.754</v>
+      </c>
+      <c r="I56" s="23">
         <v>0.15</v>
       </c>
-      <c r="I28" s="23">
-        <v>490</v>
-      </c>
-      <c r="J28" s="23">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L28" s="23">
-        <v>15</v>
-      </c>
-      <c r="M28" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="N28" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E57" s="23">
+        <v>2035</v>
+      </c>
+      <c r="G57" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H57" s="23">
+        <v>1.754</v>
+      </c>
+      <c r="I57" s="23">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E58" s="23">
+        <v>2040</v>
+      </c>
+      <c r="G58" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H58" s="23">
+        <v>2.254</v>
+      </c>
+      <c r="I58" s="23">
+        <v>0.15</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v02\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C529732-5A78-41E8-BD06-C501E0CFCAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE7F015-6462-4CB2-A219-429071561DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="11" r:id="rId1"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="315">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2664,7 +2664,10 @@
     <t>PDP Installed Capacity</t>
   </si>
   <si>
-    <t>STOCK</t>
+    <t>CAP_BND</t>
+  </si>
+  <si>
+    <t>NCAP_START</t>
   </si>
 </sst>
 </file>
@@ -4922,7 +4925,7 @@
       <c r="X10" s="60"/>
       <c r="Y10" s="60"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>98</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>15</v>
+        <v>314</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>17</v>
@@ -5167,7 +5170,9 @@
       <c r="E15" s="23">
         <v>2025</v>
       </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="23">
+        <v>2025</v>
+      </c>
       <c r="G15" s="27">
         <v>0.42</v>
       </c>
@@ -5194,7 +5199,9 @@
       <c r="E16" s="23">
         <v>2030</v>
       </c>
-      <c r="F16" s="26"/>
+      <c r="F16" s="23">
+        <v>2030</v>
+      </c>
       <c r="G16" s="27">
         <v>0.42</v>
       </c>
@@ -5221,7 +5228,9 @@
       <c r="E17" s="23">
         <v>2035</v>
       </c>
-      <c r="F17" s="26"/>
+      <c r="F17" s="23">
+        <v>2035</v>
+      </c>
       <c r="G17" s="27">
         <v>0.42</v>
       </c>
@@ -5248,7 +5257,9 @@
       <c r="E18" s="23">
         <v>2040</v>
       </c>
-      <c r="F18" s="26"/>
+      <c r="F18" s="23">
+        <v>2040</v>
+      </c>
       <c r="G18" s="27">
         <v>0.42</v>
       </c>
@@ -5338,6 +5349,9 @@
       <c r="E20" s="23">
         <v>2025</v>
       </c>
+      <c r="F20" s="23">
+        <v>2025</v>
+      </c>
       <c r="G20" s="27">
         <v>0.3</v>
       </c>
@@ -5364,6 +5378,9 @@
       <c r="E21" s="23">
         <v>2030</v>
       </c>
+      <c r="F21" s="23">
+        <v>2030</v>
+      </c>
       <c r="G21" s="27">
         <v>0.3</v>
       </c>
@@ -5390,6 +5407,9 @@
       <c r="E22" s="23">
         <v>2035</v>
       </c>
+      <c r="F22" s="23">
+        <v>2035</v>
+      </c>
       <c r="G22" s="27">
         <v>0.3</v>
       </c>
@@ -5416,6 +5436,9 @@
       <c r="E23" s="23">
         <v>2040</v>
       </c>
+      <c r="F23" s="23">
+        <v>2040</v>
+      </c>
       <c r="G23" s="27">
         <v>0.3</v>
       </c>
@@ -5507,6 +5530,9 @@
       <c r="E25" s="23">
         <v>2030</v>
       </c>
+      <c r="F25" s="23">
+        <v>2030</v>
+      </c>
       <c r="G25" s="27">
         <v>0.5</v>
       </c>
@@ -5533,6 +5559,9 @@
       <c r="E26" s="23">
         <v>2035</v>
       </c>
+      <c r="F26" s="23">
+        <v>2035</v>
+      </c>
       <c r="G26" s="27">
         <v>0.51</v>
       </c>
@@ -5571,6 +5600,9 @@
       <c r="E27" s="23">
         <v>2040</v>
       </c>
+      <c r="F27" s="23">
+        <v>2040</v>
+      </c>
       <c r="G27" s="27">
         <v>0.52</v>
       </c>
@@ -5609,6 +5641,9 @@
       <c r="E28" s="23">
         <v>2045</v>
       </c>
+      <c r="F28" s="23">
+        <v>2045</v>
+      </c>
       <c r="G28" s="27">
         <v>0.55000000000000004</v>
       </c>
@@ -5708,6 +5743,9 @@
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="23">
+        <v>2030</v>
+      </c>
+      <c r="F30" s="23">
         <v>2030</v>
       </c>
       <c r="G30" s="27">
@@ -5735,6 +5773,9 @@
       <c r="E31" s="23">
         <v>2035</v>
       </c>
+      <c r="F31" s="23">
+        <v>2035</v>
+      </c>
       <c r="G31" s="27">
         <v>0.35</v>
       </c>
@@ -5760,6 +5801,9 @@
       <c r="E32" s="23">
         <v>2040</v>
       </c>
+      <c r="F32" s="23">
+        <v>2040</v>
+      </c>
       <c r="G32" s="27">
         <v>0.35</v>
       </c>
@@ -5847,6 +5891,9 @@
       <c r="E34" s="23">
         <v>2025</v>
       </c>
+      <c r="F34" s="23">
+        <v>2025</v>
+      </c>
       <c r="G34" s="27">
         <v>1</v>
       </c>
@@ -5870,6 +5917,9 @@
       <c r="E35" s="23">
         <v>2030</v>
       </c>
+      <c r="F35" s="23">
+        <v>2030</v>
+      </c>
       <c r="G35" s="27">
         <v>1</v>
       </c>
@@ -5893,6 +5943,9 @@
       <c r="E36" s="23">
         <v>2035</v>
       </c>
+      <c r="F36" s="23">
+        <v>2035</v>
+      </c>
       <c r="G36" s="27">
         <v>1</v>
       </c>
@@ -5916,6 +5969,9 @@
       <c r="E37" s="23">
         <v>2040</v>
       </c>
+      <c r="F37" s="23">
+        <v>2040</v>
+      </c>
       <c r="G37" s="27">
         <v>1</v>
       </c>
@@ -6136,6 +6192,9 @@
       <c r="E43" s="23">
         <v>2025</v>
       </c>
+      <c r="F43" s="23">
+        <v>2025</v>
+      </c>
       <c r="G43" s="27">
         <v>1</v>
       </c>
@@ -6158,6 +6217,9 @@
       <c r="E44" s="23">
         <v>2030</v>
       </c>
+      <c r="F44" s="23">
+        <v>2030</v>
+      </c>
       <c r="G44" s="27">
         <v>1</v>
       </c>
@@ -6180,6 +6242,9 @@
       <c r="E45" s="23">
         <v>2035</v>
       </c>
+      <c r="F45" s="23">
+        <v>2035</v>
+      </c>
       <c r="G45" s="27">
         <v>1</v>
       </c>
@@ -6202,6 +6267,9 @@
       <c r="E46" s="23">
         <v>2040</v>
       </c>
+      <c r="F46" s="23">
+        <v>2040</v>
+      </c>
       <c r="G46" s="27">
         <v>1</v>
       </c>
@@ -6267,6 +6335,9 @@
       <c r="E48" s="23">
         <v>2025</v>
       </c>
+      <c r="F48" s="23">
+        <v>2025</v>
+      </c>
       <c r="G48" s="27">
         <v>1</v>
       </c>
@@ -6283,6 +6354,9 @@
       <c r="E49" s="23">
         <v>2030</v>
       </c>
+      <c r="F49" s="23">
+        <v>2030</v>
+      </c>
       <c r="G49" s="27">
         <v>1</v>
       </c>
@@ -6299,6 +6373,9 @@
       <c r="E50" s="23">
         <v>2035</v>
       </c>
+      <c r="F50" s="23">
+        <v>2035</v>
+      </c>
       <c r="G50" s="27">
         <v>1</v>
       </c>
@@ -6313,6 +6390,9 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E51" s="23">
+        <v>2040</v>
+      </c>
+      <c r="F51" s="23">
         <v>2040</v>
       </c>
       <c r="G51" s="27">
@@ -6373,6 +6453,9 @@
       <c r="E53" s="23">
         <v>2035</v>
       </c>
+      <c r="F53" s="23">
+        <v>2035</v>
+      </c>
       <c r="G53" s="27">
         <v>1</v>
       </c>
@@ -6388,6 +6471,9 @@
       <c r="E54" s="23">
         <v>2040</v>
       </c>
+      <c r="F54" s="23">
+        <v>2040</v>
+      </c>
       <c r="G54" s="27">
         <v>1</v>
       </c>
@@ -6443,6 +6529,9 @@
       <c r="E56" s="23">
         <v>2030</v>
       </c>
+      <c r="F56" s="23">
+        <v>2030</v>
+      </c>
       <c r="G56" s="23">
         <v>0.85</v>
       </c>
@@ -6457,6 +6546,9 @@
       <c r="E57" s="23">
         <v>2035</v>
       </c>
+      <c r="F57" s="23">
+        <v>2035</v>
+      </c>
       <c r="G57" s="23">
         <v>0.85</v>
       </c>
@@ -6469,6 +6561,9 @@
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E58" s="23">
+        <v>2040</v>
+      </c>
+      <c r="F58" s="23">
         <v>2040</v>
       </c>
       <c r="G58" s="23">

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v02\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE7F015-6462-4CB2-A219-429071561DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF91B727-37AD-4A15-9112-EAFCE4F73C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="11" r:id="rId1"/>
@@ -4695,7 +4695,7 @@
     <col min="3" max="3" width="18.28515625" style="23" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="23" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v02\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020-v02\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF91B727-37AD-4A15-9112-EAFCE4F73C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FDCC61-7013-4F4A-8D97-C42DB7BA04AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ELC" sheetId="11" r:id="rId1"/>
+    <sheet name="ELC" sheetId="4" r:id="rId1"/>
     <sheet name="IND" sheetId="8" r:id="rId2"/>
     <sheet name="PRI" sheetId="7" r:id="rId3"/>
     <sheet name="RCA" sheetId="6" r:id="rId4"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="290">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2088,6 +2088,9 @@
     <t>Annual Production Bound</t>
   </si>
   <si>
+    <t>M€2005/PJ</t>
+  </si>
+  <si>
     <t>AGR</t>
   </si>
   <si>
@@ -2583,91 +2586,13 @@
     <t>ELE, STG</t>
   </si>
   <si>
+    <t>PDP Installed Capacity</t>
+  </si>
+  <si>
+    <t>NCAP_BND</t>
+  </si>
+  <si>
     <t>TRAINHFO1</t>
-  </si>
-  <si>
-    <t>IMPDSL1</t>
-  </si>
-  <si>
-    <t>IMPKER1</t>
-  </si>
-  <si>
-    <t>IMPLPG1</t>
-  </si>
-  <si>
-    <t>IMPGSL1</t>
-  </si>
-  <si>
-    <t>IMPNAP1</t>
-  </si>
-  <si>
-    <t>IMPHFO1</t>
-  </si>
-  <si>
-    <t>IMPOPP1</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>GSL</t>
-  </si>
-  <si>
-    <t>NAP</t>
-  </si>
-  <si>
-    <t>HFO</t>
-  </si>
-  <si>
-    <t>OPP</t>
-  </si>
-  <si>
-    <t>M$2021/PJ</t>
-  </si>
-  <si>
-    <t>IMPELCVN1</t>
-  </si>
-  <si>
-    <t>IMPELCLAO1</t>
-  </si>
-  <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>MWh</t>
-  </si>
-  <si>
-    <t>IMPELCLAO2</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>tc</t>
-  </si>
-  <si>
-    <t>cost/PJ</t>
-  </si>
-  <si>
-    <t>IMPELCLAO3</t>
-  </si>
-  <si>
-    <t>PDP Installed Capacity</t>
-  </si>
-  <si>
-    <t>CAP_BND</t>
-  </si>
-  <si>
-    <t>NCAP_START</t>
   </si>
 </sst>
 </file>
@@ -2681,7 +2606,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2883,13 +2808,8 @@
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2944,12 +2864,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF1FB"/>
         <bgColor rgb="FFEAF1FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3093,7 +3007,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3161,9 +3075,8 @@
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3257,6 +3170,7 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3318,17 +3232,12 @@
     <xf numFmtId="49" fontId="31" fillId="10" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="59" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="59">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="calculated" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Calculation 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Comma" xfId="59" builtinId="3"/>
     <cellStyle name="Comma 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma 11" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Comma 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -3415,10 +3324,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+        <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E286F4-4061-438E-BF13-395AC8691940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE448FC7-5FA6-4416-A543-F7B93A5592EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3426,8 +3335,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1314449" y="10741025"/>
-          <a:ext cx="8231717" cy="1452033"/>
+          <a:off x="1311274" y="5296958"/>
+          <a:ext cx="7356475" cy="1423458"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4686,7 +4595,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6102E8E0-39ED-424E-B000-52DC9CECD6CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4695,7 +4605,7 @@
     <col min="3" max="3" width="18.28515625" style="23" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
@@ -4773,49 +4683,49 @@
         <v>53</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="59" t="s">
+      <c r="Q4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="61"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q5" s="61" t="s">
+      <c r="Q5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="62" t="s">
+      <c r="R5" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="S5" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="T5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="61" t="s">
+      <c r="V5" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="61" t="s">
+      <c r="W5" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="61" t="s">
+      <c r="X5" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="61" t="s">
+      <c r="Y5" s="62" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4836,35 +4746,35 @@
         <v>60</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="35"/>
-      <c r="Q6" s="63" t="s">
+      <c r="Q6" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="R6" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="S6" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="T6" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="U6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="63" t="s">
+      <c r="V6" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="63" t="s">
+      <c r="W6" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="63" t="s">
+      <c r="X6" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" s="63" t="s">
+      <c r="Y6" s="64" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4885,7 +4795,7 @@
         <v>54</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="32"/>
@@ -4913,19 +4823,19 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="5"/>
-      <c r="Q10" s="59" t="s">
+      <c r="Q10" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="59"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-    </row>
-    <row r="11" spans="1:25" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="R10" s="60"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4939,13 +4849,13 @@
         <v>98</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>314</v>
+        <v>15</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -4963,37 +4873,37 @@
         <v>69</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O11" s="15" t="s">
         <v>70</v>
       </c>
       <c r="P11" s="25"/>
-      <c r="Q11" s="61" t="s">
+      <c r="Q11" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="R11" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="S11" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="T11" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="U11" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="V11" s="61" t="s">
+      <c r="V11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="W11" s="61" t="s">
+      <c r="W11" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="X11" s="61" t="s">
+      <c r="X11" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="Y11" s="61" t="s">
+      <c r="Y11" s="62" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5013,7 +4923,7 @@
         <v>37</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>72</v>
@@ -5028,7 +4938,7 @@
         <v>41</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>38</v>
@@ -5036,31 +4946,31 @@
       <c r="O12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="Q12" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="R12" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="S12" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="T12" s="64" t="s">
+      <c r="T12" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="64" t="s">
+      <c r="U12" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="64" t="s">
+      <c r="V12" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="64" t="s">
+      <c r="W12" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="X12" s="64" t="s">
+      <c r="X12" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="Y12" s="64" t="s">
+      <c r="Y12" s="65" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5076,13 +4986,13 @@
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M13" s="19" t="s">
         <v>79</v>
@@ -5091,17 +5001,17 @@
         <v>80</v>
       </c>
       <c r="O13" s="19"/>
-      <c r="Q13" s="63" t="s">
+      <c r="Q13" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="63"/>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="63"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
@@ -5144,35 +5054,33 @@
       <c r="O14" s="27">
         <v>1</v>
       </c>
-      <c r="Q14" s="65" t="s">
+      <c r="Q14" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="T14" s="65" t="s">
+      <c r="R14" s="66"/>
+      <c r="S14" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="T14" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="U14" s="65" t="s">
+      <c r="U14" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V14" s="65" t="s">
+      <c r="V14" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W14" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
+      <c r="W14" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X14" s="66"/>
+      <c r="Y14" s="66"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E15" s="23">
         <v>2025</v>
       </c>
-      <c r="F15" s="23">
-        <v>2025</v>
-      </c>
+      <c r="F15" s="26"/>
       <c r="G15" s="27">
         <v>0.42</v>
       </c>
@@ -5185,23 +5093,21 @@
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
       <c r="O15" s="27"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="65"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E16" s="23">
         <v>2030</v>
       </c>
-      <c r="F16" s="23">
-        <v>2030</v>
-      </c>
+      <c r="F16" s="26"/>
       <c r="G16" s="27">
         <v>0.42</v>
       </c>
@@ -5214,23 +5120,21 @@
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
       <c r="O16" s="27"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="65"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="61"/>
+      <c r="X16" s="66"/>
+      <c r="Y16" s="66"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
-      <c r="F17" s="23">
-        <v>2035</v>
-      </c>
+      <c r="F17" s="26"/>
       <c r="G17" s="27">
         <v>0.42</v>
       </c>
@@ -5243,23 +5147,21 @@
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
       <c r="O17" s="27"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="66"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
-      <c r="F18" s="23">
-        <v>2040</v>
-      </c>
+      <c r="F18" s="26"/>
       <c r="G18" s="27">
         <v>0.42</v>
       </c>
@@ -5272,15 +5174,15 @@
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
       <c r="O18" s="27"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="61"/>
+      <c r="X18" s="66"/>
+      <c r="Y18" s="66"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="str">
@@ -5323,35 +5225,32 @@
       <c r="O19" s="27">
         <v>1</v>
       </c>
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65" t="s">
-        <v>153</v>
-      </c>
-      <c r="T19" s="65" t="s">
+      <c r="R19" s="66"/>
+      <c r="S19" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="T19" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="65" t="s">
+      <c r="U19" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V19" s="65" t="s">
+      <c r="V19" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
+      <c r="W19" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X19" s="66"/>
+      <c r="Y19" s="66"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E20" s="23">
         <v>2025</v>
       </c>
-      <c r="F20" s="23">
-        <v>2025</v>
-      </c>
       <c r="G20" s="27">
         <v>0.3</v>
       </c>
@@ -5364,23 +5263,20 @@
       <c r="K20" s="27"/>
       <c r="L20" s="27"/>
       <c r="O20" s="27"/>
-      <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="65"/>
-      <c r="Y20" s="65"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E21" s="23">
         <v>2030</v>
       </c>
-      <c r="F21" s="23">
-        <v>2030</v>
-      </c>
       <c r="G21" s="27">
         <v>0.3</v>
       </c>
@@ -5393,23 +5289,20 @@
       <c r="K21" s="27"/>
       <c r="L21" s="27"/>
       <c r="O21" s="27"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="66"/>
+      <c r="Y21" s="66"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E22" s="23">
         <v>2035</v>
       </c>
-      <c r="F22" s="23">
-        <v>2035</v>
-      </c>
       <c r="G22" s="27">
         <v>0.3</v>
       </c>
@@ -5422,23 +5315,20 @@
       <c r="K22" s="27"/>
       <c r="L22" s="27"/>
       <c r="O22" s="27"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E23" s="23">
         <v>2040</v>
       </c>
-      <c r="F23" s="23">
-        <v>2040</v>
-      </c>
       <c r="G23" s="27">
         <v>0.3</v>
       </c>
@@ -5451,15 +5341,15 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="O23" s="27"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="str">
@@ -5502,27 +5392,27 @@
       <c r="O24" s="27">
         <v>1</v>
       </c>
-      <c r="Q24" s="65" t="s">
+      <c r="Q24" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="T24" s="65" t="s">
+      <c r="R24" s="66"/>
+      <c r="S24" s="66" t="s">
+        <v>153</v>
+      </c>
+      <c r="T24" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="U24" s="65" t="s">
+      <c r="U24" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V24" s="65" t="s">
+      <c r="V24" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W24" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="65" t="s">
+      <c r="W24" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5530,9 +5420,6 @@
       <c r="E25" s="23">
         <v>2030</v>
       </c>
-      <c r="F25" s="23">
-        <v>2030</v>
-      </c>
       <c r="G25" s="27">
         <v>0.5</v>
       </c>
@@ -5545,23 +5432,20 @@
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
       <c r="O25" s="27"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
+      <c r="W25" s="61"/>
+      <c r="X25" s="66"/>
+      <c r="Y25" s="66"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E26" s="23">
         <v>2035</v>
       </c>
-      <c r="F26" s="23">
-        <v>2035</v>
-      </c>
       <c r="G26" s="27">
         <v>0.51</v>
       </c>
@@ -5574,35 +5458,32 @@
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
       <c r="O26" s="27"/>
-      <c r="Q26" s="65" t="s">
+      <c r="Q26" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="T26" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="U26" s="65" t="s">
+      <c r="R26" s="66"/>
+      <c r="S26" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="T26" s="66" t="s">
+        <v>159</v>
+      </c>
+      <c r="U26" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V26" s="65" t="s">
+      <c r="V26" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
+      <c r="W26" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E27" s="23">
         <v>2040</v>
       </c>
-      <c r="F27" s="23">
-        <v>2040</v>
-      </c>
       <c r="G27" s="27">
         <v>0.52</v>
       </c>
@@ -5615,35 +5496,32 @@
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
       <c r="O27" s="27"/>
-      <c r="Q27" s="65" t="s">
+      <c r="Q27" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R27" s="65"/>
-      <c r="S27" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="T27" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="U27" s="65" t="s">
+      <c r="R27" s="66"/>
+      <c r="S27" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="T27" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="U27" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V27" s="65" t="s">
+      <c r="V27" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W27" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X27" s="65"/>
-      <c r="Y27" s="65"/>
+      <c r="W27" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X27" s="66"/>
+      <c r="Y27" s="66"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="23">
         <v>2045</v>
       </c>
-      <c r="F28" s="23">
-        <v>2045</v>
-      </c>
       <c r="G28" s="27">
         <v>0.55000000000000004</v>
       </c>
@@ -5656,27 +5534,27 @@
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
       <c r="O28" s="27"/>
-      <c r="Q28" s="65" t="s">
+      <c r="Q28" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="T28" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="U28" s="65" t="s">
+      <c r="R28" s="66"/>
+      <c r="S28" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="T28" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="U28" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V28" s="65" t="s">
+      <c r="V28" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W28" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
+      <c r="W28" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
     </row>
     <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
@@ -5684,7 +5562,7 @@
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>49</v>
@@ -5719,35 +5597,32 @@
       <c r="O29" s="27">
         <v>1</v>
       </c>
-      <c r="Q29" s="65" t="s">
+      <c r="Q29" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="T29" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="U29" s="65" t="s">
+      <c r="R29" s="66"/>
+      <c r="S29" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="T29" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="U29" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V29" s="65" t="s">
+      <c r="V29" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W29" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
+      <c r="W29" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X29" s="66"/>
+      <c r="Y29" s="66"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="23">
         <v>2030</v>
       </c>
-      <c r="F30" s="23">
-        <v>2030</v>
-      </c>
       <c r="G30" s="27">
         <v>0.35</v>
       </c>
@@ -5759,23 +5634,20 @@
       </c>
       <c r="L30" s="27"/>
       <c r="O30" s="27"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="66"/>
+      <c r="V30" s="66"/>
+      <c r="W30" s="61"/>
+      <c r="X30" s="66"/>
+      <c r="Y30" s="66"/>
     </row>
     <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="23">
         <v>2035</v>
       </c>
-      <c r="F31" s="23">
-        <v>2035</v>
-      </c>
       <c r="G31" s="27">
         <v>0.35</v>
       </c>
@@ -5787,23 +5659,20 @@
       </c>
       <c r="L31" s="27"/>
       <c r="O31" s="27"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="66"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="66"/>
+      <c r="Y31" s="66"/>
     </row>
     <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="23">
         <v>2040</v>
       </c>
-      <c r="F32" s="23">
-        <v>2040</v>
-      </c>
       <c r="G32" s="27">
         <v>0.35</v>
       </c>
@@ -5815,15 +5684,15 @@
       </c>
       <c r="L32" s="27"/>
       <c r="O32" s="27"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="66"/>
+      <c r="V32" s="66"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="66"/>
+      <c r="Y32" s="66"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="23" t="str">
@@ -5831,7 +5700,7 @@
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>49</v>
@@ -5867,33 +5736,30 @@
         <v>0.35</v>
       </c>
       <c r="Q33" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S33" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="T33" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="U33" s="65" t="s">
+      <c r="T33" s="66" t="s">
+        <v>195</v>
+      </c>
+      <c r="U33" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V33" s="65" t="s">
+      <c r="V33" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W33" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
+      <c r="W33" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="X33" s="66"/>
+      <c r="Y33" s="66"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E34" s="23">
         <v>2025</v>
       </c>
-      <c r="F34" s="23">
-        <v>2025</v>
-      </c>
       <c r="G34" s="27">
         <v>1</v>
       </c>
@@ -5906,20 +5772,17 @@
       <c r="L34" s="27"/>
       <c r="O34" s="27"/>
       <c r="S34" s="23"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
+      <c r="T34" s="66"/>
+      <c r="U34" s="66"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="61"/>
+      <c r="X34" s="66"/>
+      <c r="Y34" s="66"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E35" s="23">
         <v>2030</v>
       </c>
-      <c r="F35" s="23">
-        <v>2030</v>
-      </c>
       <c r="G35" s="27">
         <v>1</v>
       </c>
@@ -5932,20 +5795,17 @@
       <c r="L35" s="27"/>
       <c r="O35" s="27"/>
       <c r="S35" s="23"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
+      <c r="T35" s="66"/>
+      <c r="U35" s="66"/>
+      <c r="V35" s="66"/>
+      <c r="W35" s="61"/>
+      <c r="X35" s="66"/>
+      <c r="Y35" s="66"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E36" s="23">
         <v>2035</v>
       </c>
-      <c r="F36" s="23">
-        <v>2035</v>
-      </c>
       <c r="G36" s="27">
         <v>1</v>
       </c>
@@ -5958,20 +5818,17 @@
       <c r="L36" s="27"/>
       <c r="O36" s="27"/>
       <c r="S36" s="23"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
+      <c r="T36" s="66"/>
+      <c r="U36" s="66"/>
+      <c r="V36" s="66"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="66"/>
+      <c r="Y36" s="66"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E37" s="23">
         <v>2040</v>
       </c>
-      <c r="F37" s="23">
-        <v>2040</v>
-      </c>
       <c r="G37" s="27">
         <v>1</v>
       </c>
@@ -5984,12 +5841,12 @@
       <c r="L37" s="27"/>
       <c r="O37" s="27"/>
       <c r="S37" s="23"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="60"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="66"/>
+      <c r="V37" s="66"/>
+      <c r="W37" s="61"/>
+      <c r="X37" s="66"/>
+      <c r="Y37" s="66"/>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="23" t="str">
@@ -5997,7 +5854,7 @@
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>49</v>
@@ -6030,23 +5887,23 @@
       <c r="O38" s="27">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="65" t="s">
+      <c r="Q38" s="66" t="s">
         <v>81</v>
       </c>
       <c r="S38" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="T38" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="U38" s="65" t="s">
+      <c r="T38" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="U38" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V38" s="65" t="s">
+      <c r="V38" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W38" s="60" t="s">
-        <v>202</v>
+      <c r="W38" s="61" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.2">
@@ -6071,12 +5928,12 @@
         <v>25.364999999999998</v>
       </c>
       <c r="O39" s="27"/>
-      <c r="Q39" s="65"/>
+      <c r="Q39" s="66"/>
       <c r="S39" s="23"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="60"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="66"/>
+      <c r="V39" s="66"/>
+      <c r="W39" s="61"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="F40" s="23">
@@ -6100,12 +5957,12 @@
         <v>24.096749999999997</v>
       </c>
       <c r="O40" s="27"/>
-      <c r="Q40" s="65"/>
+      <c r="Q40" s="66"/>
       <c r="S40" s="23"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="65"/>
-      <c r="W40" s="60"/>
+      <c r="T40" s="66"/>
+      <c r="U40" s="66"/>
+      <c r="V40" s="66"/>
+      <c r="W40" s="61"/>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="F41" s="23">
@@ -6121,12 +5978,12 @@
         <v>0.35</v>
       </c>
       <c r="O41" s="27"/>
-      <c r="Q41" s="65"/>
+      <c r="Q41" s="66"/>
       <c r="S41" s="23"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="65"/>
-      <c r="V41" s="65"/>
-      <c r="W41" s="60"/>
+      <c r="T41" s="66"/>
+      <c r="U41" s="66"/>
+      <c r="V41" s="66"/>
+      <c r="W41" s="61"/>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="23" t="str">
@@ -6134,7 +5991,7 @@
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>49</v>
@@ -6169,32 +6026,29 @@
       <c r="O42" s="27">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="65" t="s">
+      <c r="Q42" s="66" t="s">
         <v>81</v>
       </c>
       <c r="S42" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="T42" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="U42" s="65" t="s">
+      <c r="T42" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="U42" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="V42" s="65" t="s">
+      <c r="V42" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="W42" s="60" t="s">
-        <v>202</v>
+      <c r="W42" s="61" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E43" s="23">
         <v>2025</v>
       </c>
-      <c r="F43" s="23">
-        <v>2025</v>
-      </c>
       <c r="G43" s="27">
         <v>1</v>
       </c>
@@ -6206,20 +6060,17 @@
       </c>
       <c r="L43" s="27"/>
       <c r="O43" s="27"/>
-      <c r="Q43" s="65"/>
+      <c r="Q43" s="66"/>
       <c r="S43" s="23"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="60"/>
+      <c r="T43" s="66"/>
+      <c r="U43" s="66"/>
+      <c r="V43" s="66"/>
+      <c r="W43" s="61"/>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E44" s="23">
         <v>2030</v>
       </c>
-      <c r="F44" s="23">
-        <v>2030</v>
-      </c>
       <c r="G44" s="27">
         <v>1</v>
       </c>
@@ -6231,20 +6082,17 @@
       </c>
       <c r="L44" s="27"/>
       <c r="O44" s="27"/>
-      <c r="Q44" s="65"/>
+      <c r="Q44" s="66"/>
       <c r="S44" s="23"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="60"/>
+      <c r="T44" s="66"/>
+      <c r="U44" s="66"/>
+      <c r="V44" s="66"/>
+      <c r="W44" s="61"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E45" s="23">
         <v>2035</v>
       </c>
-      <c r="F45" s="23">
-        <v>2035</v>
-      </c>
       <c r="G45" s="27">
         <v>1</v>
       </c>
@@ -6256,20 +6104,17 @@
       </c>
       <c r="L45" s="27"/>
       <c r="O45" s="27"/>
-      <c r="Q45" s="65"/>
+      <c r="Q45" s="66"/>
       <c r="S45" s="23"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="60"/>
+      <c r="T45" s="66"/>
+      <c r="U45" s="66"/>
+      <c r="V45" s="66"/>
+      <c r="W45" s="61"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E46" s="23">
         <v>2040</v>
       </c>
-      <c r="F46" s="23">
-        <v>2040</v>
-      </c>
       <c r="G46" s="27">
         <v>1</v>
       </c>
@@ -6281,12 +6126,12 @@
       </c>
       <c r="L46" s="27"/>
       <c r="O46" s="27"/>
-      <c r="Q46" s="65"/>
+      <c r="Q46" s="66"/>
       <c r="S46" s="23"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="60"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="66"/>
+      <c r="V46" s="66"/>
+      <c r="W46" s="61"/>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="23" t="str">
@@ -6294,7 +6139,7 @@
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>49</v>
@@ -6335,9 +6180,6 @@
       <c r="E48" s="23">
         <v>2025</v>
       </c>
-      <c r="F48" s="23">
-        <v>2025</v>
-      </c>
       <c r="G48" s="27">
         <v>1</v>
       </c>
@@ -6354,9 +6196,6 @@
       <c r="E49" s="23">
         <v>2030</v>
       </c>
-      <c r="F49" s="23">
-        <v>2030</v>
-      </c>
       <c r="G49" s="27">
         <v>1</v>
       </c>
@@ -6373,9 +6212,6 @@
       <c r="E50" s="23">
         <v>2035</v>
       </c>
-      <c r="F50" s="23">
-        <v>2035</v>
-      </c>
       <c r="G50" s="27">
         <v>1</v>
       </c>
@@ -6390,9 +6226,6 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E51" s="23">
-        <v>2040</v>
-      </c>
-      <c r="F51" s="23">
         <v>2040</v>
       </c>
       <c r="G51" s="27">
@@ -6413,7 +6246,7 @@
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>49</v>
@@ -6453,9 +6286,6 @@
       <c r="E53" s="23">
         <v>2035</v>
       </c>
-      <c r="F53" s="23">
-        <v>2035</v>
-      </c>
       <c r="G53" s="27">
         <v>1</v>
       </c>
@@ -6471,9 +6301,6 @@
       <c r="E54" s="23">
         <v>2040</v>
       </c>
-      <c r="F54" s="23">
-        <v>2040</v>
-      </c>
       <c r="G54" s="27">
         <v>1</v>
       </c>
@@ -6487,7 +6314,7 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B55" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>49</v>
@@ -6529,9 +6356,6 @@
       <c r="E56" s="23">
         <v>2030</v>
       </c>
-      <c r="F56" s="23">
-        <v>2030</v>
-      </c>
       <c r="G56" s="23">
         <v>0.85</v>
       </c>
@@ -6546,9 +6370,6 @@
       <c r="E57" s="23">
         <v>2035</v>
       </c>
-      <c r="F57" s="23">
-        <v>2035</v>
-      </c>
       <c r="G57" s="23">
         <v>0.85</v>
       </c>
@@ -6563,9 +6384,6 @@
       <c r="E58" s="23">
         <v>2040</v>
       </c>
-      <c r="F58" s="23">
-        <v>2040</v>
-      </c>
       <c r="G58" s="23">
         <v>0.85</v>
       </c>
@@ -6577,6 +6395,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -6665,49 +6484,49 @@
         <v>114</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="59"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="61"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="M5" s="61" t="s">
+      <c r="M5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="62" t="s">
+      <c r="N5" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="61" t="s">
+      <c r="O5" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="61" t="s">
+      <c r="P5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="61" t="s">
+      <c r="Q5" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="61" t="s">
+      <c r="R5" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="S5" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="T5" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="62" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6718,31 +6537,31 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="H6" s="35"/>
-      <c r="M6" s="63" t="s">
+      <c r="M6" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="N6" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="63" t="s">
+      <c r="O6" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="63" t="s">
+      <c r="P6" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="63" t="s">
+      <c r="Q6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="R6" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="S6" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="T6" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="U6" s="64" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6754,7 +6573,7 @@
       <c r="F7" s="32"/>
       <c r="H7" s="32"/>
       <c r="M7" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N7"/>
       <c r="O7" s="2" t="s">
@@ -6765,10 +6584,10 @@
         <v>52</v>
       </c>
       <c r="R7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
@@ -6777,19 +6596,19 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="M8" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N8"/>
       <c r="O8" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -6812,17 +6631,17 @@
       <c r="J10" s="5"/>
       <c r="K10" s="33"/>
       <c r="L10"/>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="59"/>
-      <c r="O10" s="65"/>
-      <c r="P10" s="65"/>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="65"/>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
@@ -6843,8 +6662,8 @@
       <c r="G11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="45" t="s">
-        <v>185</v>
+      <c r="H11" s="46" t="s">
+        <v>186</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>39</v>
@@ -6856,31 +6675,31 @@
         <v>69</v>
       </c>
       <c r="L11"/>
-      <c r="M11" s="61" t="s">
+      <c r="M11" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="62" t="s">
+      <c r="N11" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="61" t="s">
+      <c r="O11" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="61" t="s">
+      <c r="P11" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="Q11" s="61" t="s">
+      <c r="Q11" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="R11" s="61" t="s">
+      <c r="R11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="S11" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="T11" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="U11" s="62" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6911,34 +6730,34 @@
         <v>40</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="63" t="s">
+      <c r="M12" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="63" t="s">
+      <c r="N12" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="63" t="s">
+      <c r="O12" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="63" t="s">
+      <c r="P12" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="63" t="s">
+      <c r="Q12" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="63" t="s">
+      <c r="R12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S12" s="63" t="s">
+      <c r="S12" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="T12" s="63" t="s">
+      <c r="T12" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="U12" s="63" t="s">
+      <c r="U12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6950,31 +6769,31 @@
       <c r="D13" s="11"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76" t="s">
-        <v>132</v>
+      <c r="G13" s="76"/>
+      <c r="H13" s="77" t="s">
+        <v>133</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>79</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="63" t="s">
+      <c r="M13" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="N13" s="63"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -6982,10 +6801,10 @@
         <v>IBOILNCOA</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
-      </c>
-      <c r="D14" s="65" t="s">
         <v>252</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>253</v>
       </c>
       <c r="E14" s="30">
         <v>2022</v>
@@ -6999,7 +6818,7 @@
       <c r="H14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="23">
         <v>975</v>
       </c>
       <c r="J14"/>
@@ -7007,25 +6826,25 @@
         <v>15</v>
       </c>
       <c r="L14"/>
-      <c r="M14" s="60" t="s">
+      <c r="M14" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N14" s="65"/>
-      <c r="O14" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="P14" s="60" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q14" s="65" t="s">
+      <c r="N14" s="66"/>
+      <c r="O14" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="P14" s="61" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q14" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" t="str">
@@ -7033,10 +6852,10 @@
         <v>IBOILNBIO</v>
       </c>
       <c r="C15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="66" t="s">
         <v>253</v>
-      </c>
-      <c r="D15" s="65" t="s">
-        <v>252</v>
       </c>
       <c r="E15" s="30">
         <v>2022</v>
@@ -7050,7 +6869,7 @@
       <c r="H15" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I15" s="83">
+      <c r="I15" s="23">
         <v>750</v>
       </c>
       <c r="J15" s="30"/>
@@ -7058,25 +6877,25 @@
         <v>15</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="60" t="s">
+      <c r="M15" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N15" s="65"/>
-      <c r="O15" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="P15" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q15" s="65" t="s">
+      <c r="N15" s="66"/>
+      <c r="O15" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q15" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R15" s="65" t="s">
+      <c r="R15" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -7084,10 +6903,10 @@
         <v>IBOILNELC</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D16" s="65" t="s">
-        <v>252</v>
+        <v>245</v>
+      </c>
+      <c r="D16" s="66" t="s">
+        <v>253</v>
       </c>
       <c r="E16" s="30">
         <v>2022</v>
@@ -7101,7 +6920,7 @@
       <c r="H16" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I16" s="83">
+      <c r="I16" s="23">
         <v>2078.7684537684499</v>
       </c>
       <c r="J16" s="30"/>
@@ -7109,37 +6928,37 @@
         <v>15</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="60" t="s">
+      <c r="M16" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="65"/>
-      <c r="O16" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="P16" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q16" s="65" t="s">
+      <c r="N16" s="66"/>
+      <c r="O16" s="61" t="s">
+        <v>248</v>
+      </c>
+      <c r="P16" s="61" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q16" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R16" s="65" t="s">
+      <c r="R16" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S16" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
+      <c r="S16" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" t="s">
         <v>262</v>
-      </c>
-      <c r="C17" t="s">
-        <v>260</v>
-      </c>
-      <c r="D17" t="s">
-        <v>261</v>
       </c>
       <c r="E17" s="30">
         <v>2022</v>
@@ -7153,7 +6972,7 @@
       <c r="H17" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="23">
         <v>500</v>
       </c>
       <c r="J17"/>
@@ -7161,25 +6980,25 @@
         <v>10</v>
       </c>
       <c r="L17"/>
-      <c r="M17" s="60" t="s">
+      <c r="M17" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="65"/>
+      <c r="N17" s="66"/>
       <c r="O17" t="s">
-        <v>262</v>
-      </c>
-      <c r="P17" s="60" t="s">
         <v>263</v>
       </c>
-      <c r="Q17" s="65" t="s">
+      <c r="P17" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q17" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="65" t="s">
+      <c r="R17" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -7187,10 +7006,10 @@
         <v>ICOMPNELC</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E18" s="30">
         <v>2022</v>
@@ -7204,7 +7023,7 @@
       <c r="H18" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="83">
+      <c r="I18" s="23">
         <v>1340</v>
       </c>
       <c r="J18"/>
@@ -7212,27 +7031,27 @@
         <v>15.5</v>
       </c>
       <c r="L18"/>
-      <c r="M18" s="60" t="s">
+      <c r="M18" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="65"/>
-      <c r="O18" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="P18" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q18" s="65" t="s">
+      <c r="N18" s="66"/>
+      <c r="O18" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="P18" s="61" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q18" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S18" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
+      <c r="S18" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
@@ -7240,10 +7059,10 @@
         <v>IPUMPNELC</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E19" s="30">
         <v>2022</v>
@@ -7257,7 +7076,7 @@
       <c r="H19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="83">
+      <c r="I19" s="23">
         <v>1700</v>
       </c>
       <c r="J19"/>
@@ -7265,27 +7084,27 @@
         <v>10</v>
       </c>
       <c r="L19"/>
-      <c r="M19" s="60" t="s">
+      <c r="M19" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="65"/>
-      <c r="O19" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="P19" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q19" s="65" t="s">
+      <c r="N19" s="66"/>
+      <c r="O19" s="61" t="s">
+        <v>250</v>
+      </c>
+      <c r="P19" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q19" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="65" t="s">
+      <c r="R19" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
+      <c r="S19" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="T19" s="66"/>
+      <c r="U19" s="66"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -7293,10 +7112,10 @@
         <v>IMOTONELC</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E20" s="30">
         <v>2022</v>
@@ -7310,7 +7129,7 @@
       <c r="H20" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I20" s="83">
+      <c r="I20" s="23">
         <v>120</v>
       </c>
       <c r="J20" s="30"/>
@@ -7321,10 +7140,10 @@
         <v>90</v>
       </c>
       <c r="O20" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q20" t="s">
         <v>52</v>
@@ -7332,19 +7151,19 @@
       <c r="R20" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="65" t="s">
-        <v>202</v>
+      <c r="S20" s="66" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B21" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>265</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>264</v>
       </c>
       <c r="E21" s="30">
         <v>2022</v>
@@ -7358,7 +7177,7 @@
       <c r="H21" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="83">
+      <c r="I21" s="23">
         <v>100</v>
       </c>
       <c r="K21" s="23">
@@ -7368,10 +7187,10 @@
         <v>90</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="s">
         <v>52</v>
@@ -7379,19 +7198,19 @@
       <c r="R21" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="65" t="s">
-        <v>202</v>
+      <c r="S21" s="66" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B22" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E22" s="30">
         <v>2022</v>
@@ -7405,7 +7224,7 @@
       <c r="H22" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="83">
+      <c r="I22" s="23">
         <v>100</v>
       </c>
       <c r="K22" s="23">
@@ -7415,10 +7234,10 @@
         <v>90</v>
       </c>
       <c r="O22" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q22" t="s">
         <v>52</v>
@@ -7431,7 +7250,7 @@
       <c r="P23" s="2"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D27" s="79"/>
+      <c r="D27" s="80"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7440,7 +7259,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -7450,22 +7269,22 @@
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" customWidth="1"/>
     <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
     <col min="20" max="16384" width="8.85546875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="22" t="s">
         <v>43</v>
       </c>
@@ -7483,7 +7302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -7491,80 +7310,80 @@
         <v>52</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="K2" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="K3" s="61" t="s">
+      <c r="L2" s="60"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="K3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="62" t="s">
+      <c r="L3" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="61" t="s">
+      <c r="M3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="61" t="s">
+      <c r="N3" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="61" t="s">
+      <c r="O3" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="61" t="s">
+      <c r="P3" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="R3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="61" t="s">
+      <c r="S3" s="62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="2"/>
-      <c r="K4" s="63" t="s">
+      <c r="K4" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="M4" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="63" t="s">
+      <c r="R4" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="64" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
       <c r="K5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -7574,24 +7393,24 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="F7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L7" s="60"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
@@ -7616,35 +7435,35 @@
       <c r="I8" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="61" t="s">
+      <c r="K8" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="62" t="s">
+      <c r="L8" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="61" t="s">
+      <c r="N8" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="61" t="s">
+      <c r="O8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="61" t="s">
+      <c r="P8" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="61" t="s">
+      <c r="Q8" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="61" t="s">
+      <c r="R8" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="61" t="s">
+      <c r="S8" s="62" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>71</v>
       </c>
@@ -7665,35 +7484,35 @@
       <c r="I9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="63" t="s">
+      <c r="K9" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="63" t="s">
+      <c r="L9" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="63" t="s">
+      <c r="M9" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="N9" s="63" t="s">
+      <c r="N9" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="63" t="s">
+      <c r="O9" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="P9" s="63" t="s">
+      <c r="P9" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="63" t="s">
+      <c r="Q9" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="63" t="s">
+      <c r="R9" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="S9" s="63" t="s">
+      <c r="S9" s="64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>78</v>
       </c>
@@ -7705,322 +7524,100 @@
         <v>52</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>301</v>
+        <v>121</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="63" t="s">
+      <c r="K10" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2022</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="44"/>
-      <c r="H11" s="23">
-        <v>22.5</v>
-      </c>
+      <c r="H11" s="45"/>
       <c r="I11" s="43"/>
       <c r="K11" s="2"/>
       <c r="N11" s="21"/>
-      <c r="U11" s="23">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>288</v>
-      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2022</v>
-      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="44"/>
-      <c r="H12" s="23">
-        <v>23.4</v>
-      </c>
+      <c r="H12" s="45"/>
       <c r="I12" s="43"/>
       <c r="N12" s="21"/>
-      <c r="U12" s="23">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>289</v>
-      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2022</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="44"/>
-      <c r="H13" s="23">
-        <v>15.4</v>
-      </c>
+      <c r="H13" s="45"/>
       <c r="I13" s="43"/>
       <c r="N13" s="21"/>
-      <c r="U13" s="23">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>290</v>
-      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2022</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="23">
-        <v>20.8</v>
-      </c>
+      <c r="H14" s="45"/>
       <c r="I14" s="30"/>
       <c r="N14" s="21"/>
-      <c r="U14" s="23">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>291</v>
-      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2022</v>
-      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="H15" s="23">
-        <v>12.6</v>
-      </c>
+      <c r="H15" s="45"/>
       <c r="I15" s="30"/>
       <c r="N15" s="21"/>
-      <c r="U15" s="23">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>292</v>
-      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" t="s">
-        <v>299</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2022</v>
-      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="23">
-        <v>13.5</v>
-      </c>
       <c r="I16" s="43"/>
-      <c r="U16" s="23">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2022</v>
-      </c>
-      <c r="H17" s="23">
-        <v>14.5</v>
-      </c>
-      <c r="U17" s="23">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="60" t="s">
-        <v>302</v>
-      </c>
-      <c r="D18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2022</v>
-      </c>
-      <c r="H18" s="82">
-        <v>35.75</v>
-      </c>
-      <c r="I18">
-        <v>8.91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19">
-        <v>2026</v>
-      </c>
-      <c r="H19">
-        <v>22.05</v>
-      </c>
-      <c r="I19" s="80">
-        <v>2.6490239999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20">
-        <v>2028</v>
-      </c>
-      <c r="H20">
-        <v>21.39</v>
-      </c>
-      <c r="I20">
-        <v>14.19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21">
-        <v>2029</v>
-      </c>
-      <c r="H21">
-        <v>21.39</v>
-      </c>
-      <c r="I21">
-        <v>14.19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="44"/>
-      <c r="C24" s="2"/>
-      <c r="K24" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B25" s="44"/>
       <c r="C25" s="2"/>
-      <c r="K25" s="80">
-        <v>168</v>
-      </c>
-      <c r="L25" s="80">
-        <f>K25*24*365*0.5</f>
-        <v>735840</v>
-      </c>
-      <c r="M25" s="80">
-        <f>L25*N25</f>
-        <v>2.6490239999999998</v>
-      </c>
-      <c r="N25" s="2">
-        <v>3.5999999999999998E-6</v>
-      </c>
-      <c r="O25">
-        <v>7.9399999999999998E-2</v>
-      </c>
-      <c r="P25" s="81">
-        <f>L25*O25*10^3</f>
-        <v>58425696</v>
-      </c>
-      <c r="Q25" s="80">
-        <f>P25/M25</f>
-        <v>22055555.555555556</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="K26" s="80">
-        <v>900</v>
-      </c>
-      <c r="L26" s="80">
-        <f>K26*24*365*0.5</f>
-        <v>3942000</v>
-      </c>
-      <c r="M26" s="80">
-        <f>L26*N26</f>
-        <v>14.191199999999998</v>
-      </c>
-      <c r="N26" s="2">
-        <v>3.5999999999999998E-6</v>
-      </c>
-      <c r="O26">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="P26" s="81">
-        <f>L26*O26*10^3</f>
-        <v>303534000</v>
-      </c>
-      <c r="Q26" s="80">
-        <f>P26/M26</f>
-        <v>21388888.888888892</v>
-      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C26" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -8084,10 +7681,10 @@
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>88</v>
@@ -8099,7 +7696,7 @@
         <v>114</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>54</v>
@@ -8107,10 +7704,10 @@
     </row>
     <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>88</v>
@@ -8122,22 +7719,22 @@
         <v>53</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="59"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -8156,36 +7753,36 @@
         <v>53</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="61" t="s">
+      <c r="M6" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="61" t="s">
+      <c r="O6" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="61" t="s">
+      <c r="P6" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="61" t="s">
+      <c r="Q6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="61" t="s">
+      <c r="R6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="S6" s="61" t="s">
+      <c r="S6" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="61" t="s">
+      <c r="T6" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="61" t="s">
+      <c r="U6" s="62" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8195,31 +7792,31 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
-      <c r="M7" s="63" t="s">
+      <c r="M7" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="N7" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="63" t="s">
+      <c r="O7" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="63" t="s">
+      <c r="P7" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="63" t="s">
+      <c r="Q7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="63" t="s">
+      <c r="R7" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="S7" s="63" t="s">
+      <c r="S7" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="63" t="s">
+      <c r="T7" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="U7" s="63" t="s">
+      <c r="U7" s="64" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8230,7 +7827,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="M8" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>49</v>
@@ -8240,10 +7837,10 @@
         <v>52</v>
       </c>
       <c r="R8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2" t="s">
@@ -8257,18 +7854,18 @@
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="M9" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -8298,17 +7895,17 @@
       <c r="I13" s="7"/>
       <c r="J13" s="5"/>
       <c r="K13" s="33"/>
-      <c r="M13" s="59" t="s">
+      <c r="M13" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="N13" s="59"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="66"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+      <c r="U13" s="66"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
@@ -8329,8 +7926,8 @@
       <c r="G14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="45" t="s">
-        <v>185</v>
+      <c r="H14" s="46" t="s">
+        <v>186</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>39</v>
@@ -8341,31 +7938,31 @@
       <c r="K14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="61" t="s">
+      <c r="M14" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="62" t="s">
+      <c r="N14" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="61" t="s">
+      <c r="O14" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="P14" s="61" t="s">
+      <c r="P14" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="Q14" s="61" t="s">
+      <c r="Q14" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="61" t="s">
+      <c r="R14" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="S14" s="61" t="s">
+      <c r="S14" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="T14" s="61" t="s">
+      <c r="T14" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="U14" s="61" t="s">
+      <c r="U14" s="62" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8396,33 +7993,33 @@
         <v>40</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="M15" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="M15" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="63" t="s">
+      <c r="N15" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="O15" s="63" t="s">
+      <c r="O15" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="63" t="s">
+      <c r="P15" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="63" t="s">
+      <c r="Q15" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="63" t="s">
+      <c r="R15" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="S15" s="63" t="s">
+      <c r="S15" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="T15" s="63" t="s">
+      <c r="T15" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="U15" s="63" t="s">
+      <c r="U15" s="64" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8435,40 +8032,40 @@
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="46" t="s">
-        <v>132</v>
+      <c r="H16" s="47" t="s">
+        <v>133</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="63" t="s">
+      <c r="M16" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="63"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="63"/>
-      <c r="T16" s="63"/>
-      <c r="U16" s="63"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="str">
+      <c r="B17" t="str">
         <f>O17</f>
         <v>CSCNSOL1</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>238</v>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>239</v>
       </c>
       <c r="E17" s="30">
         <v>2022</v>
@@ -8491,44 +8088,44 @@
       <c r="K17">
         <v>15</v>
       </c>
-      <c r="M17" s="60" t="s">
+      <c r="M17" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65" t="s">
+      <c r="N17" s="66"/>
+      <c r="O17" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="P17" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="P17" s="60" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q17" s="65" t="s">
+      <c r="Q17" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="65" t="s">
+      <c r="R17" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
+      <c r="S17" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="str">
+      <c r="B18" t="str">
         <f t="shared" ref="B18:B27" si="0">O18</f>
         <v>CSCNELC1</v>
       </c>
-      <c r="C18" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="55" t="s">
-        <v>238</v>
+      <c r="C18" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>239</v>
       </c>
       <c r="E18" s="30">
         <v>2022</v>
       </c>
       <c r="F18" s="31">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G18" s="31">
         <v>0.3</v>
@@ -8536,86 +8133,86 @@
       <c r="H18">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="48">
         <v>550</v>
       </c>
-      <c r="J18" s="52">
+      <c r="J18" s="53">
         <v>12</v>
       </c>
       <c r="K18">
         <v>20</v>
       </c>
-      <c r="M18" s="60" t="s">
+      <c r="M18" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="P18" s="60" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q18" s="65" t="s">
+      <c r="N18" s="66"/>
+      <c r="O18" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="P18" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q18" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="S18" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
+      <c r="S18" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="48" t="str">
+      <c r="B19" s="49" t="str">
         <f t="shared" si="0"/>
         <v>CAPNELC1</v>
       </c>
-      <c r="C19" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" s="48" t="s">
+      <c r="C19" s="49" t="s">
         <v>126</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>127</v>
       </c>
       <c r="E19" s="30">
         <v>2022</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="49">
         <v>1.02</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="50">
         <v>0.3</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="49">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="50">
         <v>0.5</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48">
+      <c r="J19" s="49"/>
+      <c r="K19" s="49">
         <v>5</v>
       </c>
-      <c r="M19" s="60" t="s">
+      <c r="M19" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="P19" s="60" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q19" s="65" t="s">
+      <c r="N19" s="66"/>
+      <c r="O19" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="P19" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q19" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="65" t="s">
+      <c r="R19" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="66"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -8623,10 +8220,10 @@
         <v>COTNOIL1</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" s="30">
         <v>2022</v>
@@ -8646,77 +8243,77 @@
       <c r="K20">
         <v>15</v>
       </c>
-      <c r="M20" s="60" t="s">
+      <c r="M20" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N20" s="65"/>
-      <c r="O20" s="65" t="s">
-        <v>129</v>
-      </c>
-      <c r="P20" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q20" s="65" t="s">
+      <c r="N20" s="66"/>
+      <c r="O20" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="P20" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q20" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="65" t="s">
+      <c r="R20" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
     </row>
     <row r="21" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53" t="str">
+      <c r="B21" s="54" t="str">
         <f t="shared" si="0"/>
         <v>COTNELC1</v>
       </c>
-      <c r="C21" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>127</v>
+      <c r="C21" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>128</v>
       </c>
       <c r="E21" s="30">
         <v>2022</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="54">
         <v>1.05</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="55">
         <v>0.3</v>
       </c>
-      <c r="H21" s="53">
+      <c r="H21" s="54">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="55">
         <v>0.75</v>
       </c>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53">
+      <c r="J21" s="54"/>
+      <c r="K21" s="54">
         <v>15</v>
       </c>
-      <c r="M21" s="60" t="s">
+      <c r="M21" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="P21" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q21" s="67" t="s">
+      <c r="N21" s="68"/>
+      <c r="O21" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="P21" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q21" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="67" t="s">
+      <c r="R21" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
+      <c r="S21" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="T21" s="68"/>
+      <c r="U21" s="68"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
@@ -8724,10 +8321,10 @@
         <v>RSCNSOL1</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E22" s="30">
         <v>2022</v>
@@ -8751,36 +8348,36 @@
         <v>15</v>
       </c>
       <c r="L22" s="2"/>
-      <c r="M22" s="60" t="s">
+      <c r="M22" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N22" s="65"/>
-      <c r="O22" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="P22" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q22" s="65" t="s">
+      <c r="N22" s="66"/>
+      <c r="O22" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="P22" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q22" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R22" s="65" t="s">
+      <c r="R22" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>RSCNELC1</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>239</v>
+      <c r="C23" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>240</v>
       </c>
       <c r="E23" s="30">
         <v>2022</v>
@@ -8794,87 +8391,87 @@
       <c r="H23" s="39">
         <v>31.536000000000001</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="48">
         <v>550</v>
       </c>
-      <c r="J23" s="52">
+      <c r="J23" s="53">
         <v>11</v>
       </c>
       <c r="K23">
         <v>20</v>
       </c>
       <c r="L23" s="2"/>
-      <c r="M23" s="60" t="s">
+      <c r="M23" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N23" s="65"/>
-      <c r="O23" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="P23" s="60" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q23" s="65" t="s">
+      <c r="N23" s="66"/>
+      <c r="O23" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="P23" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q23" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R23" s="65" t="s">
+      <c r="R23" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="48" t="str">
+      <c r="B24" s="49" t="str">
         <f t="shared" si="0"/>
         <v>RAPNELC1</v>
       </c>
-      <c r="C24" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="48" t="s">
+      <c r="C24" s="49" t="s">
         <v>140</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>141</v>
       </c>
       <c r="E24" s="30">
         <v>2022</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="49">
         <v>1.02</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="50">
         <v>0.3</v>
       </c>
-      <c r="H24" s="77">
+      <c r="H24" s="78">
         <v>31.536000000000001</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="50">
         <v>0.5</v>
       </c>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48">
+      <c r="J24" s="49"/>
+      <c r="K24" s="49">
         <v>5</v>
       </c>
-      <c r="M24" s="60" t="s">
+      <c r="M24" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="65"/>
-      <c r="O24" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="P24" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q24" s="65" t="s">
+      <c r="N24" s="66"/>
+      <c r="O24" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="P24" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q24" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R24" s="65" t="s">
+      <c r="R24" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S24" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="T24" s="65"/>
-      <c r="U24" s="65"/>
+      <c r="S24" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
@@ -8882,7 +8479,7 @@
         <v>ROTNOIL1</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
@@ -8905,25 +8502,25 @@
       <c r="K25">
         <v>15</v>
       </c>
-      <c r="M25" s="60" t="s">
+      <c r="M25" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N25" s="65"/>
-      <c r="O25" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="P25" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q25" s="65" t="s">
+      <c r="N25" s="66"/>
+      <c r="O25" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="P25" s="61" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q25" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R25" s="65" t="s">
+      <c r="R25" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
@@ -8931,7 +8528,7 @@
         <v>ROTNBIO1</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -8954,87 +8551,87 @@
       <c r="K26">
         <v>15</v>
       </c>
-      <c r="M26" s="60" t="s">
+      <c r="M26" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N26" s="65"/>
-      <c r="O26" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="P26" s="60" t="s">
+      <c r="N26" s="66"/>
+      <c r="O26" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="Q26" s="65" t="s">
+      <c r="P26" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q26" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R26" s="65" t="s">
+      <c r="R26" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
     </row>
     <row r="27" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="str">
+      <c r="B27" s="54" t="str">
         <f t="shared" si="0"/>
         <v>ROTNELC1</v>
       </c>
-      <c r="C27" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="D27" s="53" t="s">
+      <c r="C27" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="54" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="30">
         <v>2022</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="54">
         <v>1.05</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="55">
         <v>0.3</v>
       </c>
-      <c r="H27" s="78">
+      <c r="H27" s="79">
         <v>31.536000000000001</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="55">
         <v>0.75</v>
       </c>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53">
+      <c r="J27" s="54"/>
+      <c r="K27" s="54">
         <v>15</v>
       </c>
-      <c r="M27" s="60" t="s">
+      <c r="M27" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="P27" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q27" s="67" t="s">
+      <c r="N27" s="68"/>
+      <c r="O27" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="P27" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q27" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="R27" s="67" t="s">
+      <c r="R27" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="S27" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
+      <c r="S27" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="T27" s="68"/>
+      <c r="U27" s="68"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
         <v>273</v>
-      </c>
-      <c r="C28" t="s">
-        <v>267</v>
-      </c>
-      <c r="D28" t="s">
-        <v>272</v>
       </c>
       <c r="E28" s="30">
         <v>2022</v>
@@ -9054,31 +8651,31 @@
       <c r="K28">
         <v>20</v>
       </c>
-      <c r="M28" s="60" t="s">
+      <c r="M28" s="61" t="s">
         <v>90</v>
       </c>
       <c r="O28" t="s">
-        <v>273</v>
-      </c>
-      <c r="P28" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="Q28" s="65" t="s">
+      <c r="P28" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q28" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R28" s="65" t="s">
+      <c r="R28" s="66" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E29" s="30">
         <v>2022</v>
@@ -9098,23 +8695,23 @@
       <c r="K29">
         <v>4</v>
       </c>
-      <c r="M29" s="60" t="s">
+      <c r="M29" s="61" t="s">
         <v>90</v>
       </c>
       <c r="O29" t="s">
+        <v>277</v>
+      </c>
+      <c r="P29" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="P29" s="60" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q29" s="65" t="s">
+      <c r="Q29" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R29" s="65" t="s">
+      <c r="R29" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S29" s="60" t="s">
-        <v>202</v>
+      <c r="S29" s="61" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.2">
@@ -9220,7 +8817,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>95</v>
@@ -9229,44 +8826,44 @@
       <c r="I2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="N3" s="61" t="s">
+      <c r="N3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="62" t="s">
+      <c r="O3" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="61" t="s">
+      <c r="P3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="R3" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="61" t="s">
+      <c r="S3" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="61" t="s">
+      <c r="T3" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="61" t="s">
+      <c r="U3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="61" t="s">
+      <c r="V3" s="62" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9276,31 +8873,31 @@
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="63" t="s">
+      <c r="R4" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="63" t="s">
+      <c r="T4" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="U4" s="63" t="s">
+      <c r="U4" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="63" t="s">
+      <c r="V4" s="64" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9311,7 +8908,7 @@
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
       <c r="N5" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>49</v>
@@ -9321,10 +8918,10 @@
         <v>52</v>
       </c>
       <c r="S5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="T5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
@@ -9333,18 +8930,18 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="N6" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -9357,17 +8954,17 @@
       <c r="G8" s="6"/>
       <c r="J8" s="5"/>
       <c r="K8" s="33"/>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="59"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
+      <c r="O8" s="60"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="66"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
@@ -9401,34 +8998,34 @@
         <v>69</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M9" s="25"/>
-      <c r="N9" s="61" t="s">
+      <c r="N9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="62" t="s">
+      <c r="O9" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="61" t="s">
+      <c r="P9" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="61" t="s">
+      <c r="Q9" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="R9" s="61" t="s">
+      <c r="R9" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="S9" s="61" t="s">
+      <c r="S9" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="61" t="s">
+      <c r="T9" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="61" t="s">
+      <c r="U9" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="V9" s="61" t="s">
+      <c r="V9" s="62" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9459,37 +9056,37 @@
         <v>40</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L10" s="17" t="s">
         <v>38</v>
       </c>
       <c r="M10" s="37"/>
-      <c r="N10" s="63" t="s">
+      <c r="N10" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="63" t="s">
+      <c r="O10" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="63" t="s">
+      <c r="P10" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="63" t="s">
+      <c r="Q10" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="R10" s="63" t="s">
+      <c r="R10" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="63" t="s">
+      <c r="S10" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="T10" s="63" t="s">
+      <c r="T10" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="U10" s="63" t="s">
+      <c r="U10" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="V10" s="63" t="s">
+      <c r="V10" s="64" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9501,7 +9098,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>103</v>
@@ -9510,29 +9107,29 @@
         <v>104</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K11" s="19" t="s">
         <v>79</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M11" s="37"/>
-      <c r="N11" s="69" t="s">
+      <c r="N11" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
@@ -9543,7 +9140,7 @@
         <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E12">
         <v>2022</v>
@@ -9572,24 +9169,24 @@
       <c r="N12" t="s">
         <v>90</v>
       </c>
-      <c r="O12" s="65"/>
-      <c r="P12" s="60" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q12" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="R12" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S12" s="65" t="s">
+      <c r="O12" s="66"/>
+      <c r="P12" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q12" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="R12" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S12" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65" t="s">
+      <c r="T12" s="66"/>
+      <c r="U12" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V12" s="65"/>
+      <c r="V12" s="66"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
@@ -9600,7 +9197,7 @@
         <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13">
         <v>2022</v>
@@ -9629,24 +9226,24 @@
       <c r="N13" t="s">
         <v>90</v>
       </c>
-      <c r="O13" s="65"/>
-      <c r="P13" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q13" s="60" t="s">
-        <v>142</v>
-      </c>
-      <c r="R13" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S13" s="65" t="s">
+      <c r="O13" s="66"/>
+      <c r="P13" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q13" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="R13" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S13" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65" t="s">
+      <c r="T13" s="66"/>
+      <c r="U13" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V13" s="65"/>
+      <c r="V13" s="66"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -9657,7 +9254,7 @@
         <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E14">
         <v>2022</v>
@@ -9686,81 +9283,81 @@
       <c r="N14" t="s">
         <v>90</v>
       </c>
-      <c r="O14" s="65"/>
-      <c r="P14" s="60" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q14" s="60" t="s">
-        <v>143</v>
-      </c>
-      <c r="R14" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S14" s="65" t="s">
+      <c r="O14" s="66"/>
+      <c r="P14" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q14" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="R14" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65" t="s">
+      <c r="T14" s="66"/>
+      <c r="U14" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V14" s="65"/>
+      <c r="V14" s="66"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B15" s="47" t="str">
+      <c r="B15" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TCANELC1</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="47">
+      <c r="D15" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="48">
         <v>2026</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="51">
         <v>1.5600711423474201</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="53">
         <v>12</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="51">
         <v>1.25</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="52">
         <v>20</v>
       </c>
-      <c r="J15" s="50">
+      <c r="J15" s="51">
         <v>0.15</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="48">
         <v>20</v>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="57">
         <v>1E-3</v>
       </c>
-      <c r="N15" s="47" t="s">
+      <c r="N15" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q15" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="R15" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="S15" s="71" t="s">
+      <c r="O15" s="72"/>
+      <c r="P15" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q15" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="R15" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71" t="s">
+      <c r="T15" s="72"/>
+      <c r="U15" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="V15" s="71"/>
+      <c r="V15" s="72"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -9771,7 +9368,7 @@
         <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E16">
         <v>2022</v>
@@ -9800,24 +9397,24 @@
       <c r="N16" t="s">
         <v>90</v>
       </c>
-      <c r="O16" s="65"/>
-      <c r="P16" s="60" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q16" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="R16" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S16" s="65" t="s">
+      <c r="O16" s="66"/>
+      <c r="P16" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q16" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="R16" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S16" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65" t="s">
+      <c r="T16" s="66"/>
+      <c r="U16" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V16" s="65"/>
+      <c r="V16" s="66"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
@@ -9828,7 +9425,7 @@
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E17">
         <v>2022</v>
@@ -9857,24 +9454,24 @@
       <c r="N17" t="s">
         <v>90</v>
       </c>
-      <c r="O17" s="65"/>
-      <c r="P17" s="60" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q17" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="R17" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S17" s="65" t="s">
+      <c r="O17" s="66"/>
+      <c r="P17" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q17" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="R17" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S17" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65" t="s">
+      <c r="T17" s="66"/>
+      <c r="U17" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V17" s="65"/>
+      <c r="V17" s="66"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -9885,7 +9482,7 @@
         <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E18">
         <v>2022</v>
@@ -9914,81 +9511,81 @@
       <c r="N18" t="s">
         <v>90</v>
       </c>
-      <c r="O18" s="65"/>
-      <c r="P18" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q18" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="R18" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="S18" s="65" t="s">
+      <c r="O18" s="66"/>
+      <c r="P18" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q18" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="R18" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="S18" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65" t="s">
+      <c r="T18" s="66"/>
+      <c r="U18" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="V18" s="65"/>
+      <c r="V18" s="66"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="47" t="str">
+      <c r="B19" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TPUNELC1</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="47">
+      <c r="D19" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="48">
         <v>2026</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="51">
         <v>3.15E-2</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="48">
         <v>15</v>
       </c>
-      <c r="H19" s="47">
+      <c r="H19" s="48">
         <v>200</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="52">
         <v>40</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="51">
         <v>0.22499999999999998</v>
       </c>
-      <c r="K19" s="47">
+      <c r="K19" s="48">
         <v>30</v>
       </c>
-      <c r="L19" s="47">
+      <c r="L19" s="48">
         <v>1E-3</v>
       </c>
-      <c r="N19" s="47" t="s">
+      <c r="N19" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O19" s="71"/>
-      <c r="P19" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q19" s="72" t="s">
-        <v>148</v>
-      </c>
-      <c r="R19" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="S19" s="71" t="s">
+      <c r="O19" s="72"/>
+      <c r="P19" s="73" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q19" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="R19" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="S19" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71" t="s">
+      <c r="T19" s="72"/>
+      <c r="U19" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="V19" s="71"/>
+      <c r="V19" s="72"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -9999,7 +9596,7 @@
         <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E20">
         <v>2022</v>
@@ -10029,13 +9626,13 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S20" t="s">
         <v>95</v>
@@ -10045,61 +9642,61 @@
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B21" s="47" t="str">
+      <c r="B21" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TMOTNELC1</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="E21" s="47">
+      <c r="D21" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E21" s="48">
         <v>2026</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="48">
         <v>3.2</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="48">
         <v>8</v>
       </c>
-      <c r="H21" s="47">
+      <c r="H21" s="48">
         <v>1.2</v>
       </c>
-      <c r="I21" s="47">
+      <c r="I21" s="48">
         <v>2</v>
       </c>
-      <c r="J21" s="47">
+      <c r="J21" s="48">
         <v>0.02</v>
       </c>
-      <c r="K21" s="47">
+      <c r="K21" s="48">
         <v>10</v>
       </c>
-      <c r="L21" s="56">
+      <c r="L21" s="57">
         <v>1E-3</v>
       </c>
-      <c r="N21" s="47" t="s">
+      <c r="N21" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q21" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="R21" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S21" s="47" t="s">
+      <c r="O21" s="48"/>
+      <c r="P21" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q21" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="R21" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S21" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47" t="s">
+      <c r="T21" s="48"/>
+      <c r="U21" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V21" s="47"/>
+      <c r="V21" s="48"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
@@ -10110,7 +9707,7 @@
         <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E22">
         <v>2022</v>
@@ -10140,13 +9737,13 @@
         <v>90</v>
       </c>
       <c r="P22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S22" t="s">
         <v>95</v>
@@ -10164,7 +9761,7 @@
         <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23">
         <v>2022</v>
@@ -10194,13 +9791,13 @@
         <v>90</v>
       </c>
       <c r="P23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S23" t="s">
         <v>95</v>
@@ -10210,61 +9807,61 @@
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B24" s="47" t="str">
+      <c r="B24" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TTRINELC1</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="47" t="s">
-        <v>207</v>
-      </c>
-      <c r="E24" s="47">
+      <c r="D24" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="48">
         <v>2026</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="48">
         <v>2.1</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="48">
         <v>12</v>
       </c>
-      <c r="H24" s="47">
+      <c r="H24" s="48">
         <v>2</v>
       </c>
-      <c r="I24" s="47">
+      <c r="I24" s="48">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J24" s="47">
+      <c r="J24" s="48">
         <v>0.12</v>
       </c>
-      <c r="K24" s="47">
+      <c r="K24" s="48">
         <v>10</v>
       </c>
-      <c r="L24" s="47">
+      <c r="L24" s="48">
         <v>1E-3</v>
       </c>
-      <c r="N24" s="47" t="s">
+      <c r="N24" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q24" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="R24" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S24" s="47" t="s">
+      <c r="O24" s="48"/>
+      <c r="P24" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q24" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="R24" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S24" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T24" s="47"/>
-      <c r="U24" s="47" t="s">
+      <c r="T24" s="48"/>
+      <c r="U24" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V24" s="47"/>
+      <c r="V24" s="48"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
@@ -10274,8 +9871,8 @@
       <c r="C25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="65" t="s">
-        <v>208</v>
+      <c r="D25" s="66" t="s">
+        <v>209</v>
       </c>
       <c r="E25">
         <v>2022</v>
@@ -10305,13 +9902,13 @@
         <v>90</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S25" t="s">
         <v>95</v>
@@ -10328,8 +9925,8 @@
       <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="65" t="s">
-        <v>208</v>
+      <c r="D26" s="66" t="s">
+        <v>209</v>
       </c>
       <c r="E26">
         <v>2022</v>
@@ -10359,13 +9956,13 @@
         <v>90</v>
       </c>
       <c r="P26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S26" t="s">
         <v>95</v>
@@ -10375,118 +9972,118 @@
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B27" s="47" t="str">
+      <c r="B27" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TFRENELC1</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="47">
+      <c r="D27" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="E27" s="48">
         <v>2026</v>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="48">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="48">
         <v>50</v>
       </c>
-      <c r="H27" s="47">
+      <c r="H27" s="48">
         <v>12</v>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="48">
         <v>145</v>
       </c>
-      <c r="J27" s="47">
+      <c r="J27" s="48">
         <v>0.85</v>
       </c>
-      <c r="K27" s="47">
+      <c r="K27" s="48">
         <v>30</v>
       </c>
-      <c r="L27" s="56">
+      <c r="L27" s="57">
         <v>1E-3</v>
       </c>
-      <c r="N27" s="47" t="s">
+      <c r="N27" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q27" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="R27" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S27" s="47" t="s">
+      <c r="O27" s="48"/>
+      <c r="P27" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q27" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S27" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47" t="s">
+      <c r="T27" s="48"/>
+      <c r="U27" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V27" s="47"/>
+      <c r="V27" s="48"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" s="47" t="str">
+      <c r="B28" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TAVINKER1</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="65" t="s">
-        <v>209</v>
-      </c>
-      <c r="E28" s="47">
+      <c r="E28" s="48">
         <v>2022</v>
       </c>
-      <c r="F28" s="47">
+      <c r="F28" s="48">
         <v>0.1</v>
       </c>
-      <c r="G28" s="47">
+      <c r="G28" s="48">
         <v>65</v>
       </c>
-      <c r="H28" s="47">
+      <c r="H28" s="48">
         <v>180</v>
       </c>
-      <c r="I28" s="47">
+      <c r="I28" s="48">
         <v>50000</v>
       </c>
-      <c r="J28" s="47">
+      <c r="J28" s="48">
         <v>70</v>
       </c>
-      <c r="K28" s="47">
+      <c r="K28" s="48">
         <v>30</v>
       </c>
-      <c r="L28" s="47">
+      <c r="L28" s="48">
         <v>1E-3</v>
       </c>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O28" s="47"/>
-      <c r="P28" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q28" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="R28" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S28" s="47" t="s">
+      <c r="O28" s="48"/>
+      <c r="P28" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q28" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="R28" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S28" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T28" s="47"/>
-      <c r="U28" s="47" t="s">
+      <c r="T28" s="48"/>
+      <c r="U28" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V28" s="47"/>
+      <c r="V28" s="48"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B29" t="str">
@@ -10496,8 +10093,8 @@
       <c r="C29" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="73" t="s">
-        <v>211</v>
+      <c r="D29" s="74" t="s">
+        <v>212</v>
       </c>
       <c r="E29">
         <v>2022</v>
@@ -10527,13 +10124,13 @@
         <v>90</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S29" t="s">
         <v>95</v>
@@ -10543,61 +10140,61 @@
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" s="47" t="str">
+      <c r="B30" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TRAINELC1</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="74" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="47">
+      <c r="D30" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="48">
         <v>2040</v>
       </c>
-      <c r="F30" s="47">
+      <c r="F30" s="48">
         <v>0.78</v>
       </c>
-      <c r="G30" s="47">
+      <c r="G30" s="48">
         <v>66</v>
       </c>
-      <c r="H30" s="47">
+      <c r="H30" s="48">
         <v>500</v>
       </c>
-      <c r="I30" s="47">
+      <c r="I30" s="48">
         <v>3100</v>
       </c>
-      <c r="J30" s="47">
+      <c r="J30" s="48">
         <v>22</v>
       </c>
-      <c r="K30" s="47">
+      <c r="K30" s="48">
         <v>30</v>
       </c>
-      <c r="L30" s="56">
+      <c r="L30" s="57">
         <v>1E-3</v>
       </c>
-      <c r="N30" s="47" t="s">
+      <c r="N30" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q30" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="R30" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S30" s="47" t="s">
+      <c r="O30" s="48"/>
+      <c r="P30" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q30" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="R30" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S30" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47" t="s">
+      <c r="T30" s="48"/>
+      <c r="U30" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V30" s="47"/>
+      <c r="V30" s="48"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B31" t="str">
@@ -10607,8 +10204,8 @@
       <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="65" t="s">
-        <v>212</v>
+      <c r="D31" s="66" t="s">
+        <v>213</v>
       </c>
       <c r="E31">
         <v>2022</v>
@@ -10638,13 +10235,13 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q31" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S31" t="s">
         <v>95</v>
@@ -10661,8 +10258,8 @@
       <c r="C32" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="65" t="s">
-        <v>212</v>
+      <c r="D32" s="66" t="s">
+        <v>213</v>
       </c>
       <c r="E32">
         <v>2022</v>
@@ -10692,13 +10289,13 @@
         <v>90</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S32" t="s">
         <v>95</v>
@@ -10708,61 +10305,61 @@
       </c>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B33" s="47" t="str">
+      <c r="B33" s="48" t="str">
         <f t="shared" si="0"/>
         <v>TMARNELC1</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="71" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="47">
+      <c r="D33" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="48">
         <v>2026</v>
       </c>
-      <c r="F33" s="47">
+      <c r="F33" s="48">
         <v>0.85</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="48">
         <v>50</v>
       </c>
-      <c r="H33" s="47">
+      <c r="H33" s="48">
         <v>400</v>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="48">
         <v>9500</v>
       </c>
-      <c r="J33" s="47">
+      <c r="J33" s="48">
         <v>70</v>
       </c>
-      <c r="K33" s="47">
+      <c r="K33" s="48">
         <v>30</v>
       </c>
-      <c r="L33" s="47">
+      <c r="L33" s="48">
         <v>1E-3</v>
       </c>
-      <c r="N33" s="47" t="s">
+      <c r="N33" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q33" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="R33" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="S33" s="47" t="s">
+      <c r="O33" s="48"/>
+      <c r="P33" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q33" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="R33" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="S33" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="T33" s="47"/>
-      <c r="U33" s="47" t="s">
+      <c r="T33" s="48"/>
+      <c r="U33" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="V33" s="47"/>
+      <c r="V33" s="48"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10779,25 +10376,25 @@
   <dimension ref="B2:AC2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.140625" style="57"/>
-    <col min="13" max="13" width="5" style="57" customWidth="1"/>
-    <col min="14" max="15" width="2" style="57" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.140625" style="57"/>
-    <col min="27" max="27" width="2" style="57" customWidth="1"/>
-    <col min="28" max="28" width="2.28515625" style="57" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="57"/>
+    <col min="1" max="1" width="2" style="58" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="9.140625" style="58"/>
+    <col min="13" max="13" width="5" style="58" customWidth="1"/>
+    <col min="14" max="15" width="2" style="58" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="9.140625" style="58"/>
+    <col min="27" max="27" width="2" style="58" customWidth="1"/>
+    <col min="28" max="28" width="2.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="58"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
-        <v>166</v>
-      </c>
-      <c r="P2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="AC2" s="58" t="s">
+      <c r="P2" s="59" t="s">
         <v>168</v>
+      </c>
+      <c r="AC2" s="59" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020-v02\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FDCC61-7013-4F4A-8D97-C42DB7BA04AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74263D0B-0812-41BB-B0E8-1570B8177DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ELC" sheetId="4" r:id="rId1"/>
+    <sheet name="ELC" sheetId="12" r:id="rId1"/>
     <sheet name="IND" sheetId="8" r:id="rId2"/>
     <sheet name="PRI" sheetId="7" r:id="rId3"/>
     <sheet name="RCA" sheetId="6" r:id="rId4"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2088,9 +2088,6 @@
     <t>Annual Production Bound</t>
   </si>
   <si>
-    <t>M€2005/PJ</t>
-  </si>
-  <si>
     <t>AGR</t>
   </si>
   <si>
@@ -2586,13 +2583,88 @@
     <t>ELE, STG</t>
   </si>
   <si>
+    <t>TRAINHFO1</t>
+  </si>
+  <si>
+    <t>IMPDSL1</t>
+  </si>
+  <si>
+    <t>IMPKER1</t>
+  </si>
+  <si>
+    <t>IMPLPG1</t>
+  </si>
+  <si>
+    <t>IMPGSL1</t>
+  </si>
+  <si>
+    <t>IMPNAP1</t>
+  </si>
+  <si>
+    <t>IMPHFO1</t>
+  </si>
+  <si>
+    <t>IMPOPP1</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>NAP</t>
+  </si>
+  <si>
+    <t>HFO</t>
+  </si>
+  <si>
+    <t>OPP</t>
+  </si>
+  <si>
+    <t>M$2021/PJ</t>
+  </si>
+  <si>
+    <t>IMPELCVN1</t>
+  </si>
+  <si>
+    <t>IMPELCLAO1</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>IMPELCLAO2</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>cost/PJ</t>
+  </si>
+  <si>
+    <t>IMPELCLAO3</t>
+  </si>
+  <si>
     <t>PDP Installed Capacity</t>
   </si>
   <si>
     <t>NCAP_BND</t>
-  </si>
-  <si>
-    <t>TRAINHFO1</t>
   </si>
 </sst>
 </file>
@@ -2606,7 +2678,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2808,8 +2880,13 @@
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2864,6 +2941,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF1FB"/>
         <bgColor rgb="FFEAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3007,7 +3090,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="59">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3075,8 +3158,9 @@
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3170,7 +3254,6 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3232,12 +3315,17 @@
     <xf numFmtId="49" fontId="31" fillId="10" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="59" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="59">
+  <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="calculated" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Calculation 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Comma" xfId="59" builtinId="3"/>
     <cellStyle name="Comma 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma 11" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Comma 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -3324,10 +3412,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+        <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE448FC7-5FA6-4416-A543-F7B93A5592EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD073F9E-25D4-4666-9943-1639B4B3BF3B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3335,8 +3423,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1311274" y="5296958"/>
-          <a:ext cx="7356475" cy="1423458"/>
+          <a:off x="1314449" y="10741025"/>
+          <a:ext cx="8231717" cy="1452033"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4595,8 +4683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A4B651-1072-492F-9C98-6FB421C5AC2C}">
   <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4683,49 +4770,49 @@
         <v>53</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="60" t="s">
+      <c r="Q4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="60"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="61"/>
-      <c r="Y4" s="61"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q5" s="62" t="s">
+      <c r="Q5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="63" t="s">
+      <c r="R5" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="62" t="s">
+      <c r="S5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="62" t="s">
+      <c r="T5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="62" t="s">
+      <c r="U5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="62" t="s">
+      <c r="V5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="62" t="s">
+      <c r="W5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="62" t="s">
+      <c r="X5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="62" t="s">
+      <c r="Y5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4746,35 +4833,35 @@
         <v>60</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="35"/>
-      <c r="Q6" s="64" t="s">
+      <c r="Q6" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="R6" s="64" t="s">
+      <c r="R6" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="S6" s="64" t="s">
+      <c r="S6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="64" t="s">
+      <c r="T6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="64" t="s">
+      <c r="U6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="64" t="s">
+      <c r="V6" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="64" t="s">
+      <c r="W6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="64" t="s">
+      <c r="X6" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" s="64" t="s">
+      <c r="Y6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4795,7 +4882,7 @@
         <v>54</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="32"/>
@@ -4823,17 +4910,17 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="5"/>
-      <c r="Q10" s="60" t="s">
+      <c r="Q10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="60"/>
-      <c r="S10" s="61"/>
-      <c r="T10" s="61"/>
-      <c r="U10" s="61"/>
-      <c r="V10" s="61"/>
-      <c r="W10" s="61"/>
-      <c r="X10" s="61"/>
-      <c r="Y10" s="61"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
@@ -4855,7 +4942,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -4873,37 +4960,37 @@
         <v>69</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O11" s="15" t="s">
         <v>70</v>
       </c>
       <c r="P11" s="25"/>
-      <c r="Q11" s="62" t="s">
+      <c r="Q11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="63" t="s">
+      <c r="R11" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="S11" s="62" t="s">
+      <c r="S11" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="T11" s="62" t="s">
+      <c r="T11" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="U11" s="62" t="s">
+      <c r="U11" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="V11" s="62" t="s">
+      <c r="V11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="W11" s="62" t="s">
+      <c r="W11" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="X11" s="62" t="s">
+      <c r="X11" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="Y11" s="62" t="s">
+      <c r="Y11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4923,7 +5010,7 @@
         <v>37</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>72</v>
@@ -4938,7 +5025,7 @@
         <v>41</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>38</v>
@@ -4946,31 +5033,31 @@
       <c r="O12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="Q12" s="65" t="s">
+      <c r="Q12" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="65" t="s">
+      <c r="R12" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="S12" s="65" t="s">
+      <c r="S12" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="T12" s="65" t="s">
+      <c r="T12" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="65" t="s">
+      <c r="U12" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="65" t="s">
+      <c r="V12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="65" t="s">
+      <c r="W12" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="X12" s="65" t="s">
+      <c r="X12" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="Y12" s="65" t="s">
+      <c r="Y12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4986,13 +5073,13 @@
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="L13" s="19" t="s">
         <v>201</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>202</v>
       </c>
       <c r="M13" s="19" t="s">
         <v>79</v>
@@ -5001,17 +5088,17 @@
         <v>80</v>
       </c>
       <c r="O13" s="19"/>
-      <c r="Q13" s="64" t="s">
+      <c r="Q13" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="R13" s="64"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="64"/>
-      <c r="V13" s="64"/>
-      <c r="W13" s="64"/>
-      <c r="X13" s="64"/>
-      <c r="Y13" s="64"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="63"/>
+      <c r="Y13" s="63"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
@@ -5054,27 +5141,27 @@
       <c r="O14" s="27">
         <v>1</v>
       </c>
-      <c r="Q14" s="66" t="s">
+      <c r="Q14" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="T14" s="66" t="s">
+      <c r="R14" s="65"/>
+      <c r="S14" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="T14" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="U14" s="66" t="s">
+      <c r="U14" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V14" s="66" t="s">
+      <c r="V14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W14" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="66"/>
+      <c r="W14" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E15" s="23">
@@ -5093,15 +5180,15 @@
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
       <c r="O15" s="27"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="61"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="60"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E16" s="23">
@@ -5120,15 +5207,15 @@
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
       <c r="O16" s="27"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-      <c r="V16" s="66"/>
-      <c r="W16" s="61"/>
-      <c r="X16" s="66"/>
-      <c r="Y16" s="66"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
@@ -5147,15 +5234,15 @@
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
       <c r="O17" s="27"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
-      <c r="V17" s="66"/>
-      <c r="W17" s="61"/>
-      <c r="X17" s="66"/>
-      <c r="Y17" s="66"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
@@ -5174,15 +5261,15 @@
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
       <c r="O18" s="27"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="66"/>
-      <c r="U18" s="66"/>
-      <c r="V18" s="66"/>
-      <c r="W18" s="61"/>
-      <c r="X18" s="66"/>
-      <c r="Y18" s="66"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="str">
@@ -5225,27 +5312,27 @@
       <c r="O19" s="27">
         <v>1</v>
       </c>
-      <c r="Q19" s="66" t="s">
+      <c r="Q19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="T19" s="66" t="s">
+      <c r="R19" s="65"/>
+      <c r="S19" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="T19" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="66" t="s">
+      <c r="U19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V19" s="66" t="s">
+      <c r="V19" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X19" s="66"/>
-      <c r="Y19" s="66"/>
+      <c r="W19" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E20" s="23">
@@ -5263,15 +5350,15 @@
       <c r="K20" s="27"/>
       <c r="L20" s="27"/>
       <c r="O20" s="27"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="66"/>
-      <c r="V20" s="66"/>
-      <c r="W20" s="61"/>
-      <c r="X20" s="66"/>
-      <c r="Y20" s="66"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="65"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="65"/>
+      <c r="Y20" s="65"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E21" s="23">
@@ -5289,15 +5376,15 @@
       <c r="K21" s="27"/>
       <c r="L21" s="27"/>
       <c r="O21" s="27"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="66"/>
-      <c r="V21" s="66"/>
-      <c r="W21" s="61"/>
-      <c r="X21" s="66"/>
-      <c r="Y21" s="66"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="65"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E22" s="23">
@@ -5315,15 +5402,15 @@
       <c r="K22" s="27"/>
       <c r="L22" s="27"/>
       <c r="O22" s="27"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="61"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E23" s="23">
@@ -5341,15 +5428,15 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="O23" s="27"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="str">
@@ -5392,27 +5479,27 @@
       <c r="O24" s="27">
         <v>1</v>
       </c>
-      <c r="Q24" s="66" t="s">
+      <c r="Q24" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66" t="s">
-        <v>153</v>
-      </c>
-      <c r="T24" s="66" t="s">
+      <c r="R24" s="65"/>
+      <c r="S24" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="T24" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="U24" s="66" t="s">
+      <c r="U24" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V24" s="66" t="s">
+      <c r="V24" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W24" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66" t="s">
+      <c r="W24" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5432,15 +5519,15 @@
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
       <c r="O25" s="27"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="61"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="66"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E26" s="23">
@@ -5458,27 +5545,27 @@
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
       <c r="O26" s="27"/>
-      <c r="Q26" s="66" t="s">
+      <c r="Q26" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="T26" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="U26" s="66" t="s">
+      <c r="R26" s="65"/>
+      <c r="S26" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="T26" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="U26" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V26" s="66" t="s">
+      <c r="V26" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
+      <c r="W26" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E27" s="23">
@@ -5496,27 +5583,27 @@
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
       <c r="O27" s="27"/>
-      <c r="Q27" s="66" t="s">
+      <c r="Q27" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66" t="s">
-        <v>156</v>
-      </c>
-      <c r="T27" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="U27" s="66" t="s">
+      <c r="R27" s="65"/>
+      <c r="S27" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="T27" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="U27" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V27" s="66" t="s">
+      <c r="V27" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W27" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
+      <c r="W27" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="23">
@@ -5534,27 +5621,27 @@
       <c r="K28" s="27"/>
       <c r="L28" s="27"/>
       <c r="O28" s="27"/>
-      <c r="Q28" s="66" t="s">
+      <c r="Q28" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="T28" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="U28" s="66" t="s">
+      <c r="R28" s="65"/>
+      <c r="S28" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="T28" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="U28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V28" s="66" t="s">
+      <c r="V28" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W28" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
+      <c r="W28" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
     </row>
     <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
@@ -5562,7 +5649,7 @@
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>49</v>
@@ -5597,27 +5684,27 @@
       <c r="O29" s="27">
         <v>1</v>
       </c>
-      <c r="Q29" s="66" t="s">
+      <c r="Q29" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66" t="s">
-        <v>158</v>
-      </c>
-      <c r="T29" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="U29" s="66" t="s">
+      <c r="R29" s="65"/>
+      <c r="S29" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="T29" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="U29" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V29" s="66" t="s">
+      <c r="V29" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W29" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="66"/>
+      <c r="W29" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="65"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="23">
@@ -5634,15 +5721,15 @@
       </c>
       <c r="L30" s="27"/>
       <c r="O30" s="27"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="66"/>
-      <c r="V30" s="66"/>
-      <c r="W30" s="61"/>
-      <c r="X30" s="66"/>
-      <c r="Y30" s="66"/>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="65"/>
+      <c r="U30" s="65"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="65"/>
     </row>
     <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="23">
@@ -5659,15 +5746,15 @@
       </c>
       <c r="L31" s="27"/>
       <c r="O31" s="27"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="66"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="66"/>
-      <c r="Y31" s="66"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="65"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
     </row>
     <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="23">
@@ -5684,15 +5771,15 @@
       </c>
       <c r="L32" s="27"/>
       <c r="O32" s="27"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="61"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="66"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="65"/>
+      <c r="T32" s="65"/>
+      <c r="U32" s="65"/>
+      <c r="V32" s="65"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="65"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="23" t="str">
@@ -5700,7 +5787,7 @@
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>49</v>
@@ -5736,25 +5823,25 @@
         <v>0.35</v>
       </c>
       <c r="Q33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S33" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="T33" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="T33" s="66" t="s">
-        <v>195</v>
-      </c>
-      <c r="U33" s="66" t="s">
+      <c r="U33" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V33" s="66" t="s">
+      <c r="V33" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W33" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
+      <c r="W33" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="65"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E34" s="23">
@@ -5772,12 +5859,12 @@
       <c r="L34" s="27"/>
       <c r="O34" s="27"/>
       <c r="S34" s="23"/>
-      <c r="T34" s="66"/>
-      <c r="U34" s="66"/>
-      <c r="V34" s="66"/>
-      <c r="W34" s="61"/>
-      <c r="X34" s="66"/>
-      <c r="Y34" s="66"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="60"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E35" s="23">
@@ -5795,12 +5882,12 @@
       <c r="L35" s="27"/>
       <c r="O35" s="27"/>
       <c r="S35" s="23"/>
-      <c r="T35" s="66"/>
-      <c r="U35" s="66"/>
-      <c r="V35" s="66"/>
-      <c r="W35" s="61"/>
-      <c r="X35" s="66"/>
-      <c r="Y35" s="66"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E36" s="23">
@@ -5818,12 +5905,12 @@
       <c r="L36" s="27"/>
       <c r="O36" s="27"/>
       <c r="S36" s="23"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="66"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="61"/>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E37" s="23">
@@ -5841,12 +5928,12 @@
       <c r="L37" s="27"/>
       <c r="O37" s="27"/>
       <c r="S37" s="23"/>
-      <c r="T37" s="66"/>
-      <c r="U37" s="66"/>
-      <c r="V37" s="66"/>
-      <c r="W37" s="61"/>
-      <c r="X37" s="66"/>
-      <c r="Y37" s="66"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="60"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="23" t="str">
@@ -5854,7 +5941,7 @@
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>49</v>
@@ -5887,23 +5974,23 @@
       <c r="O38" s="27">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="66" t="s">
+      <c r="Q38" s="65" t="s">
         <v>81</v>
       </c>
       <c r="S38" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="T38" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="T38" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="U38" s="66" t="s">
+      <c r="U38" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V38" s="66" t="s">
+      <c r="V38" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W38" s="61" t="s">
-        <v>203</v>
+      <c r="W38" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.2">
@@ -5928,12 +6015,12 @@
         <v>25.364999999999998</v>
       </c>
       <c r="O39" s="27"/>
-      <c r="Q39" s="66"/>
+      <c r="Q39" s="65"/>
       <c r="S39" s="23"/>
-      <c r="T39" s="66"/>
-      <c r="U39" s="66"/>
-      <c r="V39" s="66"/>
-      <c r="W39" s="61"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="60"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="F40" s="23">
@@ -5957,12 +6044,12 @@
         <v>24.096749999999997</v>
       </c>
       <c r="O40" s="27"/>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="65"/>
       <c r="S40" s="23"/>
-      <c r="T40" s="66"/>
-      <c r="U40" s="66"/>
-      <c r="V40" s="66"/>
-      <c r="W40" s="61"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="65"/>
+      <c r="W40" s="60"/>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="F41" s="23">
@@ -5978,12 +6065,12 @@
         <v>0.35</v>
       </c>
       <c r="O41" s="27"/>
-      <c r="Q41" s="66"/>
+      <c r="Q41" s="65"/>
       <c r="S41" s="23"/>
-      <c r="T41" s="66"/>
-      <c r="U41" s="66"/>
-      <c r="V41" s="66"/>
-      <c r="W41" s="61"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="60"/>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="23" t="str">
@@ -5991,7 +6078,7 @@
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>49</v>
@@ -6026,23 +6113,23 @@
       <c r="O42" s="27">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="66" t="s">
+      <c r="Q42" s="65" t="s">
         <v>81</v>
       </c>
       <c r="S42" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="T42" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="T42" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="U42" s="66" t="s">
+      <c r="U42" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V42" s="66" t="s">
+      <c r="V42" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W42" s="61" t="s">
-        <v>203</v>
+      <c r="W42" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.2">
@@ -6060,12 +6147,12 @@
       </c>
       <c r="L43" s="27"/>
       <c r="O43" s="27"/>
-      <c r="Q43" s="66"/>
+      <c r="Q43" s="65"/>
       <c r="S43" s="23"/>
-      <c r="T43" s="66"/>
-      <c r="U43" s="66"/>
-      <c r="V43" s="66"/>
-      <c r="W43" s="61"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="60"/>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E44" s="23">
@@ -6082,12 +6169,12 @@
       </c>
       <c r="L44" s="27"/>
       <c r="O44" s="27"/>
-      <c r="Q44" s="66"/>
+      <c r="Q44" s="65"/>
       <c r="S44" s="23"/>
-      <c r="T44" s="66"/>
-      <c r="U44" s="66"/>
-      <c r="V44" s="66"/>
-      <c r="W44" s="61"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="60"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E45" s="23">
@@ -6104,12 +6191,12 @@
       </c>
       <c r="L45" s="27"/>
       <c r="O45" s="27"/>
-      <c r="Q45" s="66"/>
+      <c r="Q45" s="65"/>
       <c r="S45" s="23"/>
-      <c r="T45" s="66"/>
-      <c r="U45" s="66"/>
-      <c r="V45" s="66"/>
-      <c r="W45" s="61"/>
+      <c r="T45" s="65"/>
+      <c r="U45" s="65"/>
+      <c r="V45" s="65"/>
+      <c r="W45" s="60"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E46" s="23">
@@ -6126,12 +6213,12 @@
       </c>
       <c r="L46" s="27"/>
       <c r="O46" s="27"/>
-      <c r="Q46" s="66"/>
+      <c r="Q46" s="65"/>
       <c r="S46" s="23"/>
-      <c r="T46" s="66"/>
-      <c r="U46" s="66"/>
-      <c r="V46" s="66"/>
-      <c r="W46" s="61"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="65"/>
+      <c r="V46" s="65"/>
+      <c r="W46" s="60"/>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="23" t="str">
@@ -6139,7 +6226,7 @@
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>49</v>
@@ -6246,7 +6333,7 @@
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>49</v>
@@ -6314,7 +6401,7 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B55" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>49</v>
@@ -6395,7 +6482,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -6484,49 +6570,49 @@
         <v>114</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="60" t="s">
+      <c r="M4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="60"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="M5" s="62" t="s">
+      <c r="M5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="62" t="s">
+      <c r="O5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="62" t="s">
+      <c r="P5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="62" t="s">
+      <c r="Q5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="62" t="s">
+      <c r="R5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="62" t="s">
+      <c r="S5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="T5" s="62" t="s">
+      <c r="T5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="62" t="s">
+      <c r="U5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6537,31 +6623,31 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="H6" s="35"/>
-      <c r="M6" s="64" t="s">
+      <c r="M6" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="64" t="s">
+      <c r="N6" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="64" t="s">
+      <c r="O6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="64" t="s">
+      <c r="Q6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="64" t="s">
+      <c r="R6" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="S6" s="64" t="s">
+      <c r="S6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="64" t="s">
+      <c r="T6" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="U6" s="64" t="s">
+      <c r="U6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6573,7 +6659,7 @@
       <c r="F7" s="32"/>
       <c r="H7" s="32"/>
       <c r="M7" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N7"/>
       <c r="O7" s="2" t="s">
@@ -6584,10 +6670,10 @@
         <v>52</v>
       </c>
       <c r="R7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
@@ -6596,19 +6682,19 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="M8" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N8"/>
       <c r="O8" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -6631,17 +6717,17 @@
       <c r="J10" s="5"/>
       <c r="K10" s="33"/>
       <c r="L10"/>
-      <c r="M10" s="60" t="s">
+      <c r="M10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="60"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-      <c r="T10" s="66"/>
-      <c r="U10" s="66"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
@@ -6662,8 +6748,8 @@
       <c r="G11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="46" t="s">
-        <v>186</v>
+      <c r="H11" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>39</v>
@@ -6675,31 +6761,31 @@
         <v>69</v>
       </c>
       <c r="L11"/>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="63" t="s">
+      <c r="N11" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="62" t="s">
+      <c r="O11" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="62" t="s">
+      <c r="P11" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="Q11" s="62" t="s">
+      <c r="Q11" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="R11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="S11" s="62" t="s">
+      <c r="S11" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="T11" s="62" t="s">
+      <c r="T11" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="U11" s="62" t="s">
+      <c r="U11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6730,34 +6816,34 @@
         <v>40</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="64" t="s">
+      <c r="M12" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="64" t="s">
+      <c r="N12" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="64" t="s">
+      <c r="O12" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="64" t="s">
+      <c r="P12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="Q12" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="R12" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="S12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="T12" s="64" t="s">
+      <c r="T12" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="U12" s="64" t="s">
+      <c r="U12" s="63" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6769,31 +6855,31 @@
       <c r="D13" s="11"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="77" t="s">
-        <v>133</v>
+      <c r="G13" s="75"/>
+      <c r="H13" s="76" t="s">
+        <v>132</v>
       </c>
       <c r="I13" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>232</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>233</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>79</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="64" t="s">
+      <c r="M13" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="64"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -6801,10 +6887,10 @@
         <v>IBOILNCOA</v>
       </c>
       <c r="C14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D14" s="65" t="s">
         <v>252</v>
-      </c>
-      <c r="D14" s="66" t="s">
-        <v>253</v>
       </c>
       <c r="E14" s="30">
         <v>2022</v>
@@ -6818,7 +6904,7 @@
       <c r="H14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="83">
         <v>975</v>
       </c>
       <c r="J14"/>
@@ -6826,25 +6912,25 @@
         <v>15</v>
       </c>
       <c r="L14"/>
-      <c r="M14" s="61" t="s">
+      <c r="M14" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="61" t="s">
-        <v>246</v>
-      </c>
-      <c r="P14" s="61" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q14" s="66" t="s">
+      <c r="N14" s="65"/>
+      <c r="O14" s="60" t="s">
+        <v>245</v>
+      </c>
+      <c r="P14" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q14" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R14" s="66" t="s">
+      <c r="R14" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" t="str">
@@ -6852,10 +6938,10 @@
         <v>IBOILNBIO</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D15" s="66" t="s">
         <v>253</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>252</v>
       </c>
       <c r="E15" s="30">
         <v>2022</v>
@@ -6869,7 +6955,7 @@
       <c r="H15" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="83">
         <v>750</v>
       </c>
       <c r="J15" s="30"/>
@@ -6877,25 +6963,25 @@
         <v>15</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="61" t="s">
+      <c r="M15" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="P15" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q15" s="66" t="s">
+      <c r="N15" s="65"/>
+      <c r="O15" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="P15" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q15" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R15" s="66" t="s">
+      <c r="R15" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -6903,10 +6989,10 @@
         <v>IBOILNELC</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" s="66" t="s">
-        <v>253</v>
+        <v>244</v>
+      </c>
+      <c r="D16" s="65" t="s">
+        <v>252</v>
       </c>
       <c r="E16" s="30">
         <v>2022</v>
@@ -6920,7 +7006,7 @@
       <c r="H16" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="83">
         <v>2078.7684537684499</v>
       </c>
       <c r="J16" s="30"/>
@@ -6928,37 +7014,37 @@
         <v>15</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="61" t="s">
+      <c r="M16" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="66"/>
-      <c r="O16" s="61" t="s">
-        <v>248</v>
-      </c>
-      <c r="P16" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q16" s="66" t="s">
+      <c r="N16" s="65"/>
+      <c r="O16" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="P16" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q16" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R16" s="66" t="s">
+      <c r="R16" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S16" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
+      <c r="S16" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C17" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" t="s">
         <v>261</v>
-      </c>
-      <c r="D17" t="s">
-        <v>262</v>
       </c>
       <c r="E17" s="30">
         <v>2022</v>
@@ -6972,7 +7058,7 @@
       <c r="H17" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="83">
         <v>500</v>
       </c>
       <c r="J17"/>
@@ -6980,25 +7066,25 @@
         <v>10</v>
       </c>
       <c r="L17"/>
-      <c r="M17" s="61" t="s">
+      <c r="M17" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="66"/>
+      <c r="N17" s="65"/>
       <c r="O17" t="s">
+        <v>262</v>
+      </c>
+      <c r="P17" s="60" t="s">
         <v>263</v>
       </c>
-      <c r="P17" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q17" s="66" t="s">
+      <c r="Q17" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="66" t="s">
+      <c r="R17" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -7006,10 +7092,10 @@
         <v>ICOMPNELC</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E18" s="30">
         <v>2022</v>
@@ -7023,7 +7109,7 @@
       <c r="H18" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="83">
         <v>1340</v>
       </c>
       <c r="J18"/>
@@ -7031,27 +7117,27 @@
         <v>15.5</v>
       </c>
       <c r="L18"/>
-      <c r="M18" s="61" t="s">
+      <c r="M18" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="66"/>
-      <c r="O18" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="P18" s="61" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q18" s="66" t="s">
+      <c r="N18" s="65"/>
+      <c r="O18" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="P18" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q18" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="66" t="s">
+      <c r="R18" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S18" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="T18" s="66"/>
-      <c r="U18" s="66"/>
+      <c r="S18" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
@@ -7059,10 +7145,10 @@
         <v>IPUMPNELC</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E19" s="30">
         <v>2022</v>
@@ -7076,7 +7162,7 @@
       <c r="H19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="83">
         <v>1700</v>
       </c>
       <c r="J19"/>
@@ -7084,27 +7170,27 @@
         <v>10</v>
       </c>
       <c r="L19"/>
-      <c r="M19" s="61" t="s">
+      <c r="M19" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="66"/>
-      <c r="O19" s="61" t="s">
-        <v>250</v>
-      </c>
-      <c r="P19" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q19" s="66" t="s">
+      <c r="N19" s="65"/>
+      <c r="O19" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="P19" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="66" t="s">
+      <c r="R19" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="T19" s="66"/>
-      <c r="U19" s="66"/>
+      <c r="S19" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -7112,10 +7198,10 @@
         <v>IMOTONELC</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E20" s="30">
         <v>2022</v>
@@ -7129,7 +7215,7 @@
       <c r="H20" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="83">
         <v>120</v>
       </c>
       <c r="J20" s="30"/>
@@ -7140,10 +7226,10 @@
         <v>90</v>
       </c>
       <c r="O20" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q20" t="s">
         <v>52</v>
@@ -7151,19 +7237,19 @@
       <c r="R20" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="66" t="s">
-        <v>203</v>
+      <c r="S20" s="65" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B21" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E21" s="30">
         <v>2022</v>
@@ -7177,7 +7263,7 @@
       <c r="H21" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="83">
         <v>100</v>
       </c>
       <c r="K21" s="23">
@@ -7187,10 +7273,10 @@
         <v>90</v>
       </c>
       <c r="O21" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="P21" t="s">
         <v>266</v>
-      </c>
-      <c r="P21" t="s">
-        <v>267</v>
       </c>
       <c r="Q21" t="s">
         <v>52</v>
@@ -7198,19 +7284,19 @@
       <c r="R21" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="66" t="s">
-        <v>203</v>
+      <c r="S21" s="65" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B22" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E22" s="30">
         <v>2022</v>
@@ -7224,7 +7310,7 @@
       <c r="H22" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="83">
         <v>100</v>
       </c>
       <c r="K22" s="23">
@@ -7234,10 +7320,10 @@
         <v>90</v>
       </c>
       <c r="O22" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="Q22" t="s">
         <v>52</v>
@@ -7250,7 +7336,7 @@
       <c r="P23" s="2"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D27" s="80"/>
+      <c r="D27" s="79"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7259,7 +7345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -7269,22 +7355,22 @@
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
     <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
     <col min="18" max="18" width="15.140625" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
     <col min="20" max="16384" width="8.85546875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="22" t="s">
         <v>43</v>
       </c>
@@ -7302,7 +7388,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -7310,80 +7396,80 @@
         <v>52</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K2" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="K2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="60"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-    </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="K3" s="62" t="s">
+      <c r="L2" s="59"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="K3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="63" t="s">
+      <c r="L3" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="62" t="s">
+      <c r="M3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="62" t="s">
+      <c r="N3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="62" t="s">
+      <c r="O3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="62" t="s">
+      <c r="Q3" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="62" t="s">
+      <c r="R3" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="62" t="s">
+      <c r="S3" s="61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="2"/>
-      <c r="K4" s="64" t="s">
+      <c r="K4" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="64" t="s">
+      <c r="L4" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="M4" s="64" t="s">
+      <c r="M4" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="64" t="s">
+      <c r="O4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="Q4" s="64" t="s">
+      <c r="Q4" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="64" t="s">
+      <c r="R4" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="64" t="s">
+      <c r="S4" s="63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="K5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -7393,24 +7479,24 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="L7" s="59"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
@@ -7435,35 +7521,35 @@
       <c r="I8" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="62" t="s">
+      <c r="K8" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="62" t="s">
+      <c r="N8" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="62" t="s">
+      <c r="O8" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="62" t="s">
+      <c r="P8" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="62" t="s">
+      <c r="Q8" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="62" t="s">
+      <c r="R8" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="62" t="s">
+      <c r="S8" s="61" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>71</v>
       </c>
@@ -7484,35 +7570,35 @@
       <c r="I9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="64" t="s">
+      <c r="K9" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="64" t="s">
+      <c r="L9" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="64" t="s">
+      <c r="M9" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="N9" s="64" t="s">
+      <c r="N9" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="64" t="s">
+      <c r="O9" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="P9" s="64" t="s">
+      <c r="P9" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="64" t="s">
+      <c r="Q9" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="64" t="s">
+      <c r="R9" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="S9" s="64" t="s">
+      <c r="S9" s="63" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>78</v>
       </c>
@@ -7524,100 +7610,322 @@
         <v>52</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>121</v>
+        <v>301</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="64" t="s">
+      <c r="K10" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
-      <c r="P10" s="67"/>
-      <c r="Q10" s="67"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="67"/>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2022</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="44"/>
-      <c r="H11" s="45"/>
+      <c r="H11" s="23">
+        <v>22.5</v>
+      </c>
       <c r="I11" s="43"/>
       <c r="K11" s="2"/>
       <c r="N11" s="21"/>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B12" s="2"/>
+      <c r="U11" s="23">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2022</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="44"/>
-      <c r="H12" s="45"/>
+      <c r="H12" s="23">
+        <v>23.4</v>
+      </c>
       <c r="I12" s="43"/>
       <c r="N12" s="21"/>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B13" s="2"/>
+      <c r="U12" s="23">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2022</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="H13" s="23">
+        <v>15.4</v>
+      </c>
       <c r="I13" s="43"/>
       <c r="N13" s="21"/>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B14" s="2"/>
+      <c r="U13" s="23">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2022</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="45"/>
+      <c r="H14" s="23">
+        <v>20.8</v>
+      </c>
       <c r="I14" s="30"/>
       <c r="N14" s="21"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B15" s="2"/>
+      <c r="U14" s="23">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2022</v>
+      </c>
       <c r="F15" s="2"/>
-      <c r="H15" s="45"/>
+      <c r="H15" s="23">
+        <v>12.6</v>
+      </c>
       <c r="I15" s="30"/>
       <c r="N15" s="21"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B16" s="2"/>
+      <c r="U15" s="23">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>292</v>
+      </c>
       <c r="C16" s="2"/>
+      <c r="D16" t="s">
+        <v>299</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2022</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="23">
+        <v>13.5</v>
+      </c>
       <c r="I16" s="43"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="44"/>
+      <c r="U16" s="23">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2022</v>
+      </c>
+      <c r="H17" s="23">
+        <v>14.5</v>
+      </c>
+      <c r="U17" s="23">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="60" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2022</v>
+      </c>
+      <c r="H18" s="82">
+        <v>35.75</v>
+      </c>
+      <c r="I18">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>2026</v>
+      </c>
+      <c r="H19">
+        <v>22.05</v>
+      </c>
+      <c r="I19" s="80">
+        <v>2.6490239999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20">
+        <v>2028</v>
+      </c>
+      <c r="H20">
+        <v>21.39</v>
+      </c>
+      <c r="I20">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21">
+        <v>2029</v>
+      </c>
+      <c r="H21">
+        <v>21.39</v>
+      </c>
+      <c r="I21">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B24" s="44"/>
+      <c r="C24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C26" s="2"/>
+      <c r="K25" s="80">
+        <v>168</v>
+      </c>
+      <c r="L25" s="80">
+        <f>K25*24*365*0.5</f>
+        <v>735840</v>
+      </c>
+      <c r="M25" s="80">
+        <f>L25*N25</f>
+        <v>2.6490239999999998</v>
+      </c>
+      <c r="N25" s="2">
+        <v>3.5999999999999998E-6</v>
+      </c>
+      <c r="O25">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="P25" s="81">
+        <f>L25*O25*10^3</f>
+        <v>58425696</v>
+      </c>
+      <c r="Q25" s="80">
+        <f>P25/M25</f>
+        <v>22055555.555555556</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="K26" s="80">
+        <v>900</v>
+      </c>
+      <c r="L26" s="80">
+        <f>K26*24*365*0.5</f>
+        <v>3942000</v>
+      </c>
+      <c r="M26" s="80">
+        <f>L26*N26</f>
+        <v>14.191199999999998</v>
+      </c>
+      <c r="N26" s="2">
+        <v>3.5999999999999998E-6</v>
+      </c>
+      <c r="O26">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="P26" s="81">
+        <f>L26*O26*10^3</f>
+        <v>303534000</v>
+      </c>
+      <c r="Q26" s="80">
+        <f>P26/M26</f>
+        <v>21388888.888888892</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -7681,10 +7989,10 @@
     </row>
     <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>88</v>
@@ -7696,7 +8004,7 @@
         <v>114</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>54</v>
@@ -7704,10 +8012,10 @@
     </row>
     <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>88</v>
@@ -7719,22 +8027,22 @@
         <v>53</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="60" t="s">
+      <c r="M5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="60"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="60"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -7753,36 +8061,36 @@
         <v>53</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="N6" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="62" t="s">
+      <c r="O6" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="62" t="s">
+      <c r="P6" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="62" t="s">
+      <c r="Q6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="62" t="s">
+      <c r="R6" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="S6" s="62" t="s">
+      <c r="S6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="62" t="s">
+      <c r="T6" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="62" t="s">
+      <c r="U6" s="61" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7792,31 +8100,31 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
-      <c r="M7" s="64" t="s">
+      <c r="M7" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="64" t="s">
+      <c r="N7" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="64" t="s">
+      <c r="O7" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="64" t="s">
+      <c r="Q7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="64" t="s">
+      <c r="R7" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="S7" s="64" t="s">
+      <c r="S7" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="64" t="s">
+      <c r="T7" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="U7" s="64" t="s">
+      <c r="U7" s="63" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7827,7 +8135,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="M8" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>49</v>
@@ -7837,10 +8145,10 @@
         <v>52</v>
       </c>
       <c r="R8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2" t="s">
@@ -7854,18 +8162,18 @@
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="M9" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -7895,17 +8203,17 @@
       <c r="I13" s="7"/>
       <c r="J13" s="5"/>
       <c r="K13" s="33"/>
-      <c r="M13" s="60" t="s">
+      <c r="M13" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="N13" s="60"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
@@ -7926,8 +8234,8 @@
       <c r="G14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="46" t="s">
-        <v>186</v>
+      <c r="H14" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>39</v>
@@ -7938,31 +8246,31 @@
       <c r="K14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="62" t="s">
+      <c r="M14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="63" t="s">
+      <c r="N14" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="62" t="s">
+      <c r="O14" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="P14" s="62" t="s">
+      <c r="P14" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="Q14" s="62" t="s">
+      <c r="Q14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="62" t="s">
+      <c r="R14" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="S14" s="62" t="s">
+      <c r="S14" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="T14" s="62" t="s">
+      <c r="T14" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="U14" s="62" t="s">
+      <c r="U14" s="61" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7993,33 +8301,33 @@
         <v>40</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="M15" s="64" t="s">
+        <v>186</v>
+      </c>
+      <c r="M15" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="64" t="s">
+      <c r="N15" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="O15" s="64" t="s">
+      <c r="O15" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="64" t="s">
+      <c r="P15" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="64" t="s">
+      <c r="Q15" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="64" t="s">
+      <c r="R15" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="S15" s="64" t="s">
+      <c r="S15" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="T15" s="64" t="s">
+      <c r="T15" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="U15" s="64" t="s">
+      <c r="U15" s="63" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8032,40 +8340,40 @@
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="47" t="s">
-        <v>133</v>
+      <c r="H16" s="46" t="s">
+        <v>132</v>
       </c>
       <c r="I16" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>232</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>233</v>
       </c>
       <c r="K16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="64" t="s">
+      <c r="M16" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="64"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="64"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="64"/>
-      <c r="U16" s="64"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="63"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="63"/>
+      <c r="R16" s="63"/>
+      <c r="S16" s="63"/>
+      <c r="T16" s="63"/>
+      <c r="U16" s="63"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" t="str">
+      <c r="B17" s="2" t="str">
         <f>O17</f>
         <v>CSCNSOL1</v>
       </c>
-      <c r="C17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" t="s">
-        <v>239</v>
+      <c r="C17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="E17" s="30">
         <v>2022</v>
@@ -8088,44 +8396,44 @@
       <c r="K17">
         <v>15</v>
       </c>
-      <c r="M17" s="61" t="s">
+      <c r="M17" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="P17" s="61" t="s">
+      <c r="N17" s="65"/>
+      <c r="O17" s="65" t="s">
         <v>236</v>
       </c>
-      <c r="Q17" s="66" t="s">
+      <c r="P17" s="60" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q17" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="66" t="s">
+      <c r="R17" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
+      <c r="S17" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" t="str">
+      <c r="B18" s="2" t="str">
         <f t="shared" ref="B18:B27" si="0">O18</f>
         <v>CSCNELC1</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>239</v>
+      <c r="C18" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>238</v>
       </c>
       <c r="E18" s="30">
         <v>2022</v>
       </c>
       <c r="F18" s="31">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G18" s="31">
         <v>0.3</v>
@@ -8133,86 +8441,86 @@
       <c r="H18">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="47">
         <v>550</v>
       </c>
-      <c r="J18" s="53">
+      <c r="J18" s="52">
         <v>12</v>
       </c>
       <c r="K18">
         <v>20</v>
       </c>
-      <c r="M18" s="61" t="s">
+      <c r="M18" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="P18" s="61" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q18" s="66" t="s">
+      <c r="N18" s="65"/>
+      <c r="O18" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="P18" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q18" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="66" t="s">
+      <c r="R18" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="S18" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="T18" s="66"/>
-      <c r="U18" s="66"/>
+      <c r="S18" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="49" t="str">
+      <c r="B19" s="48" t="str">
         <f t="shared" si="0"/>
         <v>CAPNELC1</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="48" t="s">
         <v>126</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>127</v>
       </c>
       <c r="E19" s="30">
         <v>2022</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="48">
         <v>1.02</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="49">
         <v>0.3</v>
       </c>
-      <c r="H19" s="49">
+      <c r="H19" s="48">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="50">
+      <c r="I19" s="49">
         <v>0.5</v>
       </c>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49">
+      <c r="J19" s="48"/>
+      <c r="K19" s="48">
         <v>5</v>
       </c>
-      <c r="M19" s="61" t="s">
+      <c r="M19" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="P19" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q19" s="66" t="s">
+      <c r="N19" s="65"/>
+      <c r="O19" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="66" t="s">
+      <c r="R19" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="66"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -8220,10 +8528,10 @@
         <v>COTNOIL1</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" s="30">
         <v>2022</v>
@@ -8243,77 +8551,77 @@
       <c r="K20">
         <v>15</v>
       </c>
-      <c r="M20" s="61" t="s">
+      <c r="M20" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="P20" s="61" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q20" s="66" t="s">
+      <c r="N20" s="65"/>
+      <c r="O20" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="P20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q20" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="66" t="s">
+      <c r="R20" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="66"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="65"/>
     </row>
     <row r="21" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="54" t="str">
+      <c r="B21" s="53" t="str">
         <f t="shared" si="0"/>
         <v>COTNELC1</v>
       </c>
-      <c r="C21" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>128</v>
+      <c r="C21" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>127</v>
       </c>
       <c r="E21" s="30">
         <v>2022</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="53">
         <v>1.05</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="54">
         <v>0.3</v>
       </c>
-      <c r="H21" s="54">
+      <c r="H21" s="53">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="54">
         <v>0.75</v>
       </c>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54">
+      <c r="J21" s="53"/>
+      <c r="K21" s="53">
         <v>15</v>
       </c>
-      <c r="M21" s="61" t="s">
+      <c r="M21" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="P21" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q21" s="68" t="s">
+      <c r="N21" s="67"/>
+      <c r="O21" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="P21" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q21" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="68" t="s">
+      <c r="R21" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
+      <c r="S21" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
@@ -8321,10 +8629,10 @@
         <v>RSCNSOL1</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E22" s="30">
         <v>2022</v>
@@ -8348,36 +8656,36 @@
         <v>15</v>
       </c>
       <c r="L22" s="2"/>
-      <c r="M22" s="61" t="s">
+      <c r="M22" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N22" s="66"/>
-      <c r="O22" s="61" t="s">
-        <v>241</v>
-      </c>
-      <c r="P22" s="61" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q22" s="66" t="s">
+      <c r="N22" s="65"/>
+      <c r="O22" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="P22" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q22" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R22" s="66" t="s">
+      <c r="R22" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>RSCNELC1</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>240</v>
+      <c r="C23" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>239</v>
       </c>
       <c r="E23" s="30">
         <v>2022</v>
@@ -8391,87 +8699,87 @@
       <c r="H23" s="39">
         <v>31.536000000000001</v>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="47">
         <v>550</v>
       </c>
-      <c r="J23" s="53">
+      <c r="J23" s="52">
         <v>11</v>
       </c>
       <c r="K23">
         <v>20</v>
       </c>
       <c r="L23" s="2"/>
-      <c r="M23" s="61" t="s">
+      <c r="M23" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N23" s="66"/>
-      <c r="O23" s="61" t="s">
-        <v>242</v>
-      </c>
-      <c r="P23" s="61" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q23" s="66" t="s">
+      <c r="N23" s="65"/>
+      <c r="O23" s="60" t="s">
+        <v>241</v>
+      </c>
+      <c r="P23" s="60" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q23" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R23" s="66" t="s">
+      <c r="R23" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="49" t="str">
+      <c r="B24" s="48" t="str">
         <f t="shared" si="0"/>
         <v>RAPNELC1</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="48" t="s">
         <v>140</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>141</v>
       </c>
       <c r="E24" s="30">
         <v>2022</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="48">
         <v>1.02</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="49">
         <v>0.3</v>
       </c>
-      <c r="H24" s="78">
+      <c r="H24" s="77">
         <v>31.536000000000001</v>
       </c>
-      <c r="I24" s="50">
+      <c r="I24" s="49">
         <v>0.5</v>
       </c>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49">
+      <c r="J24" s="48"/>
+      <c r="K24" s="48">
         <v>5</v>
       </c>
-      <c r="M24" s="61" t="s">
+      <c r="M24" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="66"/>
-      <c r="O24" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="P24" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q24" s="66" t="s">
+      <c r="N24" s="65"/>
+      <c r="O24" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="P24" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q24" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R24" s="66" t="s">
+      <c r="R24" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S24" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
+      <c r="S24" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
@@ -8479,7 +8787,7 @@
         <v>ROTNOIL1</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
@@ -8502,25 +8810,25 @@
       <c r="K25">
         <v>15</v>
       </c>
-      <c r="M25" s="61" t="s">
+      <c r="M25" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N25" s="66"/>
-      <c r="O25" s="61" t="s">
-        <v>172</v>
-      </c>
-      <c r="P25" s="61" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q25" s="66" t="s">
+      <c r="N25" s="65"/>
+      <c r="O25" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="P25" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q25" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R25" s="66" t="s">
+      <c r="R25" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
@@ -8528,7 +8836,7 @@
         <v>ROTNBIO1</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -8551,87 +8859,87 @@
       <c r="K26">
         <v>15</v>
       </c>
-      <c r="M26" s="61" t="s">
+      <c r="M26" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N26" s="66"/>
-      <c r="O26" s="61" t="s">
+      <c r="N26" s="65"/>
+      <c r="O26" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="P26" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="P26" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q26" s="66" t="s">
+      <c r="Q26" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R26" s="66" t="s">
+      <c r="R26" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="65"/>
     </row>
     <row r="27" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="54" t="str">
+      <c r="B27" s="53" t="str">
         <f t="shared" si="0"/>
         <v>ROTNELC1</v>
       </c>
-      <c r="C27" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" s="54" t="s">
+      <c r="C27" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="53" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="30">
         <v>2022</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="53">
         <v>1.05</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="54">
         <v>0.3</v>
       </c>
-      <c r="H27" s="79">
+      <c r="H27" s="78">
         <v>31.536000000000001</v>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="54">
         <v>0.75</v>
       </c>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54">
+      <c r="J27" s="53"/>
+      <c r="K27" s="53">
         <v>15</v>
       </c>
-      <c r="M27" s="61" t="s">
+      <c r="M27" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="N27" s="68"/>
-      <c r="O27" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="P27" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q27" s="68" t="s">
+      <c r="N27" s="67"/>
+      <c r="O27" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="P27" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q27" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="R27" s="68" t="s">
+      <c r="R27" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="S27" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="T27" s="68"/>
-      <c r="U27" s="68"/>
+      <c r="S27" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E28" s="30">
         <v>2022</v>
@@ -8651,31 +8959,31 @@
       <c r="K28">
         <v>20</v>
       </c>
-      <c r="M28" s="61" t="s">
+      <c r="M28" s="60" t="s">
         <v>90</v>
       </c>
       <c r="O28" t="s">
+        <v>273</v>
+      </c>
+      <c r="P28" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="P28" s="61" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q28" s="66" t="s">
+      <c r="Q28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R28" s="66" t="s">
+      <c r="R28" s="65" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E29" s="30">
         <v>2022</v>
@@ -8695,23 +9003,23 @@
       <c r="K29">
         <v>4</v>
       </c>
-      <c r="M29" s="61" t="s">
+      <c r="M29" s="60" t="s">
         <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>277</v>
-      </c>
-      <c r="P29" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Q29" s="66" t="s">
+      <c r="P29" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q29" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="R29" s="66" t="s">
+      <c r="R29" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="S29" s="61" t="s">
-        <v>203</v>
+      <c r="S29" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.2">
@@ -8817,7 +9125,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>95</v>
@@ -8826,44 +9134,44 @@
       <c r="I2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="N3" s="62" t="s">
+      <c r="N3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="63" t="s">
+      <c r="O3" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="62" t="s">
+      <c r="Q3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="62" t="s">
+      <c r="R3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="62" t="s">
+      <c r="S3" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="62" t="s">
+      <c r="T3" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="61" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8873,31 +9181,31 @@
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="O4" s="64" t="s">
+      <c r="O4" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="Q4" s="64" t="s">
+      <c r="Q4" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="64" t="s">
+      <c r="R4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="64" t="s">
+      <c r="S4" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="64" t="s">
+      <c r="T4" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="U4" s="64" t="s">
+      <c r="U4" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="64" t="s">
+      <c r="V4" s="63" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8908,7 +9216,7 @@
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
       <c r="N5" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>49</v>
@@ -8918,10 +9226,10 @@
         <v>52</v>
       </c>
       <c r="S5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
@@ -8930,18 +9238,18 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="N6" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
@@ -8954,17 +9262,17 @@
       <c r="G8" s="6"/>
       <c r="J8" s="5"/>
       <c r="K8" s="33"/>
-      <c r="N8" s="60" t="s">
+      <c r="N8" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="60"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="66"/>
-      <c r="U8" s="66"/>
-      <c r="V8" s="66"/>
+      <c r="O8" s="59"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
@@ -8998,34 +9306,34 @@
         <v>69</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M9" s="25"/>
-      <c r="N9" s="62" t="s">
+      <c r="N9" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="63" t="s">
+      <c r="O9" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="62" t="s">
+      <c r="P9" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="62" t="s">
+      <c r="Q9" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="R9" s="62" t="s">
+      <c r="R9" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="S9" s="62" t="s">
+      <c r="S9" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="62" t="s">
+      <c r="T9" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="62" t="s">
+      <c r="U9" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="V9" s="62" t="s">
+      <c r="V9" s="61" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9056,37 +9364,37 @@
         <v>40</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L10" s="17" t="s">
         <v>38</v>
       </c>
       <c r="M10" s="37"/>
-      <c r="N10" s="64" t="s">
+      <c r="N10" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="64" t="s">
+      <c r="O10" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="64" t="s">
+      <c r="P10" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="64" t="s">
+      <c r="Q10" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="R10" s="64" t="s">
+      <c r="R10" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="64" t="s">
+      <c r="S10" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="T10" s="64" t="s">
+      <c r="T10" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="U10" s="64" t="s">
+      <c r="U10" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="V10" s="64" t="s">
+      <c r="V10" s="63" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9098,7 +9406,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>103</v>
@@ -9107,29 +9415,29 @@
         <v>104</v>
       </c>
       <c r="I11" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>204</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>205</v>
       </c>
       <c r="K11" s="19" t="s">
         <v>79</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M11" s="37"/>
-      <c r="N11" s="70" t="s">
+      <c r="N11" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
@@ -9140,7 +9448,7 @@
         <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E12">
         <v>2022</v>
@@ -9169,24 +9477,24 @@
       <c r="N12" t="s">
         <v>90</v>
       </c>
-      <c r="O12" s="66"/>
-      <c r="P12" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q12" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="R12" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S12" s="66" t="s">
+      <c r="O12" s="65"/>
+      <c r="P12" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q12" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="R12" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S12" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66" t="s">
+      <c r="T12" s="65"/>
+      <c r="U12" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V12" s="66"/>
+      <c r="V12" s="65"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
@@ -9197,7 +9505,7 @@
         <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E13">
         <v>2022</v>
@@ -9226,24 +9534,24 @@
       <c r="N13" t="s">
         <v>90</v>
       </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q13" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="R13" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S13" s="66" t="s">
+      <c r="O13" s="65"/>
+      <c r="P13" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q13" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="R13" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S13" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66" t="s">
+      <c r="T13" s="65"/>
+      <c r="U13" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V13" s="66"/>
+      <c r="V13" s="65"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -9254,7 +9562,7 @@
         <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14">
         <v>2022</v>
@@ -9283,81 +9591,81 @@
       <c r="N14" t="s">
         <v>90</v>
       </c>
-      <c r="O14" s="66"/>
-      <c r="P14" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q14" s="61" t="s">
-        <v>144</v>
-      </c>
-      <c r="R14" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S14" s="66" t="s">
+      <c r="O14" s="65"/>
+      <c r="P14" s="60" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q14" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="R14" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S14" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66" t="s">
+      <c r="T14" s="65"/>
+      <c r="U14" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V14" s="66"/>
+      <c r="V14" s="65"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B15" s="48" t="str">
+      <c r="B15" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TCANELC1</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="48">
+      <c r="D15" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="47">
         <v>2026</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="50">
         <v>1.5600711423474201</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="52">
         <v>12</v>
       </c>
-      <c r="H15" s="51">
+      <c r="H15" s="50">
         <v>1.25</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="51">
         <v>20</v>
       </c>
-      <c r="J15" s="51">
+      <c r="J15" s="50">
         <v>0.15</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="47">
         <v>20</v>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="56">
         <v>1E-3</v>
       </c>
-      <c r="N15" s="48" t="s">
+      <c r="N15" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q15" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="R15" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="S15" s="72" t="s">
+      <c r="O15" s="71"/>
+      <c r="P15" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q15" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="R15" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="S15" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="T15" s="72"/>
-      <c r="U15" s="72" t="s">
+      <c r="T15" s="71"/>
+      <c r="U15" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="V15" s="72"/>
+      <c r="V15" s="71"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -9368,7 +9676,7 @@
         <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E16">
         <v>2022</v>
@@ -9397,24 +9705,24 @@
       <c r="N16" t="s">
         <v>90</v>
       </c>
-      <c r="O16" s="66"/>
-      <c r="P16" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q16" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="R16" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S16" s="66" t="s">
+      <c r="O16" s="65"/>
+      <c r="P16" s="60" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q16" s="60" t="s">
+        <v>145</v>
+      </c>
+      <c r="R16" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S16" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66" t="s">
+      <c r="T16" s="65"/>
+      <c r="U16" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V16" s="66"/>
+      <c r="V16" s="65"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
@@ -9425,7 +9733,7 @@
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17">
         <v>2022</v>
@@ -9454,24 +9762,24 @@
       <c r="N17" t="s">
         <v>90</v>
       </c>
-      <c r="O17" s="66"/>
-      <c r="P17" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q17" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="R17" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S17" s="66" t="s">
+      <c r="O17" s="65"/>
+      <c r="P17" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q17" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S17" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66" t="s">
+      <c r="T17" s="65"/>
+      <c r="U17" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V17" s="66"/>
+      <c r="V17" s="65"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -9482,7 +9790,7 @@
         <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E18">
         <v>2022</v>
@@ -9511,81 +9819,81 @@
       <c r="N18" t="s">
         <v>90</v>
       </c>
-      <c r="O18" s="66"/>
-      <c r="P18" s="61" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q18" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="R18" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="S18" s="66" t="s">
+      <c r="O18" s="65"/>
+      <c r="P18" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="R18" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="S18" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="T18" s="66"/>
-      <c r="U18" s="66" t="s">
+      <c r="T18" s="65"/>
+      <c r="U18" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="V18" s="66"/>
+      <c r="V18" s="65"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="48" t="str">
+      <c r="B19" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TPUNELC1</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="48">
+      <c r="D19" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="47">
         <v>2026</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="50">
         <v>3.15E-2</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="47">
         <v>15</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="47">
         <v>200</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="51">
         <v>40</v>
       </c>
-      <c r="J19" s="51">
+      <c r="J19" s="50">
         <v>0.22499999999999998</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="47">
         <v>30</v>
       </c>
-      <c r="L19" s="48">
+      <c r="L19" s="47">
         <v>1E-3</v>
       </c>
-      <c r="N19" s="48" t="s">
+      <c r="N19" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q19" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="R19" s="72" t="s">
-        <v>189</v>
-      </c>
-      <c r="S19" s="72" t="s">
+      <c r="O19" s="71"/>
+      <c r="P19" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q19" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="R19" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="S19" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="T19" s="72"/>
-      <c r="U19" s="72" t="s">
+      <c r="T19" s="71"/>
+      <c r="U19" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="V19" s="72"/>
+      <c r="V19" s="71"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -9596,7 +9904,7 @@
         <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E20">
         <v>2022</v>
@@ -9626,13 +9934,13 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S20" t="s">
         <v>95</v>
@@ -9642,61 +9950,61 @@
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B21" s="48" t="str">
+      <c r="B21" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TMOTNELC1</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="E21" s="48">
+      <c r="D21" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="47">
         <v>2026</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="47">
         <v>3.2</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="47">
         <v>8</v>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="47">
         <v>1.2</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="47">
         <v>2</v>
       </c>
-      <c r="J21" s="48">
+      <c r="J21" s="47">
         <v>0.02</v>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="47">
         <v>10</v>
       </c>
-      <c r="L21" s="57">
+      <c r="L21" s="56">
         <v>1E-3</v>
       </c>
-      <c r="N21" s="48" t="s">
+      <c r="N21" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O21" s="48"/>
-      <c r="P21" s="48" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q21" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="R21" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S21" s="48" t="s">
+      <c r="O21" s="47"/>
+      <c r="P21" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q21" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="R21" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S21" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48" t="s">
+      <c r="T21" s="47"/>
+      <c r="U21" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V21" s="48"/>
+      <c r="V21" s="47"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
@@ -9707,7 +10015,7 @@
         <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E22">
         <v>2022</v>
@@ -9737,13 +10045,13 @@
         <v>90</v>
       </c>
       <c r="P22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S22" t="s">
         <v>95</v>
@@ -9761,7 +10069,7 @@
         <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E23">
         <v>2022</v>
@@ -9791,13 +10099,13 @@
         <v>90</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S23" t="s">
         <v>95</v>
@@ -9807,61 +10115,61 @@
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B24" s="48" t="str">
+      <c r="B24" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TTRINELC1</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="48">
+      <c r="D24" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="47">
         <v>2026</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="47">
         <v>2.1</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="47">
         <v>12</v>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="47">
         <v>2</v>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="47">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J24" s="48">
+      <c r="J24" s="47">
         <v>0.12</v>
       </c>
-      <c r="K24" s="48">
+      <c r="K24" s="47">
         <v>10</v>
       </c>
-      <c r="L24" s="48">
+      <c r="L24" s="47">
         <v>1E-3</v>
       </c>
-      <c r="N24" s="48" t="s">
+      <c r="N24" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q24" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="R24" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S24" s="48" t="s">
+      <c r="O24" s="47"/>
+      <c r="P24" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q24" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="R24" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S24" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48" t="s">
+      <c r="T24" s="47"/>
+      <c r="U24" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V24" s="48"/>
+      <c r="V24" s="47"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
@@ -9871,8 +10179,8 @@
       <c r="C25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="66" t="s">
-        <v>209</v>
+      <c r="D25" s="65" t="s">
+        <v>208</v>
       </c>
       <c r="E25">
         <v>2022</v>
@@ -9902,13 +10210,13 @@
         <v>90</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S25" t="s">
         <v>95</v>
@@ -9925,8 +10233,8 @@
       <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="66" t="s">
-        <v>209</v>
+      <c r="D26" s="65" t="s">
+        <v>208</v>
       </c>
       <c r="E26">
         <v>2022</v>
@@ -9956,13 +10264,13 @@
         <v>90</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S26" t="s">
         <v>95</v>
@@ -9972,118 +10280,118 @@
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B27" s="48" t="str">
+      <c r="B27" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TFRENELC1</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="72" t="s">
-        <v>209</v>
-      </c>
-      <c r="E27" s="48">
+      <c r="D27" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="47">
         <v>2026</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="47">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="47">
         <v>50</v>
       </c>
-      <c r="H27" s="48">
+      <c r="H27" s="47">
         <v>12</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="47">
         <v>145</v>
       </c>
-      <c r="J27" s="48">
+      <c r="J27" s="47">
         <v>0.85</v>
       </c>
-      <c r="K27" s="48">
+      <c r="K27" s="47">
         <v>30</v>
       </c>
-      <c r="L27" s="57">
+      <c r="L27" s="56">
         <v>1E-3</v>
       </c>
-      <c r="N27" s="48" t="s">
+      <c r="N27" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q27" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="R27" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S27" s="48" t="s">
+      <c r="O27" s="47"/>
+      <c r="P27" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q27" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="R27" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S27" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48" t="s">
+      <c r="T27" s="47"/>
+      <c r="U27" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V27" s="48"/>
+      <c r="V27" s="47"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" s="48" t="str">
+      <c r="B28" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TAVINKER1</v>
       </c>
-      <c r="C28" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="D28" s="66" t="s">
+      <c r="C28" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="48">
+      <c r="D28" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="47">
         <v>2022</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="47">
         <v>0.1</v>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="47">
         <v>65</v>
       </c>
-      <c r="H28" s="48">
+      <c r="H28" s="47">
         <v>180</v>
       </c>
-      <c r="I28" s="48">
+      <c r="I28" s="47">
         <v>50000</v>
       </c>
-      <c r="J28" s="48">
+      <c r="J28" s="47">
         <v>70</v>
       </c>
-      <c r="K28" s="48">
+      <c r="K28" s="47">
         <v>30</v>
       </c>
-      <c r="L28" s="48">
+      <c r="L28" s="47">
         <v>1E-3</v>
       </c>
-      <c r="N28" s="48" t="s">
+      <c r="N28" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q28" s="48" t="s">
-        <v>231</v>
-      </c>
-      <c r="R28" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S28" s="48" t="s">
+      <c r="O28" s="47"/>
+      <c r="P28" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q28" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="R28" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S28" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48" t="s">
+      <c r="T28" s="47"/>
+      <c r="U28" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V28" s="48"/>
+      <c r="V28" s="47"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B29" t="str">
@@ -10093,8 +10401,8 @@
       <c r="C29" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="74" t="s">
-        <v>212</v>
+      <c r="D29" s="73" t="s">
+        <v>211</v>
       </c>
       <c r="E29">
         <v>2022</v>
@@ -10124,13 +10432,13 @@
         <v>90</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S29" t="s">
         <v>95</v>
@@ -10140,61 +10448,61 @@
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" s="48" t="str">
+      <c r="B30" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TRAINELC1</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="75" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" s="48">
+      <c r="D30" s="74" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="47">
         <v>2040</v>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="47">
         <v>0.78</v>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="47">
         <v>66</v>
       </c>
-      <c r="H30" s="48">
+      <c r="H30" s="47">
         <v>500</v>
       </c>
-      <c r="I30" s="48">
+      <c r="I30" s="47">
         <v>3100</v>
       </c>
-      <c r="J30" s="48">
+      <c r="J30" s="47">
         <v>22</v>
       </c>
-      <c r="K30" s="48">
+      <c r="K30" s="47">
         <v>30</v>
       </c>
-      <c r="L30" s="57">
+      <c r="L30" s="56">
         <v>1E-3</v>
       </c>
-      <c r="N30" s="48" t="s">
+      <c r="N30" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q30" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="R30" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S30" s="48" t="s">
+      <c r="O30" s="47"/>
+      <c r="P30" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q30" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="R30" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S30" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48" t="s">
+      <c r="T30" s="47"/>
+      <c r="U30" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V30" s="48"/>
+      <c r="V30" s="47"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B31" t="str">
@@ -10204,8 +10512,8 @@
       <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="66" t="s">
-        <v>213</v>
+      <c r="D31" s="65" t="s">
+        <v>212</v>
       </c>
       <c r="E31">
         <v>2022</v>
@@ -10235,13 +10543,13 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S31" t="s">
         <v>95</v>
@@ -10258,8 +10566,8 @@
       <c r="C32" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="66" t="s">
-        <v>213</v>
+      <c r="D32" s="65" t="s">
+        <v>212</v>
       </c>
       <c r="E32">
         <v>2022</v>
@@ -10289,13 +10597,13 @@
         <v>90</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S32" t="s">
         <v>95</v>
@@ -10305,61 +10613,61 @@
       </c>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B33" s="48" t="str">
+      <c r="B33" s="47" t="str">
         <f t="shared" si="0"/>
         <v>TMARNELC1</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="72" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="48">
+      <c r="D33" s="71" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="47">
         <v>2026</v>
       </c>
-      <c r="F33" s="48">
+      <c r="F33" s="47">
         <v>0.85</v>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="47">
         <v>50</v>
       </c>
-      <c r="H33" s="48">
+      <c r="H33" s="47">
         <v>400</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="47">
         <v>9500</v>
       </c>
-      <c r="J33" s="48">
+      <c r="J33" s="47">
         <v>70</v>
       </c>
-      <c r="K33" s="48">
+      <c r="K33" s="47">
         <v>30</v>
       </c>
-      <c r="L33" s="48">
+      <c r="L33" s="47">
         <v>1E-3</v>
       </c>
-      <c r="N33" s="48" t="s">
+      <c r="N33" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q33" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="R33" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="S33" s="48" t="s">
+      <c r="O33" s="47"/>
+      <c r="P33" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q33" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="R33" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="S33" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48" t="s">
+      <c r="T33" s="47"/>
+      <c r="U33" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="V33" s="48"/>
+      <c r="V33" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10376,25 +10684,25 @@
   <dimension ref="B2:AC2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2" style="58" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.140625" style="58"/>
-    <col min="13" max="13" width="5" style="58" customWidth="1"/>
-    <col min="14" max="15" width="2" style="58" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.140625" style="58"/>
-    <col min="27" max="27" width="2" style="58" customWidth="1"/>
-    <col min="28" max="28" width="2.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="58"/>
+    <col min="1" max="1" width="2" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="9.140625" style="57"/>
+    <col min="13" max="13" width="5" style="57" customWidth="1"/>
+    <col min="14" max="15" width="2" style="57" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="9.140625" style="57"/>
+    <col min="27" max="27" width="2" style="57" customWidth="1"/>
+    <col min="28" max="28" width="2.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="57"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="P2" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="59" t="s">
+      <c r="AC2" s="58" t="s">
         <v>168</v>
-      </c>
-      <c r="AC2" s="59" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74263D0B-0812-41BB-B0E8-1570B8177DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA11136-A126-4FD5-BE5F-BF2B46CE86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -3160,7 +3160,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3319,6 +3319,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3405,7 +3408,7 @@
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>21166</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
@@ -4684,7 +4687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A4B651-1072-492F-9C98-6FB421C5AC2C}">
-  <dimension ref="A1:Y58"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
@@ -4696,31 +4699,31 @@
     <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" style="23" customWidth="1"/>
-    <col min="13" max="13" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" style="23" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" style="23" customWidth="1"/>
+    <col min="14" max="14" width="7" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2" style="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.28515625" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q2" s="36"/>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="R2" s="36"/>
       <c r="S2" s="36"/>
       <c r="T2" s="36"/>
@@ -4729,8 +4732,9 @@
       <c r="W2" s="36"/>
       <c r="X2" s="36"/>
       <c r="Y2" s="36"/>
-    </row>
-    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.25">
+      <c r="Z2" s="36"/>
+    </row>
+    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4753,7 +4757,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>49</v>
       </c>
@@ -4775,48 +4779,48 @@
       <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="59" t="s">
+      <c r="R4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="60"/>
+      <c r="S4" s="59"/>
       <c r="T4" s="60"/>
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
       <c r="Y4" s="60"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q5" s="61" t="s">
+      <c r="Z4" s="60"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="62" t="s">
+      <c r="S5" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="T5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="U5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="V5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="61" t="s">
+      <c r="W5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="61" t="s">
+      <c r="X5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="61" t="s">
+      <c r="Y5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="61" t="s">
+      <c r="Z5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>56</v>
       </c>
@@ -4837,35 +4841,36 @@
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="35"/>
-      <c r="Q6" s="63" t="s">
+      <c r="J6" s="35"/>
+      <c r="R6" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="S6" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="T6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="U6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="V6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="63" t="s">
+      <c r="W6" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="63" t="s">
+      <c r="X6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="63" t="s">
+      <c r="Y6" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" s="63" t="s">
+      <c r="Z6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>65</v>
       </c>
@@ -4886,43 +4891,44 @@
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="32"/>
-      <c r="Q7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="J7" s="32"/>
+      <c r="R7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q9" s="3"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="7"/>
+      <c r="K10" s="6"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="5"/>
-      <c r="Q10" s="59" t="s">
+      <c r="M10" s="7"/>
+      <c r="N10" s="5"/>
+      <c r="R10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="59"/>
-      <c r="S10" s="60"/>
+      <c r="S10" s="59"/>
       <c r="T10" s="60"/>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
       <c r="W10" s="60"/>
       <c r="X10" s="60"/>
       <c r="Y10" s="60"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="60"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4948,53 +4954,56 @@
         <v>35</v>
       </c>
       <c r="J11" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="N11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="N11" s="15" t="s">
+      <c r="O11" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="O11" s="15" t="s">
+      <c r="P11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="61" t="s">
+      <c r="Q11" s="25"/>
+      <c r="R11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="S11" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="T11" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="U11" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="V11" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="V11" s="61" t="s">
+      <c r="W11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="W11" s="61" t="s">
+      <c r="X11" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="X11" s="61" t="s">
+      <c r="Y11" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="Y11" s="61" t="s">
+      <c r="Z11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -5015,53 +5024,54 @@
       <c r="I12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="17"/>
+      <c r="K12" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="L12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="M12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="N12" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="O12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="17" t="s">
+      <c r="P12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="R12" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="S12" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="T12" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="T12" s="64" t="s">
+      <c r="U12" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="64" t="s">
+      <c r="V12" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="64" t="s">
+      <c r="W12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="64" t="s">
+      <c r="X12" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="X12" s="64" t="s">
+      <c r="Y12" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="Y12" s="64" t="s">
+      <c r="Z12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>78</v>
       </c>
@@ -5072,26 +5082,26 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="20"/>
+      <c r="K13" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="L13" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="M13" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="N13" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="O13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="O13" s="19"/>
-      <c r="Q13" s="63" t="s">
+      <c r="P13" s="19"/>
+      <c r="R13" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="R13" s="63"/>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
       <c r="U13" s="63"/>
@@ -5099,10 +5109,11 @@
       <c r="W13" s="63"/>
       <c r="X13" s="63"/>
       <c r="Y13" s="63"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="63"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
-        <f>S14</f>
+        <f>T14</f>
         <v>ELCTNCOA01</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -5123,47 +5134,50 @@
       <c r="I14" s="27">
         <v>0.85</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K14" s="23">
         <v>1650</v>
       </c>
-      <c r="K14" s="27">
+      <c r="L14" s="27">
         <v>30</v>
       </c>
-      <c r="L14" s="27">
+      <c r="M14" s="27">
         <v>0.4</v>
       </c>
-      <c r="M14" s="23">
+      <c r="N14" s="23">
         <v>40</v>
       </c>
-      <c r="N14" s="23">
+      <c r="O14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O14" s="27">
+      <c r="P14" s="27">
         <v>1</v>
       </c>
-      <c r="Q14" s="65" t="s">
+      <c r="R14" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65" t="s">
+      <c r="S14" s="65"/>
+      <c r="T14" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="T14" s="65" t="s">
+      <c r="U14" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="U14" s="65" t="s">
+      <c r="V14" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V14" s="65" t="s">
+      <c r="W14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W14" s="60" t="s">
+      <c r="X14" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X14" s="65"/>
       <c r="Y14" s="65"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="65"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E15" s="23">
         <v>2025</v>
       </c>
@@ -5177,20 +5191,23 @@
       <c r="I15" s="27">
         <v>0.85</v>
       </c>
-      <c r="K15" s="27"/>
+      <c r="J15" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="Q15" s="65"/>
+      <c r="M15" s="27"/>
+      <c r="P15" s="27"/>
       <c r="R15" s="65"/>
       <c r="S15" s="65"/>
       <c r="T15" s="65"/>
       <c r="U15" s="65"/>
       <c r="V15" s="65"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="60"/>
       <c r="Y15" s="65"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="65"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E16" s="23">
         <v>2030</v>
       </c>
@@ -5204,20 +5221,23 @@
       <c r="I16" s="27">
         <v>0.85</v>
       </c>
-      <c r="K16" s="27"/>
+      <c r="J16" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="Q16" s="65"/>
+      <c r="M16" s="27"/>
+      <c r="P16" s="27"/>
       <c r="R16" s="65"/>
       <c r="S16" s="65"/>
       <c r="T16" s="65"/>
       <c r="U16" s="65"/>
       <c r="V16" s="65"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="65"/>
+      <c r="W16" s="65"/>
+      <c r="X16" s="60"/>
       <c r="Y16" s="65"/>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="65"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
@@ -5231,20 +5251,23 @@
       <c r="I17" s="27">
         <v>0.85</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="J17" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="Q17" s="65"/>
+      <c r="M17" s="27"/>
+      <c r="P17" s="27"/>
       <c r="R17" s="65"/>
       <c r="S17" s="65"/>
       <c r="T17" s="65"/>
       <c r="U17" s="65"/>
       <c r="V17" s="65"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="60"/>
       <c r="Y17" s="65"/>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="65"/>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
@@ -5258,22 +5281,25 @@
       <c r="I18" s="27">
         <v>0.85</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="J18" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="Q18" s="65"/>
+      <c r="M18" s="27"/>
+      <c r="P18" s="27"/>
       <c r="R18" s="65"/>
       <c r="S18" s="65"/>
       <c r="T18" s="65"/>
       <c r="U18" s="65"/>
       <c r="V18" s="65"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="60"/>
       <c r="Y18" s="65"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="65"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="str">
-        <f>S19</f>
+        <f>T19</f>
         <v>ELCTNOIL01</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -5294,47 +5320,50 @@
       <c r="I19" s="27">
         <v>0.85</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K19" s="23">
         <v>250</v>
       </c>
-      <c r="K19" s="27">
+      <c r="L19" s="27">
         <v>20</v>
       </c>
-      <c r="L19" s="27">
+      <c r="M19" s="27">
         <v>0.2</v>
       </c>
-      <c r="M19" s="23">
+      <c r="N19" s="23">
         <v>40</v>
       </c>
-      <c r="N19" s="23">
+      <c r="O19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O19" s="27">
+      <c r="P19" s="27">
         <v>1</v>
       </c>
-      <c r="Q19" s="65" t="s">
+      <c r="R19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65" t="s">
+      <c r="S19" s="65"/>
+      <c r="T19" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="T19" s="65" t="s">
+      <c r="U19" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="65" t="s">
+      <c r="V19" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V19" s="65" t="s">
+      <c r="W19" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="60" t="s">
+      <c r="X19" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X19" s="65"/>
       <c r="Y19" s="65"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="65"/>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E20" s="23">
         <v>2025</v>
       </c>
@@ -5347,20 +5376,23 @@
       <c r="I20" s="27">
         <v>0.85</v>
       </c>
-      <c r="K20" s="27"/>
+      <c r="J20" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="Q20" s="65"/>
+      <c r="M20" s="27"/>
+      <c r="P20" s="27"/>
       <c r="R20" s="65"/>
       <c r="S20" s="65"/>
       <c r="T20" s="65"/>
       <c r="U20" s="65"/>
       <c r="V20" s="65"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="65"/>
+      <c r="W20" s="65"/>
+      <c r="X20" s="60"/>
       <c r="Y20" s="65"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="65"/>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E21" s="23">
         <v>2030</v>
       </c>
@@ -5373,20 +5405,23 @@
       <c r="I21" s="27">
         <v>0.85</v>
       </c>
-      <c r="K21" s="27"/>
+      <c r="J21" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="Q21" s="65"/>
+      <c r="M21" s="27"/>
+      <c r="P21" s="27"/>
       <c r="R21" s="65"/>
       <c r="S21" s="65"/>
       <c r="T21" s="65"/>
       <c r="U21" s="65"/>
       <c r="V21" s="65"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="60"/>
       <c r="Y21" s="65"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="65"/>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E22" s="23">
         <v>2035</v>
       </c>
@@ -5399,20 +5434,23 @@
       <c r="I22" s="27">
         <v>0.85</v>
       </c>
-      <c r="K22" s="27"/>
+      <c r="J22" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="Q22" s="65"/>
+      <c r="M22" s="27"/>
+      <c r="P22" s="27"/>
       <c r="R22" s="65"/>
       <c r="S22" s="65"/>
       <c r="T22" s="65"/>
       <c r="U22" s="65"/>
       <c r="V22" s="65"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="60"/>
       <c r="Y22" s="65"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="65"/>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E23" s="23">
         <v>2040</v>
       </c>
@@ -5425,22 +5463,25 @@
       <c r="I23" s="27">
         <v>0.85</v>
       </c>
-      <c r="K23" s="27"/>
+      <c r="J23" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="Q23" s="65"/>
+      <c r="M23" s="27"/>
+      <c r="P23" s="27"/>
       <c r="R23" s="65"/>
       <c r="S23" s="65"/>
       <c r="T23" s="65"/>
       <c r="U23" s="65"/>
       <c r="V23" s="65"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="60"/>
       <c r="Y23" s="65"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="65"/>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="str">
-        <f>S24</f>
+        <f>T24</f>
         <v>ELCTNGAS01</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -5461,49 +5502,52 @@
       <c r="I24" s="27">
         <v>0.85</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K24" s="23">
         <v>1100</v>
       </c>
-      <c r="K24" s="27">
+      <c r="L24" s="27">
         <v>30</v>
       </c>
-      <c r="L24" s="27">
+      <c r="M24" s="27">
         <v>0.35</v>
       </c>
-      <c r="M24" s="23">
+      <c r="N24" s="23">
         <v>40</v>
       </c>
-      <c r="N24" s="23">
+      <c r="O24" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O24" s="27">
+      <c r="P24" s="27">
         <v>1</v>
       </c>
-      <c r="Q24" s="65" t="s">
+      <c r="R24" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65" t="s">
+      <c r="S24" s="65"/>
+      <c r="T24" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="T24" s="65" t="s">
+      <c r="U24" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="U24" s="65" t="s">
+      <c r="V24" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V24" s="65" t="s">
+      <c r="W24" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W24" s="60" t="s">
+      <c r="X24" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="65" t="s">
+      <c r="Y24" s="65"/>
+      <c r="Z24" s="65" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E25" s="23">
         <v>2030</v>
       </c>
@@ -5516,20 +5560,23 @@
       <c r="I25" s="27">
         <v>0.85</v>
       </c>
-      <c r="K25" s="27"/>
+      <c r="J25" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="Q25" s="65"/>
+      <c r="M25" s="27"/>
+      <c r="P25" s="27"/>
       <c r="R25" s="65"/>
       <c r="S25" s="65"/>
       <c r="T25" s="65"/>
       <c r="U25" s="65"/>
       <c r="V25" s="65"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="65"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="60"/>
       <c r="Y25" s="65"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="65"/>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E26" s="23">
         <v>2035</v>
       </c>
@@ -5542,32 +5589,35 @@
       <c r="I26" s="27">
         <v>0.85</v>
       </c>
-      <c r="K26" s="27"/>
+      <c r="J26" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="Q26" s="65" t="s">
+      <c r="M26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="R26" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65" t="s">
+      <c r="S26" s="65"/>
+      <c r="T26" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="T26" s="65" t="s">
+      <c r="U26" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="U26" s="65" t="s">
+      <c r="V26" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V26" s="65" t="s">
+      <c r="W26" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W26" s="60" t="s">
+      <c r="X26" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X26" s="65"/>
       <c r="Y26" s="65"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="65"/>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E27" s="23">
         <v>2040</v>
       </c>
@@ -5580,32 +5630,35 @@
       <c r="I27" s="27">
         <v>0.85</v>
       </c>
-      <c r="K27" s="27"/>
+      <c r="J27" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="Q27" s="65" t="s">
+      <c r="M27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R27" s="65"/>
-      <c r="S27" s="65" t="s">
+      <c r="S27" s="65"/>
+      <c r="T27" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="T27" s="65" t="s">
+      <c r="U27" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="U27" s="65" t="s">
+      <c r="V27" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V27" s="65" t="s">
+      <c r="W27" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W27" s="60" t="s">
+      <c r="X27" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X27" s="65"/>
       <c r="Y27" s="65"/>
-    </row>
-    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z27" s="65"/>
+    </row>
+    <row r="28" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="23">
         <v>2045</v>
       </c>
@@ -5618,34 +5671,37 @@
       <c r="I28" s="27">
         <v>0.85</v>
       </c>
-      <c r="K28" s="27"/>
+      <c r="J28" s="84" t="s">
+        <v>283</v>
+      </c>
       <c r="L28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="Q28" s="65" t="s">
+      <c r="M28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="R28" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65" t="s">
+      <c r="S28" s="65"/>
+      <c r="T28" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="T28" s="65" t="s">
+      <c r="U28" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="U28" s="65" t="s">
+      <c r="V28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V28" s="65" t="s">
+      <c r="W28" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W28" s="60" t="s">
+      <c r="X28" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X28" s="65"/>
       <c r="Y28" s="65"/>
-    </row>
-    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z28" s="65"/>
+    </row>
+    <row r="29" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
-        <f t="shared" ref="B29" si="0">S26</f>
+        <f t="shared" ref="B29" si="0">T26</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5666,47 +5722,50 @@
       <c r="I29" s="27">
         <v>0.6</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K29" s="23">
         <v>2500</v>
       </c>
-      <c r="K29" s="23">
+      <c r="L29" s="23">
         <v>30</v>
       </c>
-      <c r="L29" s="27">
+      <c r="M29" s="27">
         <v>0.35</v>
       </c>
-      <c r="M29" s="23">
+      <c r="N29" s="23">
         <v>25</v>
       </c>
-      <c r="N29" s="23">
+      <c r="O29" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O29" s="27">
+      <c r="P29" s="27">
         <v>1</v>
       </c>
-      <c r="Q29" s="65" t="s">
+      <c r="R29" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65" t="s">
+      <c r="S29" s="65"/>
+      <c r="T29" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="T29" s="65" t="s">
+      <c r="U29" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="U29" s="65" t="s">
+      <c r="V29" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V29" s="65" t="s">
+      <c r="W29" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W29" s="60" t="s">
+      <c r="X29" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X29" s="65"/>
       <c r="Y29" s="65"/>
-    </row>
-    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z29" s="65"/>
+    </row>
+    <row r="30" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="23">
         <v>2030</v>
       </c>
@@ -5719,19 +5778,22 @@
       <c r="I30" s="27">
         <v>0.6</v>
       </c>
-      <c r="L30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="Q30" s="65"/>
+      <c r="J30" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M30" s="27"/>
+      <c r="P30" s="27"/>
       <c r="R30" s="65"/>
       <c r="S30" s="65"/>
       <c r="T30" s="65"/>
       <c r="U30" s="65"/>
       <c r="V30" s="65"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="65"/>
+      <c r="W30" s="65"/>
+      <c r="X30" s="60"/>
       <c r="Y30" s="65"/>
-    </row>
-    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z30" s="65"/>
+    </row>
+    <row r="31" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="23">
         <v>2035</v>
       </c>
@@ -5744,19 +5806,22 @@
       <c r="I31" s="27">
         <v>0.6</v>
       </c>
-      <c r="L31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="Q31" s="65"/>
+      <c r="J31" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M31" s="27"/>
+      <c r="P31" s="27"/>
       <c r="R31" s="65"/>
       <c r="S31" s="65"/>
       <c r="T31" s="65"/>
       <c r="U31" s="65"/>
       <c r="V31" s="65"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="65"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="60"/>
       <c r="Y31" s="65"/>
-    </row>
-    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z31" s="65"/>
+    </row>
+    <row r="32" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="23">
         <v>2040</v>
       </c>
@@ -5769,21 +5834,24 @@
       <c r="I32" s="27">
         <v>0.6</v>
       </c>
-      <c r="L32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="Q32" s="65"/>
+      <c r="J32" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M32" s="27"/>
+      <c r="P32" s="27"/>
       <c r="R32" s="65"/>
       <c r="S32" s="65"/>
       <c r="T32" s="65"/>
       <c r="U32" s="65"/>
       <c r="V32" s="65"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="65"/>
+      <c r="W32" s="65"/>
+      <c r="X32" s="60"/>
       <c r="Y32" s="65"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="65"/>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B33" s="23" t="str">
-        <f>S27</f>
+        <f>T27</f>
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -5804,46 +5872,49 @@
       <c r="I33" s="27">
         <v>0.5</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J33" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K33" s="23">
         <v>3000</v>
       </c>
-      <c r="K33" s="23">
+      <c r="L33" s="23">
         <v>35</v>
       </c>
-      <c r="L33" s="27">
+      <c r="M33" s="27">
         <v>2</v>
       </c>
-      <c r="M33" s="23">
+      <c r="N33" s="23">
         <v>50</v>
       </c>
-      <c r="N33" s="23">
+      <c r="O33" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O33" s="27">
+      <c r="P33" s="27">
         <v>0.35</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>285</v>
       </c>
-      <c r="S33" s="23" t="s">
+      <c r="T33" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="T33" s="65" t="s">
+      <c r="U33" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="U33" s="65" t="s">
+      <c r="V33" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V33" s="65" t="s">
+      <c r="W33" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W33" s="60" t="s">
+      <c r="X33" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="X33" s="65"/>
       <c r="Y33" s="65"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="65"/>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E34" s="23">
         <v>2025</v>
       </c>
@@ -5856,17 +5927,20 @@
       <c r="I34" s="27">
         <v>0.5</v>
       </c>
-      <c r="L34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="65"/>
+      <c r="J34" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M34" s="27"/>
+      <c r="P34" s="27"/>
+      <c r="T34" s="23"/>
       <c r="U34" s="65"/>
       <c r="V34" s="65"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="65"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="60"/>
       <c r="Y34" s="65"/>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="65"/>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E35" s="23">
         <v>2030</v>
       </c>
@@ -5879,17 +5953,20 @@
       <c r="I35" s="27">
         <v>0.5</v>
       </c>
-      <c r="L35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="65"/>
+      <c r="J35" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M35" s="27"/>
+      <c r="P35" s="27"/>
+      <c r="T35" s="23"/>
       <c r="U35" s="65"/>
       <c r="V35" s="65"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="60"/>
       <c r="Y35" s="65"/>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="65"/>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E36" s="23">
         <v>2035</v>
       </c>
@@ -5902,17 +5979,20 @@
       <c r="I36" s="27">
         <v>0.5</v>
       </c>
-      <c r="L36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="65"/>
+      <c r="J36" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M36" s="27"/>
+      <c r="P36" s="27"/>
+      <c r="T36" s="23"/>
       <c r="U36" s="65"/>
       <c r="V36" s="65"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="65"/>
+      <c r="W36" s="65"/>
+      <c r="X36" s="60"/>
       <c r="Y36" s="65"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z36" s="65"/>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E37" s="23">
         <v>2040</v>
       </c>
@@ -5925,19 +6005,22 @@
       <c r="I37" s="27">
         <v>0.5</v>
       </c>
-      <c r="L37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="65"/>
+      <c r="J37" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M37" s="27"/>
+      <c r="P37" s="27"/>
+      <c r="T37" s="23"/>
       <c r="U37" s="65"/>
       <c r="V37" s="65"/>
-      <c r="W37" s="60"/>
-      <c r="X37" s="65"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="60"/>
       <c r="Y37" s="65"/>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z37" s="65"/>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B38" s="23" t="str">
-        <f>S28</f>
+        <f>T28</f>
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
@@ -5958,43 +6041,46 @@
       <c r="I38" s="27">
         <v>0.35</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K38" s="23">
         <v>1340</v>
       </c>
-      <c r="K38" s="23">
+      <c r="L38" s="23">
         <v>26.7</v>
       </c>
-      <c r="L38" s="27"/>
-      <c r="M38" s="23">
+      <c r="M38" s="27"/>
+      <c r="N38" s="23">
         <v>25</v>
       </c>
-      <c r="N38" s="23">
+      <c r="O38" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O38" s="27">
+      <c r="P38" s="27">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="65" t="s">
+      <c r="R38" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S38" s="23" t="s">
+      <c r="T38" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="T38" s="65" t="s">
+      <c r="U38" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="U38" s="65" t="s">
+      <c r="V38" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V38" s="65" t="s">
+      <c r="W38" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W38" s="60" t="s">
+      <c r="X38" s="60" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="F39" s="23">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="E39" s="23">
         <v>2030</v>
       </c>
       <c r="G39" s="27">
@@ -6006,24 +6092,27 @@
       <c r="I39" s="27">
         <v>0.35</v>
       </c>
-      <c r="J39" s="23">
-        <f>J38*0.95</f>
+      <c r="J39" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K39" s="23">
+        <f>K38*0.95</f>
         <v>1273</v>
       </c>
-      <c r="K39" s="23">
-        <f t="shared" ref="K39:K40" si="1">K38*0.95</f>
+      <c r="L39" s="23">
+        <f t="shared" ref="L39:L40" si="1">L38*0.95</f>
         <v>25.364999999999998</v>
       </c>
-      <c r="O39" s="27"/>
-      <c r="Q39" s="65"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="65"/>
+      <c r="P39" s="27"/>
+      <c r="R39" s="65"/>
+      <c r="T39" s="23"/>
       <c r="U39" s="65"/>
       <c r="V39" s="65"/>
-      <c r="W39" s="60"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="F40" s="23">
+      <c r="W39" s="65"/>
+      <c r="X39" s="60"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="E40" s="23">
         <v>2035</v>
       </c>
       <c r="G40" s="27">
@@ -6035,24 +6124,27 @@
       <c r="I40" s="27">
         <v>0.35</v>
       </c>
-      <c r="J40" s="23">
-        <f>J39*0.95</f>
+      <c r="J40" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K40" s="23">
+        <f>K39*0.95</f>
         <v>1209.3499999999999</v>
       </c>
-      <c r="K40" s="23">
+      <c r="L40" s="23">
         <f t="shared" si="1"/>
         <v>24.096749999999997</v>
       </c>
-      <c r="O40" s="27"/>
-      <c r="Q40" s="65"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="65"/>
+      <c r="P40" s="27"/>
+      <c r="R40" s="65"/>
+      <c r="T40" s="23"/>
       <c r="U40" s="65"/>
       <c r="V40" s="65"/>
-      <c r="W40" s="60"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="F41" s="23">
+      <c r="W40" s="65"/>
+      <c r="X40" s="60"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="E41" s="23">
         <v>2040</v>
       </c>
       <c r="G41" s="27">
@@ -6064,17 +6156,20 @@
       <c r="I41" s="27">
         <v>0.35</v>
       </c>
-      <c r="O41" s="27"/>
-      <c r="Q41" s="65"/>
-      <c r="S41" s="23"/>
-      <c r="T41" s="65"/>
+      <c r="J41" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="P41" s="27"/>
+      <c r="R41" s="65"/>
+      <c r="T41" s="23"/>
       <c r="U41" s="65"/>
       <c r="V41" s="65"/>
-      <c r="W41" s="60"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W41" s="65"/>
+      <c r="X41" s="60"/>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B42" s="23" t="str">
-        <f>S29</f>
+        <f>T29</f>
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -6095,44 +6190,47 @@
       <c r="I42" s="27">
         <v>0.2</v>
       </c>
-      <c r="J42" s="23">
+      <c r="J42" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K42" s="23">
         <v>550</v>
       </c>
-      <c r="K42" s="23">
+      <c r="L42" s="23">
         <v>7</v>
       </c>
-      <c r="L42" s="27">
+      <c r="M42" s="27">
         <v>0</v>
       </c>
-      <c r="M42" s="23">
+      <c r="N42" s="23">
         <v>25</v>
       </c>
-      <c r="N42" s="23">
+      <c r="O42" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O42" s="27">
+      <c r="P42" s="27">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="65" t="s">
+      <c r="R42" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S42" s="23" t="s">
+      <c r="T42" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="T42" s="65" t="s">
+      <c r="U42" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="U42" s="65" t="s">
+      <c r="V42" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="V42" s="65" t="s">
+      <c r="W42" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="W42" s="60" t="s">
+      <c r="X42" s="60" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E43" s="23">
         <v>2025</v>
       </c>
@@ -6145,16 +6243,19 @@
       <c r="I43" s="27">
         <v>0.2</v>
       </c>
-      <c r="L43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="Q43" s="65"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="65"/>
+      <c r="J43" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M43" s="27"/>
+      <c r="P43" s="27"/>
+      <c r="R43" s="65"/>
+      <c r="T43" s="23"/>
       <c r="U43" s="65"/>
       <c r="V43" s="65"/>
-      <c r="W43" s="60"/>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W43" s="65"/>
+      <c r="X43" s="60"/>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E44" s="23">
         <v>2030</v>
       </c>
@@ -6167,16 +6268,19 @@
       <c r="I44" s="27">
         <v>0.2</v>
       </c>
-      <c r="L44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="Q44" s="65"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="65"/>
+      <c r="J44" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="R44" s="65"/>
+      <c r="T44" s="23"/>
       <c r="U44" s="65"/>
       <c r="V44" s="65"/>
-      <c r="W44" s="60"/>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W44" s="65"/>
+      <c r="X44" s="60"/>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E45" s="23">
         <v>2035</v>
       </c>
@@ -6189,16 +6293,19 @@
       <c r="I45" s="27">
         <v>0.2</v>
       </c>
-      <c r="L45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="Q45" s="65"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="65"/>
+      <c r="J45" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M45" s="27"/>
+      <c r="P45" s="27"/>
+      <c r="R45" s="65"/>
+      <c r="T45" s="23"/>
       <c r="U45" s="65"/>
       <c r="V45" s="65"/>
-      <c r="W45" s="60"/>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W45" s="65"/>
+      <c r="X45" s="60"/>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E46" s="23">
         <v>2040</v>
       </c>
@@ -6211,18 +6318,21 @@
       <c r="I46" s="27">
         <v>0.2</v>
       </c>
-      <c r="L46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="Q46" s="65"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="65"/>
+      <c r="J46" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="R46" s="65"/>
+      <c r="T46" s="23"/>
       <c r="U46" s="65"/>
       <c r="V46" s="65"/>
-      <c r="W46" s="60"/>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="W46" s="65"/>
+      <c r="X46" s="60"/>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B47" s="23" t="str">
-        <f>S38</f>
+        <f>T38</f>
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -6243,27 +6353,30 @@
       <c r="I47" s="27">
         <v>0.25</v>
       </c>
-      <c r="J47" s="23">
+      <c r="J47" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K47" s="23">
         <v>1090</v>
       </c>
-      <c r="K47" s="23">
-        <f>J47*0.02</f>
+      <c r="L47" s="23">
+        <f>K47*0.02</f>
         <v>21.8</v>
       </c>
-      <c r="L47" s="27">
+      <c r="M47" s="27">
         <v>0</v>
       </c>
-      <c r="M47" s="23">
+      <c r="N47" s="23">
         <v>25</v>
       </c>
-      <c r="N47" s="23">
+      <c r="O47" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O47" s="27">
+      <c r="P47" s="27">
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E48" s="23">
         <v>2025</v>
       </c>
@@ -6276,10 +6389,13 @@
       <c r="I48" s="27">
         <v>0.25</v>
       </c>
-      <c r="L48" s="27"/>
-      <c r="O48" s="27"/>
-    </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J48" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M48" s="27"/>
+      <c r="P48" s="27"/>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E49" s="23">
         <v>2030</v>
       </c>
@@ -6292,10 +6408,13 @@
       <c r="I49" s="27">
         <v>0.25</v>
       </c>
-      <c r="L49" s="27"/>
-      <c r="O49" s="27"/>
-    </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J49" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M49" s="27"/>
+      <c r="P49" s="27"/>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E50" s="23">
         <v>2035</v>
       </c>
@@ -6308,10 +6427,13 @@
       <c r="I50" s="27">
         <v>0.25</v>
       </c>
-      <c r="L50" s="27"/>
-      <c r="O50" s="27"/>
-    </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J50" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M50" s="27"/>
+      <c r="P50" s="27"/>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E51" s="23">
         <v>2040</v>
       </c>
@@ -6324,12 +6446,15 @@
       <c r="I51" s="27">
         <v>0.25</v>
       </c>
-      <c r="L51" s="27"/>
-      <c r="O51" s="27"/>
-    </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J51" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M51" s="27"/>
+      <c r="P51" s="27"/>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B52" s="23" t="str">
-        <f>S42</f>
+        <f>T42</f>
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
@@ -6350,26 +6475,29 @@
       <c r="I52" s="23">
         <v>0.8</v>
       </c>
-      <c r="J52" s="23">
+      <c r="J52" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K52" s="23">
         <v>1990</v>
       </c>
-      <c r="K52" s="23">
+      <c r="L52" s="23">
         <v>39.799999999999997</v>
       </c>
-      <c r="L52" s="27">
+      <c r="M52" s="27">
         <v>2</v>
       </c>
-      <c r="M52" s="23">
+      <c r="N52" s="23">
         <v>40</v>
       </c>
-      <c r="N52" s="23">
+      <c r="O52" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O52" s="23">
+      <c r="P52" s="23">
         <v>0.45</v>
       </c>
     </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E53" s="23">
         <v>2035</v>
       </c>
@@ -6382,9 +6510,12 @@
       <c r="I53" s="23">
         <v>0.8</v>
       </c>
-      <c r="L53" s="27"/>
-    </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J53" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M53" s="27"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E54" s="23">
         <v>2040</v>
       </c>
@@ -6397,9 +6528,12 @@
       <c r="I54" s="23">
         <v>0.8</v>
       </c>
-      <c r="L54" s="27"/>
-    </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J54" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="M54" s="27"/>
+    </row>
+    <row r="55" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B55" s="23" t="s">
         <v>193</v>
       </c>
@@ -6421,25 +6555,28 @@
       <c r="I55" s="23">
         <v>0.15</v>
       </c>
-      <c r="J55" s="23">
+      <c r="J55" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="K55" s="23">
         <v>490</v>
       </c>
-      <c r="K55" s="23">
+      <c r="L55" s="23">
         <v>9.8000000000000007</v>
       </c>
-      <c r="M55" s="23">
+      <c r="N55" s="23">
         <v>15</v>
       </c>
-      <c r="N55" s="23">
+      <c r="O55" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O55" s="23">
+      <c r="P55" s="23">
         <v>0.5</v>
       </c>
-      <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-    </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="23"/>
+    </row>
+    <row r="56" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E56" s="23">
         <v>2030</v>
       </c>
@@ -6452,8 +6589,11 @@
       <c r="I56" s="23">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J56" s="84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E57" s="23">
         <v>2035</v>
       </c>
@@ -6466,8 +6606,11 @@
       <c r="I57" s="23">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="J57" s="84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E58" s="23">
         <v>2040</v>
       </c>
@@ -6479,6 +6622,9 @@
       </c>
       <c r="I58" s="23">
         <v>0.15</v>
+      </c>
+      <c r="J58" s="84" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA11136-A126-4FD5-BE5F-BF2B46CE86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B22DF-33E6-411A-BF53-BCCFD936857E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="12" r:id="rId1"/>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="313">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2578,9 +2578,6 @@
   </si>
   <si>
     <t>ANNUAL</t>
-  </si>
-  <si>
-    <t>ELE, STG</t>
   </si>
   <si>
     <t>TRAINHFO1</t>
@@ -4734,7 +4731,7 @@
       <c r="Y2" s="36"/>
       <c r="Z2" s="36"/>
     </row>
-    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4948,7 +4945,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -5019,7 +5016,7 @@
         <v>37</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>72</v>
@@ -5197,13 +5194,25 @@
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
       <c r="P15" s="27"/>
-      <c r="R15" s="65"/>
+      <c r="R15" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="65"/>
-      <c r="X15" s="60"/>
+      <c r="T15" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="U15" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="V15" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W15" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X15" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y15" s="65"/>
       <c r="Z15" s="65"/>
     </row>
@@ -5227,15 +5236,29 @@
       <c r="L16" s="27"/>
       <c r="M16" s="27"/>
       <c r="P16" s="27"/>
-      <c r="R16" s="65"/>
+      <c r="R16" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S16" s="65"/>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="65"/>
-      <c r="X16" s="60"/>
+      <c r="T16" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="U16" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="V16" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W16" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X16" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y16" s="65"/>
-      <c r="Z16" s="65"/>
+      <c r="Z16" s="65" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
@@ -5257,13 +5280,25 @@
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
       <c r="P17" s="27"/>
-      <c r="R17" s="65"/>
+      <c r="R17" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="60"/>
+      <c r="T17" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="U17" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="V17" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W17" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X17" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y17" s="65"/>
       <c r="Z17" s="65"/>
     </row>
@@ -5287,19 +5322,31 @@
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
       <c r="P18" s="27"/>
-      <c r="R18" s="65"/>
+      <c r="R18" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="60"/>
+      <c r="T18" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="U18" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="V18" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W18" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X18" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y18" s="65"/>
       <c r="Z18" s="65"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="str">
-        <f>T19</f>
+        <f>T15</f>
         <v>ELCTNOIL01</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -5346,10 +5393,10 @@
       </c>
       <c r="S19" s="65"/>
       <c r="T19" s="65" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="U19" s="65" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="V19" s="65" t="s">
         <v>52</v>
@@ -5382,13 +5429,25 @@
       <c r="L20" s="27"/>
       <c r="M20" s="27"/>
       <c r="P20" s="27"/>
-      <c r="R20" s="65"/>
+      <c r="R20" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="65"/>
-      <c r="X20" s="60"/>
+      <c r="T20" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="U20" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="V20" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W20" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X20" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y20" s="65"/>
       <c r="Z20" s="65"/>
     </row>
@@ -5411,13 +5470,25 @@
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="P21" s="27"/>
-      <c r="R21" s="65"/>
+      <c r="R21" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="60"/>
+      <c r="T21" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="U21" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="V21" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W21" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X21" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y21" s="65"/>
       <c r="Z21" s="65"/>
     </row>
@@ -5440,13 +5511,25 @@
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
       <c r="P22" s="27"/>
-      <c r="R22" s="65"/>
+      <c r="R22" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="60"/>
+      <c r="T22" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="U22" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="V22" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W22" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X22" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y22" s="65"/>
       <c r="Z22" s="65"/>
     </row>
@@ -5469,19 +5552,31 @@
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
       <c r="P23" s="27"/>
-      <c r="R23" s="65"/>
+      <c r="R23" s="65" t="s">
+        <v>81</v>
+      </c>
       <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="60"/>
+      <c r="T23" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="U23" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="V23" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="W23" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="X23" s="60" t="s">
+        <v>202</v>
+      </c>
       <c r="Y23" s="65"/>
       <c r="Z23" s="65"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="str">
-        <f>T24</f>
+        <f>T16</f>
         <v>ELCTNGAS01</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -5523,29 +5618,9 @@
       <c r="P24" s="27">
         <v>1</v>
       </c>
-      <c r="R24" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="R24" s="65"/>
       <c r="S24" s="65"/>
-      <c r="T24" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="U24" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="V24" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W24" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X24" s="60" t="s">
-        <v>202</v>
-      </c>
       <c r="Y24" s="65"/>
-      <c r="Z24" s="65" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E25" s="23">
@@ -5595,25 +5670,8 @@
       <c r="L26" s="27"/>
       <c r="M26" s="27"/>
       <c r="P26" s="27"/>
-      <c r="R26" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="R26" s="65"/>
       <c r="S26" s="65"/>
-      <c r="T26" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="U26" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="V26" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W26" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X26" s="60" t="s">
-        <v>202</v>
-      </c>
       <c r="Y26" s="65"/>
       <c r="Z26" s="65"/>
     </row>
@@ -5636,25 +5694,8 @@
       <c r="L27" s="27"/>
       <c r="M27" s="27"/>
       <c r="P27" s="27"/>
-      <c r="R27" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="R27" s="65"/>
       <c r="S27" s="65"/>
-      <c r="T27" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="U27" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="V27" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W27" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X27" s="60" t="s">
-        <v>202</v>
-      </c>
       <c r="Y27" s="65"/>
       <c r="Z27" s="65"/>
     </row>
@@ -5677,31 +5718,14 @@
       <c r="L28" s="27"/>
       <c r="M28" s="27"/>
       <c r="P28" s="27"/>
-      <c r="R28" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="R28" s="65"/>
       <c r="S28" s="65"/>
-      <c r="T28" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="U28" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="V28" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W28" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X28" s="60" t="s">
-        <v>202</v>
-      </c>
       <c r="Y28" s="65"/>
       <c r="Z28" s="65"/>
     </row>
     <row r="29" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
-        <f t="shared" ref="B29" si="0">T26</f>
+        <f>T17</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5743,25 +5767,8 @@
       <c r="P29" s="27">
         <v>1</v>
       </c>
-      <c r="R29" s="65" t="s">
-        <v>81</v>
-      </c>
+      <c r="R29" s="65"/>
       <c r="S29" s="65"/>
-      <c r="T29" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="U29" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="V29" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W29" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X29" s="60" t="s">
-        <v>202</v>
-      </c>
       <c r="Y29" s="65"/>
       <c r="Z29" s="65"/>
     </row>
@@ -5851,7 +5858,7 @@
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B33" s="23" t="str">
-        <f>T27</f>
+        <f>T18</f>
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -5893,24 +5900,7 @@
       <c r="P33" s="27">
         <v>0.35</v>
       </c>
-      <c r="R33" t="s">
-        <v>285</v>
-      </c>
-      <c r="T33" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="U33" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="V33" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W33" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X33" s="60" t="s">
-        <v>202</v>
-      </c>
+      <c r="R33" s="65"/>
       <c r="Y33" s="65"/>
       <c r="Z33" s="65"/>
     </row>
@@ -5932,6 +5922,7 @@
       </c>
       <c r="M34" s="27"/>
       <c r="P34" s="27"/>
+      <c r="R34" s="65"/>
       <c r="T34" s="23"/>
       <c r="U34" s="65"/>
       <c r="V34" s="65"/>
@@ -5958,6 +5949,7 @@
       </c>
       <c r="M35" s="27"/>
       <c r="P35" s="27"/>
+      <c r="R35" s="65"/>
       <c r="T35" s="23"/>
       <c r="U35" s="65"/>
       <c r="V35" s="65"/>
@@ -5984,6 +5976,7 @@
       </c>
       <c r="M36" s="27"/>
       <c r="P36" s="27"/>
+      <c r="R36" s="65"/>
       <c r="T36" s="23"/>
       <c r="U36" s="65"/>
       <c r="V36" s="65"/>
@@ -6010,6 +6003,7 @@
       </c>
       <c r="M37" s="27"/>
       <c r="P37" s="27"/>
+      <c r="R37" s="65"/>
       <c r="T37" s="23"/>
       <c r="U37" s="65"/>
       <c r="V37" s="65"/>
@@ -6020,7 +6014,7 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B38" s="23" t="str">
-        <f>T28</f>
+        <f>T19</f>
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
@@ -6060,24 +6054,7 @@
       <c r="P38" s="27">
         <v>0.3</v>
       </c>
-      <c r="R38" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="T38" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="U38" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="V38" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W38" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X38" s="60" t="s">
-        <v>202</v>
-      </c>
+      <c r="R38" s="65"/>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E39" s="23">
@@ -6100,7 +6077,7 @@
         <v>1273</v>
       </c>
       <c r="L39" s="23">
-        <f t="shared" ref="L39:L40" si="1">L38*0.95</f>
+        <f t="shared" ref="L39:L40" si="0">L38*0.95</f>
         <v>25.364999999999998</v>
       </c>
       <c r="P39" s="27"/>
@@ -6132,7 +6109,7 @@
         <v>1209.3499999999999</v>
       </c>
       <c r="L40" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24.096749999999997</v>
       </c>
       <c r="P40" s="27"/>
@@ -6169,7 +6146,7 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B42" s="23" t="str">
-        <f>T29</f>
+        <f>T20</f>
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -6211,24 +6188,7 @@
       <c r="P42" s="27">
         <v>0.2</v>
       </c>
-      <c r="R42" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="T42" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="U42" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="V42" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W42" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="X42" s="60" t="s">
-        <v>202</v>
-      </c>
+      <c r="R42" s="65"/>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E43" s="23">
@@ -6332,7 +6292,7 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B47" s="23" t="str">
-        <f>T38</f>
+        <f>T22</f>
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -6375,6 +6335,7 @@
       <c r="P47" s="27">
         <v>0.5</v>
       </c>
+      <c r="R47" s="65"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="E48" s="23">
@@ -6394,6 +6355,7 @@
       </c>
       <c r="M48" s="27"/>
       <c r="P48" s="27"/>
+      <c r="R48" s="65"/>
     </row>
     <row r="49" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E49" s="23">
@@ -6413,6 +6375,7 @@
       </c>
       <c r="M49" s="27"/>
       <c r="P49" s="27"/>
+      <c r="R49" s="65"/>
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E50" s="23">
@@ -6432,6 +6395,7 @@
       </c>
       <c r="M50" s="27"/>
       <c r="P50" s="27"/>
+      <c r="R50" s="65"/>
     </row>
     <row r="51" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E51" s="23">
@@ -6451,10 +6415,11 @@
       </c>
       <c r="M51" s="27"/>
       <c r="P51" s="27"/>
+      <c r="R51" s="65"/>
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B52" s="23" t="str">
-        <f>T42</f>
+        <f>T23</f>
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
@@ -6496,6 +6461,7 @@
       <c r="P52" s="23">
         <v>0.45</v>
       </c>
+      <c r="R52" s="65"/>
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E53" s="23">
@@ -6514,6 +6480,7 @@
         <v>283</v>
       </c>
       <c r="M53" s="27"/>
+      <c r="R53" s="65"/>
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E54" s="23">
@@ -6532,6 +6499,7 @@
         <v>283</v>
       </c>
       <c r="M54" s="27"/>
+      <c r="R54" s="65"/>
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B55" s="23" t="s">
@@ -6573,6 +6541,7 @@
       <c r="P55" s="23">
         <v>0.5</v>
       </c>
+      <c r="R55" s="65"/>
       <c r="T55" s="23"/>
       <c r="U55" s="23"/>
     </row>
@@ -7756,7 +7725,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>52</v>
@@ -7775,11 +7744,11 @@
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E11" s="2">
         <v>2022</v>
@@ -7798,11 +7767,11 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E12" s="2">
         <v>2022</v>
@@ -7820,11 +7789,11 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E13" s="2">
         <v>2022</v>
@@ -7842,11 +7811,11 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E14" s="2">
         <v>2022</v>
@@ -7864,11 +7833,11 @@
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E15" s="2">
         <v>2022</v>
@@ -7885,11 +7854,11 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E16" s="2">
         <v>2022</v>
@@ -7906,10 +7875,10 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E17" s="2">
         <v>2022</v>
@@ -7923,7 +7892,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B18" s="60" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D18" t="s">
         <v>49</v>
@@ -7940,7 +7909,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" t="s">
         <v>49</v>
@@ -7957,7 +7926,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D20" t="s">
         <v>49</v>
@@ -7975,7 +7944,7 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D21" t="s">
         <v>49</v>
@@ -7994,25 +7963,25 @@
       <c r="B24" s="44"/>
       <c r="C24" s="2"/>
       <c r="K24" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="O24" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -10578,7 +10547,7 @@
         <v>90</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q29" t="s">
         <v>226</v>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B22DF-33E6-411A-BF53-BCCFD936857E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EA911B-5167-403C-BD8A-2D1C3439550F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -1723,7 +1724,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="313">
   <si>
     <t>~FI_T</t>
   </si>
@@ -3157,7 +3158,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3316,9 +3317,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3405,7 +3403,7 @@
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>21166</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
@@ -4397,6 +4395,47 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EB1"/>
+      <sheetName val="RES_PRI"/>
+      <sheetName val="Pri_COA"/>
+      <sheetName val="Pri_GAS"/>
+      <sheetName val="Pri_OIL"/>
+      <sheetName val="Pri_RNW"/>
+      <sheetName val="Pri_PP"/>
+      <sheetName val="Pri_ELC"/>
+      <sheetName val="Con_REF"/>
+      <sheetName val="TOTCO2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>IMP</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -4684,7 +4723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A4B651-1072-492F-9C98-6FB421C5AC2C}">
-  <dimension ref="A1:Z58"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
@@ -4696,31 +4735,31 @@
     <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" style="23" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" style="23" customWidth="1"/>
-    <col min="14" max="14" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2" style="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5703125" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.7109375" customWidth="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="7" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Q2" s="36"/>
       <c r="R2" s="36"/>
       <c r="S2" s="36"/>
       <c r="T2" s="36"/>
@@ -4729,9 +4768,8 @@
       <c r="W2" s="36"/>
       <c r="X2" s="36"/>
       <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-    </row>
-    <row r="3" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4754,7 +4792,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>49</v>
       </c>
@@ -4776,48 +4814,48 @@
       <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="59" t="s">
+      <c r="Q4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="60"/>
       <c r="T4" s="60"/>
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
       <c r="Y4" s="60"/>
-      <c r="Z4" s="60"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R5" s="61" t="s">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Q5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="62" t="s">
+      <c r="R5" s="62" t="s">
         <v>55</v>
       </c>
+      <c r="S5" s="61" t="s">
+        <v>6</v>
+      </c>
       <c r="T5" s="61" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U5" s="61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5" s="61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5" s="61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X5" s="61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y5" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
         <v>56</v>
       </c>
@@ -4838,36 +4876,35 @@
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
+      <c r="Q6" s="63" t="s">
+        <v>61</v>
+      </c>
       <c r="R6" s="63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S6" s="63" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="T6" s="63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U6" s="63" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="V6" s="63" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="W6" s="63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X6" s="63" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="Y6" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>65</v>
       </c>
@@ -4888,44 +4925,43 @@
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="R7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="5"/>
-      <c r="R10" s="59" t="s">
+      <c r="M10" s="5"/>
+      <c r="Q10" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="S10" s="59"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="60"/>
       <c r="T10" s="60"/>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
       <c r="W10" s="60"/>
       <c r="X10" s="60"/>
       <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4951,56 +4987,53 @@
         <v>35</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M11" s="16" t="s">
         <v>36</v>
       </c>
+      <c r="M11" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="P11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="61" t="s">
+      <c r="P11" s="25"/>
+      <c r="Q11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="S11" s="62" t="s">
+      <c r="R11" s="62" t="s">
         <v>55</v>
       </c>
+      <c r="S11" s="61" t="s">
+        <v>1</v>
+      </c>
       <c r="T11" s="61" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" s="61" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="V11" s="61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W11" s="61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X11" s="61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y11" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z11" s="61" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -5021,54 +5054,53 @@
       <c r="I12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="17"/>
+      <c r="J12" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="K12" s="17" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P12" s="17" t="s">
         <v>74</v>
       </c>
+      <c r="Q12" s="64" t="s">
+        <v>75</v>
+      </c>
       <c r="R12" s="64" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="S12" s="64" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="T12" s="64" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U12" s="64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V12" s="64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W12" s="64" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="X12" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y12" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z12" s="64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>78</v>
       </c>
@@ -5079,26 +5111,26 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="J13" s="19" t="s">
+        <v>199</v>
+      </c>
       <c r="K13" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="O13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="19"/>
-      <c r="R13" s="63" t="s">
+      <c r="O13" s="19"/>
+      <c r="Q13" s="63" t="s">
         <v>97</v>
       </c>
+      <c r="R13" s="63"/>
       <c r="S13" s="63"/>
       <c r="T13" s="63"/>
       <c r="U13" s="63"/>
@@ -5106,11 +5138,10 @@
       <c r="W13" s="63"/>
       <c r="X13" s="63"/>
       <c r="Y13" s="63"/>
-      <c r="Z13" s="63"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="23" t="str">
-        <f>T14</f>
+        <f>S14</f>
         <v>ELCTNCOA01</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -5131,50 +5162,47 @@
       <c r="I14" s="27">
         <v>0.85</v>
       </c>
-      <c r="J14" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="K14" s="23">
+      <c r="J14" s="23">
         <v>1650</v>
       </c>
+      <c r="K14" s="27">
+        <v>30</v>
+      </c>
       <c r="L14" s="27">
-        <v>30</v>
-      </c>
-      <c r="M14" s="27">
         <v>0.4</v>
       </c>
+      <c r="M14" s="23">
+        <v>40</v>
+      </c>
       <c r="N14" s="23">
-        <v>40</v>
-      </c>
-      <c r="O14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P14" s="27">
+      <c r="O14" s="27">
         <v>1</v>
       </c>
-      <c r="R14" s="65" t="s">
+      <c r="Q14" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65" t="s">
+        <v>151</v>
+      </c>
       <c r="T14" s="65" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="U14" s="65" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="V14" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X14" s="60" t="s">
+      <c r="W14" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X14" s="65"/>
       <c r="Y14" s="65"/>
-      <c r="Z14" s="65"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E15" s="23">
         <v>2025</v>
       </c>
@@ -5188,35 +5216,32 @@
       <c r="I15" s="27">
         <v>0.85</v>
       </c>
-      <c r="J15" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K15" s="27"/>
       <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="R15" s="65" t="s">
+      <c r="O15" s="27"/>
+      <c r="Q15" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65" t="s">
+        <v>153</v>
+      </c>
       <c r="T15" s="65" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="U15" s="65" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="V15" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W15" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X15" s="60" t="s">
+      <c r="W15" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X15" s="65"/>
       <c r="Y15" s="65"/>
-      <c r="Z15" s="65"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="E16" s="23">
         <v>2030</v>
       </c>
@@ -5230,37 +5255,34 @@
       <c r="I16" s="27">
         <v>0.85</v>
       </c>
-      <c r="J16" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K16" s="27"/>
       <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="R16" s="65" t="s">
+      <c r="O16" s="27"/>
+      <c r="Q16" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65" t="s">
+        <v>152</v>
+      </c>
       <c r="T16" s="65" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="U16" s="65" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="V16" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W16" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X16" s="60" t="s">
+      <c r="W16" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="Y16" s="65"/>
-      <c r="Z16" s="65" t="s">
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
@@ -5274,35 +5296,32 @@
       <c r="I17" s="27">
         <v>0.85</v>
       </c>
-      <c r="J17" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K17" s="27"/>
       <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="R17" s="65" t="s">
+      <c r="O17" s="27"/>
+      <c r="Q17" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65" t="s">
+        <v>154</v>
+      </c>
       <c r="T17" s="65" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="U17" s="65" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="V17" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W17" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X17" s="60" t="s">
+      <c r="W17" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X17" s="65"/>
       <c r="Y17" s="65"/>
-      <c r="Z17" s="65"/>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
@@ -5316,37 +5335,34 @@
       <c r="I18" s="27">
         <v>0.85</v>
       </c>
-      <c r="J18" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K18" s="27"/>
       <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="R18" s="65" t="s">
+      <c r="O18" s="27"/>
+      <c r="Q18" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65" t="s">
+        <v>155</v>
+      </c>
       <c r="T18" s="65" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="U18" s="65" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="V18" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W18" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X18" s="60" t="s">
+      <c r="W18" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X18" s="65"/>
       <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="str">
-        <f>T15</f>
+        <f>S15</f>
         <v>ELCTNOIL01</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -5367,50 +5383,47 @@
       <c r="I19" s="27">
         <v>0.85</v>
       </c>
-      <c r="J19" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="K19" s="23">
+      <c r="J19" s="23">
         <v>250</v>
       </c>
+      <c r="K19" s="27">
+        <v>20</v>
+      </c>
       <c r="L19" s="27">
-        <v>20</v>
-      </c>
-      <c r="M19" s="27">
         <v>0.2</v>
       </c>
+      <c r="M19" s="23">
+        <v>40</v>
+      </c>
       <c r="N19" s="23">
-        <v>40</v>
-      </c>
-      <c r="O19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P19" s="27">
+      <c r="O19" s="27">
         <v>1</v>
       </c>
-      <c r="R19" s="65" t="s">
+      <c r="Q19" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65" t="s">
+        <v>156</v>
+      </c>
       <c r="T19" s="65" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="U19" s="65" t="s">
-        <v>160</v>
+        <v>52</v>
       </c>
       <c r="V19" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W19" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X19" s="60" t="s">
+      <c r="W19" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X19" s="65"/>
       <c r="Y19" s="65"/>
-      <c r="Z19" s="65"/>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E20" s="23">
         <v>2025</v>
       </c>
@@ -5423,35 +5436,32 @@
       <c r="I20" s="27">
         <v>0.85</v>
       </c>
-      <c r="J20" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K20" s="27"/>
       <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="R20" s="65" t="s">
+      <c r="O20" s="27"/>
+      <c r="Q20" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65" t="s">
+        <v>157</v>
+      </c>
       <c r="T20" s="65" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="U20" s="65" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="V20" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W20" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X20" s="60" t="s">
+      <c r="W20" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X20" s="65"/>
       <c r="Y20" s="65"/>
-      <c r="Z20" s="65"/>
-    </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E21" s="23">
         <v>2030</v>
       </c>
@@ -5464,35 +5474,32 @@
       <c r="I21" s="27">
         <v>0.85</v>
       </c>
-      <c r="J21" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K21" s="27"/>
       <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="R21" s="65" t="s">
+      <c r="O21" s="27"/>
+      <c r="Q21" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S21" s="65"/>
-      <c r="T21" s="23" t="s">
+      <c r="R21" s="65"/>
+      <c r="S21" s="23" t="s">
         <v>193</v>
       </c>
+      <c r="T21" s="65" t="s">
+        <v>194</v>
+      </c>
       <c r="U21" s="65" t="s">
-        <v>194</v>
+        <v>52</v>
       </c>
       <c r="V21" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W21" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X21" s="60" t="s">
+      <c r="W21" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X21" s="65"/>
       <c r="Y21" s="65"/>
-      <c r="Z21" s="65"/>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E22" s="23">
         <v>2035</v>
       </c>
@@ -5505,35 +5512,32 @@
       <c r="I22" s="27">
         <v>0.85</v>
       </c>
-      <c r="J22" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K22" s="27"/>
       <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="R22" s="65" t="s">
+      <c r="O22" s="27"/>
+      <c r="Q22" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S22" s="65"/>
-      <c r="T22" s="23" t="s">
+      <c r="R22" s="65"/>
+      <c r="S22" s="23" t="s">
         <v>195</v>
       </c>
+      <c r="T22" s="65" t="s">
+        <v>196</v>
+      </c>
       <c r="U22" s="65" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="V22" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W22" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X22" s="60" t="s">
+      <c r="W22" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X22" s="65"/>
       <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-    </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E23" s="23">
         <v>2040</v>
       </c>
@@ -5546,37 +5550,34 @@
       <c r="I23" s="27">
         <v>0.85</v>
       </c>
-      <c r="J23" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K23" s="27"/>
       <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="R23" s="65" t="s">
+      <c r="O23" s="27"/>
+      <c r="Q23" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="S23" s="65"/>
-      <c r="T23" s="23" t="s">
+      <c r="R23" s="65"/>
+      <c r="S23" s="23" t="s">
         <v>197</v>
       </c>
+      <c r="T23" s="65" t="s">
+        <v>198</v>
+      </c>
       <c r="U23" s="65" t="s">
-        <v>198</v>
+        <v>52</v>
       </c>
       <c r="V23" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="W23" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="X23" s="60" t="s">
+      <c r="W23" s="60" t="s">
         <v>202</v>
       </c>
+      <c r="X23" s="65"/>
       <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-    </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="str">
-        <f>T16</f>
+        <f>S16</f>
         <v>ELCTNGAS01</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -5597,32 +5598,29 @@
       <c r="I24" s="27">
         <v>0.85</v>
       </c>
-      <c r="J24" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="K24" s="23">
+      <c r="J24" s="23">
         <v>1100</v>
       </c>
+      <c r="K24" s="27">
+        <v>30</v>
+      </c>
       <c r="L24" s="27">
-        <v>30</v>
-      </c>
-      <c r="M24" s="27">
         <v>0.35</v>
       </c>
+      <c r="M24" s="23">
+        <v>40</v>
+      </c>
       <c r="N24" s="23">
-        <v>40</v>
-      </c>
-      <c r="O24" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P24" s="27">
+      <c r="O24" s="27">
         <v>1</v>
       </c>
+      <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
-      <c r="Y24" s="65"/>
-    </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="X24" s="65"/>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E25" s="23">
         <v>2030</v>
       </c>
@@ -5635,23 +5633,20 @@
       <c r="I25" s="27">
         <v>0.85</v>
       </c>
-      <c r="J25" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K25" s="27"/>
       <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="P25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="65"/>
       <c r="S25" s="65"/>
       <c r="T25" s="65"/>
       <c r="U25" s="65"/>
       <c r="V25" s="65"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="65"/>
       <c r="Y25" s="65"/>
-      <c r="Z25" s="65"/>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E26" s="23">
         <v>2035</v>
       </c>
@@ -5664,18 +5659,15 @@
       <c r="I26" s="27">
         <v>0.85</v>
       </c>
-      <c r="J26" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K26" s="27"/>
       <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="P26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
+      <c r="X26" s="65"/>
       <c r="Y26" s="65"/>
-      <c r="Z26" s="65"/>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E27" s="23">
         <v>2040</v>
       </c>
@@ -5688,18 +5680,15 @@
       <c r="I27" s="27">
         <v>0.85</v>
       </c>
-      <c r="J27" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K27" s="27"/>
       <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="P27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="65"/>
-      <c r="S27" s="65"/>
+      <c r="X27" s="65"/>
       <c r="Y27" s="65"/>
-      <c r="Z27" s="65"/>
-    </row>
-    <row r="28" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="23">
         <v>2045</v>
       </c>
@@ -5712,20 +5701,17 @@
       <c r="I28" s="27">
         <v>0.85</v>
       </c>
-      <c r="J28" s="84" t="s">
-        <v>283</v>
-      </c>
+      <c r="K28" s="27"/>
       <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="P28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="65"/>
-      <c r="S28" s="65"/>
+      <c r="X28" s="65"/>
       <c r="Y28" s="65"/>
-      <c r="Z28" s="65"/>
-    </row>
-    <row r="29" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="23" t="str">
-        <f>T17</f>
+        <f>S17</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5746,33 +5732,30 @@
       <c r="I29" s="27">
         <v>0.6</v>
       </c>
-      <c r="J29" s="84" t="s">
-        <v>283</v>
+      <c r="J29" s="23">
+        <v>2500</v>
       </c>
       <c r="K29" s="23">
-        <v>2500</v>
-      </c>
-      <c r="L29" s="23">
         <v>30</v>
       </c>
-      <c r="M29" s="27">
+      <c r="L29" s="27">
         <v>0.35</v>
       </c>
+      <c r="M29" s="23">
+        <v>25</v>
+      </c>
       <c r="N29" s="23">
-        <v>25</v>
-      </c>
-      <c r="O29" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P29" s="27">
+      <c r="O29" s="27">
         <v>1</v>
       </c>
+      <c r="Q29" s="65"/>
       <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
+      <c r="X29" s="65"/>
       <c r="Y29" s="65"/>
-      <c r="Z29" s="65"/>
-    </row>
-    <row r="30" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="23">
         <v>2030</v>
       </c>
@@ -5785,22 +5768,19 @@
       <c r="I30" s="27">
         <v>0.6</v>
       </c>
-      <c r="J30" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M30" s="27"/>
-      <c r="P30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="65"/>
       <c r="S30" s="65"/>
       <c r="T30" s="65"/>
       <c r="U30" s="65"/>
       <c r="V30" s="65"/>
-      <c r="W30" s="65"/>
-      <c r="X30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="65"/>
       <c r="Y30" s="65"/>
-      <c r="Z30" s="65"/>
-    </row>
-    <row r="31" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="23">
         <v>2035</v>
       </c>
@@ -5813,22 +5793,19 @@
       <c r="I31" s="27">
         <v>0.6</v>
       </c>
-      <c r="J31" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M31" s="27"/>
-      <c r="P31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="Q31" s="65"/>
       <c r="R31" s="65"/>
       <c r="S31" s="65"/>
       <c r="T31" s="65"/>
       <c r="U31" s="65"/>
       <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="65"/>
       <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
-    </row>
-    <row r="32" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="23">
         <v>2040</v>
       </c>
@@ -5841,24 +5818,21 @@
       <c r="I32" s="27">
         <v>0.6</v>
       </c>
-      <c r="J32" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M32" s="27"/>
-      <c r="P32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="Q32" s="65"/>
       <c r="R32" s="65"/>
       <c r="S32" s="65"/>
       <c r="T32" s="65"/>
       <c r="U32" s="65"/>
       <c r="V32" s="65"/>
-      <c r="W32" s="65"/>
-      <c r="X32" s="60"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="65"/>
       <c r="Y32" s="65"/>
-      <c r="Z32" s="65"/>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" s="23" t="str">
-        <f>T18</f>
+        <f>S18</f>
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -5879,32 +5853,29 @@
       <c r="I33" s="27">
         <v>0.5</v>
       </c>
-      <c r="J33" s="84" t="s">
-        <v>283</v>
+      <c r="J33" s="23">
+        <v>3000</v>
       </c>
       <c r="K33" s="23">
-        <v>3000</v>
-      </c>
-      <c r="L33" s="23">
         <v>35</v>
       </c>
-      <c r="M33" s="27">
+      <c r="L33" s="27">
         <v>2</v>
       </c>
+      <c r="M33" s="23">
+        <v>50</v>
+      </c>
       <c r="N33" s="23">
-        <v>50</v>
-      </c>
-      <c r="O33" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P33" s="27">
+      <c r="O33" s="27">
         <v>0.35</v>
       </c>
-      <c r="R33" s="65"/>
+      <c r="Q33" s="65"/>
+      <c r="X33" s="65"/>
       <c r="Y33" s="65"/>
-      <c r="Z33" s="65"/>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E34" s="23">
         <v>2025</v>
       </c>
@@ -5917,21 +5888,18 @@
       <c r="I34" s="27">
         <v>0.5</v>
       </c>
-      <c r="J34" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="R34" s="65"/>
-      <c r="T34" s="23"/>
+      <c r="L34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="Q34" s="65"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="65"/>
       <c r="U34" s="65"/>
       <c r="V34" s="65"/>
-      <c r="W34" s="65"/>
-      <c r="X34" s="60"/>
+      <c r="W34" s="60"/>
+      <c r="X34" s="65"/>
       <c r="Y34" s="65"/>
-      <c r="Z34" s="65"/>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E35" s="23">
         <v>2030</v>
       </c>
@@ -5944,21 +5912,18 @@
       <c r="I35" s="27">
         <v>0.5</v>
       </c>
-      <c r="J35" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="R35" s="65"/>
-      <c r="T35" s="23"/>
+      <c r="L35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="Q35" s="65"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="65"/>
       <c r="U35" s="65"/>
       <c r="V35" s="65"/>
-      <c r="W35" s="65"/>
-      <c r="X35" s="60"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="65"/>
       <c r="Y35" s="65"/>
-      <c r="Z35" s="65"/>
-    </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E36" s="23">
         <v>2035</v>
       </c>
@@ -5971,21 +5936,18 @@
       <c r="I36" s="27">
         <v>0.5</v>
       </c>
-      <c r="J36" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="R36" s="65"/>
-      <c r="T36" s="23"/>
+      <c r="L36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="Q36" s="65"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="65"/>
       <c r="U36" s="65"/>
       <c r="V36" s="65"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="60"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="65"/>
       <c r="Y36" s="65"/>
-      <c r="Z36" s="65"/>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E37" s="23">
         <v>2040</v>
       </c>
@@ -5998,23 +5960,20 @@
       <c r="I37" s="27">
         <v>0.5</v>
       </c>
-      <c r="J37" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="R37" s="65"/>
-      <c r="T37" s="23"/>
+      <c r="L37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="Q37" s="65"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="65"/>
       <c r="U37" s="65"/>
       <c r="V37" s="65"/>
-      <c r="W37" s="65"/>
-      <c r="X37" s="60"/>
+      <c r="W37" s="60"/>
+      <c r="X37" s="65"/>
       <c r="Y37" s="65"/>
-      <c r="Z37" s="65"/>
-    </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" s="23" t="str">
-        <f>T19</f>
+        <f>S19</f>
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
@@ -6035,28 +5994,25 @@
       <c r="I38" s="27">
         <v>0.35</v>
       </c>
-      <c r="J38" s="84" t="s">
-        <v>283</v>
+      <c r="J38" s="23">
+        <v>1340</v>
       </c>
       <c r="K38" s="23">
-        <v>1340</v>
-      </c>
-      <c r="L38" s="23">
         <v>26.7</v>
       </c>
-      <c r="M38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="23">
+        <v>25</v>
+      </c>
       <c r="N38" s="23">
-        <v>25</v>
-      </c>
-      <c r="O38" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P38" s="27">
+      <c r="O38" s="27">
         <v>0.3</v>
       </c>
-      <c r="R38" s="65"/>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Q38" s="65"/>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E39" s="23">
         <v>2030</v>
       </c>
@@ -6069,26 +6025,23 @@
       <c r="I39" s="27">
         <v>0.35</v>
       </c>
-      <c r="J39" s="84" t="s">
-        <v>283</v>
+      <c r="J39" s="23">
+        <f>J38*0.95</f>
+        <v>1273</v>
       </c>
       <c r="K39" s="23">
-        <f>K38*0.95</f>
-        <v>1273</v>
-      </c>
-      <c r="L39" s="23">
-        <f t="shared" ref="L39:L40" si="0">L38*0.95</f>
+        <f t="shared" ref="K39:K40" si="0">K38*0.95</f>
         <v>25.364999999999998</v>
       </c>
-      <c r="P39" s="27"/>
-      <c r="R39" s="65"/>
-      <c r="T39" s="23"/>
+      <c r="O39" s="27"/>
+      <c r="Q39" s="65"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="65"/>
       <c r="U39" s="65"/>
       <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="60"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W39" s="60"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E40" s="23">
         <v>2035</v>
       </c>
@@ -6101,26 +6054,23 @@
       <c r="I40" s="27">
         <v>0.35</v>
       </c>
-      <c r="J40" s="84" t="s">
-        <v>283</v>
+      <c r="J40" s="23">
+        <f>J39*0.95</f>
+        <v>1209.3499999999999</v>
       </c>
       <c r="K40" s="23">
-        <f>K39*0.95</f>
-        <v>1209.3499999999999</v>
-      </c>
-      <c r="L40" s="23">
         <f t="shared" si="0"/>
         <v>24.096749999999997</v>
       </c>
-      <c r="P40" s="27"/>
-      <c r="R40" s="65"/>
-      <c r="T40" s="23"/>
+      <c r="O40" s="27"/>
+      <c r="Q40" s="65"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="65"/>
       <c r="U40" s="65"/>
       <c r="V40" s="65"/>
-      <c r="W40" s="65"/>
-      <c r="X40" s="60"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W40" s="60"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E41" s="23">
         <v>2040</v>
       </c>
@@ -6133,20 +6083,17 @@
       <c r="I41" s="27">
         <v>0.35</v>
       </c>
-      <c r="J41" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="P41" s="27"/>
-      <c r="R41" s="65"/>
-      <c r="T41" s="23"/>
+      <c r="O41" s="27"/>
+      <c r="Q41" s="65"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="65"/>
       <c r="U41" s="65"/>
       <c r="V41" s="65"/>
-      <c r="W41" s="65"/>
-      <c r="X41" s="60"/>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W41" s="60"/>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" s="23" t="str">
-        <f>T20</f>
+        <f>S20</f>
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -6167,30 +6114,27 @@
       <c r="I42" s="27">
         <v>0.2</v>
       </c>
-      <c r="J42" s="84" t="s">
-        <v>283</v>
+      <c r="J42" s="23">
+        <v>550</v>
       </c>
       <c r="K42" s="23">
-        <v>550</v>
-      </c>
-      <c r="L42" s="23">
         <v>7</v>
       </c>
-      <c r="M42" s="27">
+      <c r="L42" s="27">
         <v>0</v>
       </c>
+      <c r="M42" s="23">
+        <v>25</v>
+      </c>
       <c r="N42" s="23">
-        <v>25</v>
-      </c>
-      <c r="O42" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P42" s="27">
+      <c r="O42" s="27">
         <v>0.2</v>
       </c>
-      <c r="R42" s="65"/>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Q42" s="65"/>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E43" s="23">
         <v>2025</v>
       </c>
@@ -6203,19 +6147,16 @@
       <c r="I43" s="27">
         <v>0.2</v>
       </c>
-      <c r="J43" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="R43" s="65"/>
-      <c r="T43" s="23"/>
+      <c r="L43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="Q43" s="65"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="65"/>
       <c r="U43" s="65"/>
       <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="60"/>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W43" s="60"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E44" s="23">
         <v>2030</v>
       </c>
@@ -6228,19 +6169,16 @@
       <c r="I44" s="27">
         <v>0.2</v>
       </c>
-      <c r="J44" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="R44" s="65"/>
-      <c r="T44" s="23"/>
+      <c r="L44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="Q44" s="65"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="65"/>
       <c r="U44" s="65"/>
       <c r="V44" s="65"/>
-      <c r="W44" s="65"/>
-      <c r="X44" s="60"/>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W44" s="60"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E45" s="23">
         <v>2035</v>
       </c>
@@ -6253,19 +6191,16 @@
       <c r="I45" s="27">
         <v>0.2</v>
       </c>
-      <c r="J45" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M45" s="27"/>
-      <c r="P45" s="27"/>
-      <c r="R45" s="65"/>
-      <c r="T45" s="23"/>
+      <c r="L45" s="27"/>
+      <c r="O45" s="27"/>
+      <c r="Q45" s="65"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="65"/>
       <c r="U45" s="65"/>
       <c r="V45" s="65"/>
-      <c r="W45" s="65"/>
-      <c r="X45" s="60"/>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W45" s="60"/>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E46" s="23">
         <v>2040</v>
       </c>
@@ -6278,21 +6213,18 @@
       <c r="I46" s="27">
         <v>0.2</v>
       </c>
-      <c r="J46" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="R46" s="65"/>
-      <c r="T46" s="23"/>
+      <c r="L46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="Q46" s="65"/>
+      <c r="S46" s="23"/>
+      <c r="T46" s="65"/>
       <c r="U46" s="65"/>
       <c r="V46" s="65"/>
-      <c r="W46" s="65"/>
-      <c r="X46" s="60"/>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="W46" s="60"/>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" s="23" t="str">
-        <f>T22</f>
+        <f>S22</f>
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -6313,31 +6245,28 @@
       <c r="I47" s="27">
         <v>0.25</v>
       </c>
-      <c r="J47" s="84" t="s">
-        <v>283</v>
+      <c r="J47" s="23">
+        <v>1090</v>
       </c>
       <c r="K47" s="23">
-        <v>1090</v>
-      </c>
-      <c r="L47" s="23">
-        <f>K47*0.02</f>
+        <f>J47*0.02</f>
         <v>21.8</v>
       </c>
-      <c r="M47" s="27">
+      <c r="L47" s="27">
         <v>0</v>
       </c>
+      <c r="M47" s="23">
+        <v>25</v>
+      </c>
       <c r="N47" s="23">
-        <v>25</v>
-      </c>
-      <c r="O47" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="P47" s="27">
+      <c r="O47" s="27">
         <v>0.5</v>
       </c>
-      <c r="R47" s="65"/>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Q47" s="65"/>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E48" s="23">
         <v>2025</v>
       </c>
@@ -6350,14 +6279,11 @@
       <c r="I48" s="27">
         <v>0.25</v>
       </c>
-      <c r="J48" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="R48" s="65"/>
-    </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="Q48" s="65"/>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E49" s="23">
         <v>2030</v>
       </c>
@@ -6370,14 +6296,11 @@
       <c r="I49" s="27">
         <v>0.25</v>
       </c>
-      <c r="J49" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="R49" s="65"/>
-    </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L49" s="27"/>
+      <c r="O49" s="27"/>
+      <c r="Q49" s="65"/>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E50" s="23">
         <v>2035</v>
       </c>
@@ -6390,14 +6313,11 @@
       <c r="I50" s="27">
         <v>0.25</v>
       </c>
-      <c r="J50" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="R50" s="65"/>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L50" s="27"/>
+      <c r="O50" s="27"/>
+      <c r="Q50" s="65"/>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E51" s="23">
         <v>2040</v>
       </c>
@@ -6410,16 +6330,13 @@
       <c r="I51" s="27">
         <v>0.25</v>
       </c>
-      <c r="J51" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="R51" s="65"/>
-    </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L51" s="27"/>
+      <c r="O51" s="27"/>
+      <c r="Q51" s="65"/>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B52" s="23" t="str">
-        <f>T23</f>
+        <f>S23</f>
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
@@ -6440,30 +6357,27 @@
       <c r="I52" s="23">
         <v>0.8</v>
       </c>
-      <c r="J52" s="84" t="s">
-        <v>283</v>
+      <c r="J52" s="23">
+        <v>1990</v>
       </c>
       <c r="K52" s="23">
-        <v>1990</v>
-      </c>
-      <c r="L52" s="23">
         <v>39.799999999999997</v>
       </c>
-      <c r="M52" s="27">
+      <c r="L52" s="27">
         <v>2</v>
       </c>
+      <c r="M52" s="23">
+        <v>40</v>
+      </c>
       <c r="N52" s="23">
-        <v>40</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O52" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P52" s="23">
         <v>0.45</v>
       </c>
-      <c r="R52" s="65"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="Q52" s="65"/>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E53" s="23">
         <v>2035</v>
       </c>
@@ -6476,13 +6390,10 @@
       <c r="I53" s="23">
         <v>0.8</v>
       </c>
-      <c r="J53" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M53" s="27"/>
-      <c r="R53" s="65"/>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L53" s="27"/>
+      <c r="Q53" s="65"/>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E54" s="23">
         <v>2040</v>
       </c>
@@ -6495,13 +6406,10 @@
       <c r="I54" s="23">
         <v>0.8</v>
       </c>
-      <c r="J54" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="M54" s="27"/>
-      <c r="R54" s="65"/>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L54" s="27"/>
+      <c r="Q54" s="65"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B55" s="23" t="s">
         <v>193</v>
       </c>
@@ -6523,29 +6431,26 @@
       <c r="I55" s="23">
         <v>0.15</v>
       </c>
-      <c r="J55" s="84" t="s">
-        <v>283</v>
+      <c r="J55" s="23">
+        <v>490</v>
       </c>
       <c r="K55" s="23">
-        <v>490</v>
-      </c>
-      <c r="L55" s="23">
         <v>9.8000000000000007</v>
       </c>
+      <c r="M55" s="23">
+        <v>15</v>
+      </c>
       <c r="N55" s="23">
-        <v>15</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="O55" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="P55" s="23">
         <v>0.5</v>
       </c>
-      <c r="R55" s="65"/>
+      <c r="Q55" s="65"/>
+      <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="23"/>
-    </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E56" s="23">
         <v>2030</v>
       </c>
@@ -6558,11 +6463,8 @@
       <c r="I56" s="23">
         <v>0.15</v>
       </c>
-      <c r="J56" s="84" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E57" s="23">
         <v>2035</v>
       </c>
@@ -6575,11 +6477,8 @@
       <c r="I57" s="23">
         <v>0.15</v>
       </c>
-      <c r="J57" s="84" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
       <c r="E58" s="23">
         <v>2040</v>
       </c>
@@ -6591,9 +6490,6 @@
       </c>
       <c r="I58" s="23">
         <v>0.15</v>
-      </c>
-      <c r="J58" s="84" t="s">
-        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -7759,8 +7655,18 @@
         <v>22.5</v>
       </c>
       <c r="I11" s="43"/>
-      <c r="K11" s="2"/>
+      <c r="K11" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="N11" s="21"/>
+      <c r="O11" s="65" t="str">
+        <f>$E$2</f>
+        <v>PJ</v>
+      </c>
       <c r="U11" s="23">
         <v>22.5</v>
       </c>
@@ -7782,7 +7688,18 @@
         <v>23.4</v>
       </c>
       <c r="I12" s="43"/>
+      <c r="K12" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="N12" s="21"/>
+      <c r="O12" s="65" t="str">
+        <f t="shared" ref="O12:O21" si="0">$E$2</f>
+        <v>PJ</v>
+      </c>
       <c r="U12" s="23">
         <v>23.4</v>
       </c>
@@ -7804,7 +7721,18 @@
         <v>15.4</v>
       </c>
       <c r="I13" s="43"/>
+      <c r="K13" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="N13" s="21"/>
+      <c r="O13" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="U13" s="23">
         <v>15.4</v>
       </c>
@@ -7826,7 +7754,18 @@
         <v>20.8</v>
       </c>
       <c r="I14" s="30"/>
+      <c r="K14" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="N14" s="21"/>
+      <c r="O14" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="U14" s="23">
         <v>20.8</v>
       </c>
@@ -7847,7 +7786,18 @@
         <v>12.6</v>
       </c>
       <c r="I15" s="30"/>
+      <c r="K15" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="N15" s="21"/>
+      <c r="O15" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="U15" s="23">
         <v>12.6</v>
       </c>
@@ -7869,6 +7819,17 @@
         <v>13.5</v>
       </c>
       <c r="I16" s="43"/>
+      <c r="K16" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O16" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="U16" s="23">
         <v>13.5</v>
       </c>
@@ -7886,6 +7847,17 @@
       <c r="H17" s="23">
         <v>14.5</v>
       </c>
+      <c r="K17" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="O17" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
       <c r="U17" s="23">
         <v>14.5</v>
       </c>
@@ -7906,6 +7878,17 @@
       <c r="I18">
         <v>8.91</v>
       </c>
+      <c r="K18" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M18" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="O18" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
@@ -7923,6 +7906,17 @@
       <c r="I19" s="80">
         <v>2.6490239999999998</v>
       </c>
+      <c r="K19" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="O19" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
@@ -7939,6 +7933,17 @@
       </c>
       <c r="I20">
         <v>14.19</v>
+      </c>
+      <c r="K20" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="O20" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
@@ -7957,6 +7962,17 @@
       </c>
       <c r="I21">
         <v>14.19</v>
+      </c>
+      <c r="K21" s="65" t="str">
+        <f>[2]EB1!$B$6</f>
+        <v>IMP</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" s="65" t="str">
+        <f t="shared" si="0"/>
+        <v>PJ</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EA911B-5167-403C-BD8A-2D1C3439550F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1206A7-DCAA-40DE-9E16-A99A308018AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="12" r:id="rId1"/>
@@ -28,19 +28,6 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -3158,7 +3145,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3217,7 +3204,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="17"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="17" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="32" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -4724,52 +4710,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A4B651-1072-492F-9C98-6FB421C5AC2C}">
   <dimension ref="A1:Y58"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="23" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="23" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" style="23" customWidth="1"/>
     <col min="13" max="13" width="7" style="23" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5546875" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" customWidth="1"/>
+    <col min="24" max="24" width="12.6640625" customWidth="1"/>
+    <col min="25" max="25" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-    </row>
-    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+    </row>
+    <row r="3" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -4792,7 +4778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>49</v>
       </c>
@@ -4814,49 +4800,49 @@
       <c r="H4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="59" t="s">
+      <c r="Q4" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="Q5" s="61" t="s">
+      <c r="R4" s="58"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="59"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q5" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="62" t="s">
+      <c r="R5" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="S5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="T5" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="61" t="s">
+      <c r="V5" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="61" t="s">
+      <c r="W5" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="61" t="s">
+      <c r="X5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="61" t="s">
+      <c r="Y5" s="60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="29" t="s">
+    <row r="6" spans="1:25" ht="32.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="28" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -4875,37 +4861,37 @@
         <v>191</v>
       </c>
       <c r="H6" s="8"/>
-      <c r="I6" s="35"/>
-      <c r="Q6" s="63" t="s">
+      <c r="I6" s="34"/>
+      <c r="Q6" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="R6" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="S6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="T6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="U6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="63" t="s">
+      <c r="V6" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="63" t="s">
+      <c r="W6" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="63" t="s">
+      <c r="X6" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" s="63" t="s">
+      <c r="Y6" s="62" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
+    <row r="7" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="27" t="s">
         <v>65</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -4924,7 +4910,7 @@
         <v>192</v>
       </c>
       <c r="H7" s="9"/>
-      <c r="I7" s="32"/>
+      <c r="I7" s="31"/>
       <c r="Q7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
@@ -4934,34 +4920,33 @@
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="E10" s="6" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="24"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="5"/>
-      <c r="Q10" s="59" t="s">
+      <c r="Q10" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="59"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="R10" s="58"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="59"/>
+      <c r="U10" s="59"/>
+      <c r="V10" s="59"/>
+      <c r="W10" s="59"/>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="59"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -5004,36 +4989,36 @@
       <c r="O11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="61" t="s">
+      <c r="P11" s="24"/>
+      <c r="Q11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="R11" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="S11" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="T11" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="U11" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="V11" s="61" t="s">
+      <c r="V11" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="W11" s="61" t="s">
+      <c r="W11" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="X11" s="61" t="s">
+      <c r="X11" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="Y11" s="61" t="s">
+      <c r="Y11" s="60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -5072,35 +5057,35 @@
       <c r="O12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="Q12" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="R12" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="S12" s="64" t="s">
+      <c r="S12" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="T12" s="64" t="s">
+      <c r="T12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="U12" s="64" t="s">
+      <c r="U12" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="64" t="s">
+      <c r="V12" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="64" t="s">
+      <c r="W12" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="X12" s="64" t="s">
+      <c r="X12" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="Y12" s="64" t="s">
+      <c r="Y12" s="63" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>78</v>
       </c>
@@ -5127,19 +5112,19 @@
         <v>80</v>
       </c>
       <c r="O13" s="19"/>
-      <c r="Q13" s="63" t="s">
+      <c r="Q13" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="63"/>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="63"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="62"/>
+      <c r="W13" s="62"/>
+      <c r="X13" s="62"/>
+      <c r="Y13" s="62"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="23" t="str">
         <f>S14</f>
         <v>ELCTNCOA01</v>
@@ -5150,25 +5135,25 @@
       <c r="D14" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="25">
         <v>2023</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="26">
         <v>0.42</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="26">
         <v>1.32</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="26">
         <v>0.85</v>
       </c>
       <c r="J14" s="23">
         <v>1650</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="26">
         <v>30</v>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="26">
         <v>0.4</v>
       </c>
       <c r="M14" s="23">
@@ -5177,192 +5162,106 @@
       <c r="N14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="26">
         <v>1</v>
       </c>
-      <c r="Q14" s="65" t="s">
+      <c r="Q14" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65" t="s">
+      <c r="R14" s="64"/>
+      <c r="S14" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="T14" s="65" t="s">
+      <c r="T14" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="U14" s="65" t="s">
+      <c r="U14" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="V14" s="65" t="s">
+      <c r="V14" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="W14" s="60" t="s">
+      <c r="W14" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E15" s="23">
         <v>2025</v>
       </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="27">
+      <c r="F15" s="25"/>
+      <c r="G15" s="26">
         <v>0.42</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="26">
         <v>1.32</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="26">
         <v>0.85</v>
       </c>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="Q15" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R15" s="65"/>
-      <c r="S15" s="65" t="s">
-        <v>153</v>
-      </c>
-      <c r="T15" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="U15" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V15" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W15" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="65"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="O15" s="26"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E16" s="23">
         <v>2030</v>
       </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="27">
+      <c r="F16" s="25"/>
+      <c r="G16" s="26">
         <v>0.42</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="26">
         <v>1.44</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="26">
         <v>0.85</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="Q16" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="T16" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="U16" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V16" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W16" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="65" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="O16" s="26"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E17" s="23">
         <v>2035</v>
       </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27">
+      <c r="F17" s="25"/>
+      <c r="G17" s="26">
         <v>0.42</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="26">
         <v>1.44</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="26">
         <v>0.85</v>
       </c>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="Q17" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="T17" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="U17" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V17" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W17" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="65"/>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="O17" s="26"/>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E18" s="23">
         <v>2040</v>
       </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27">
+      <c r="F18" s="25"/>
+      <c r="G18" s="26">
         <v>0.42</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="26">
         <v>1.44</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="26">
         <v>0.85</v>
       </c>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="Q18" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="T18" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="U18" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V18" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W18" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="O18" s="26"/>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="str">
-        <f>S15</f>
+        <f>S19</f>
         <v>ELCTNOIL01</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -5374,22 +5273,22 @@
       <c r="F19" s="23">
         <v>2023</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="26">
         <v>0.3</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="26">
         <v>0.52139999999999997</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="26">
         <v>0.85</v>
       </c>
       <c r="J19" s="23">
         <v>250</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="26">
         <v>20</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="26">
         <v>0.2</v>
       </c>
       <c r="M19" s="23">
@@ -5398,186 +5297,102 @@
       <c r="N19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="26">
         <v>1</v>
       </c>
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="T19" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="U19" s="65" t="s">
+      <c r="R19" s="64"/>
+      <c r="S19" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="T19" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="U19" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="V19" s="65" t="s">
+      <c r="V19" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="60" t="s">
+      <c r="W19" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="X19" s="65"/>
-      <c r="Y19" s="65"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E20" s="23">
         <v>2025</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="26">
         <v>0.3</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="26">
         <v>0.52139999999999997</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="26">
         <v>0.85</v>
       </c>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="Q20" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="T20" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="U20" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V20" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W20" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X20" s="65"/>
-      <c r="Y20" s="65"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="O20" s="26"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E21" s="23">
         <v>2030</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="26">
         <v>0.3</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="26">
         <v>0.52139999999999997</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <v>0.85</v>
       </c>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="Q21" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R21" s="65"/>
-      <c r="S21" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="T21" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="U21" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V21" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W21" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="O21" s="26"/>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E22" s="23">
         <v>2035</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="26">
         <v>0.3</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="26">
         <v>0.52139999999999997</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="26">
         <v>0.85</v>
       </c>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="Q22" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R22" s="65"/>
-      <c r="S22" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="T22" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="U22" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V22" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W22" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="O22" s="26"/>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E23" s="23">
         <v>2040</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="26">
         <v>0.3</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="26">
         <v>0.52139999999999997</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="26">
         <v>0.85</v>
       </c>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="Q23" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="R23" s="65"/>
-      <c r="S23" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="T23" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="U23" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="V23" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="W23" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="O23" s="26"/>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" s="23" t="str">
-        <f>S16</f>
+        <f>S24</f>
         <v>ELCTNGAS01</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -5589,22 +5404,22 @@
       <c r="F24" s="23">
         <v>2027</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="26">
         <v>0.5</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="26">
         <v>0.9</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="26">
         <v>0.85</v>
       </c>
       <c r="J24" s="23">
         <v>1100</v>
       </c>
-      <c r="K24" s="27">
+      <c r="K24" s="26">
         <v>30</v>
       </c>
-      <c r="L24" s="27">
+      <c r="L24" s="26">
         <v>0.35</v>
       </c>
       <c r="M24" s="23">
@@ -5613,105 +5428,104 @@
       <c r="N24" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="26">
         <v>1</v>
       </c>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="65"/>
-      <c r="X24" s="65"/>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Q24" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R24" s="64"/>
+      <c r="S24" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="T24" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="U24" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V24" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W24" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="64" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E25" s="23">
         <v>2030</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="26">
         <v>0.5</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="26">
         <v>0.9</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="26">
         <v>0.85</v>
       </c>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="O25" s="26"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E26" s="23">
         <v>2035</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="26">
         <v>0.51</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="26">
         <v>0.9</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="26">
         <v>0.85</v>
       </c>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="O26" s="26"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E27" s="23">
         <v>2040</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="26">
         <v>0.52</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="26">
         <v>0.9</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="26">
         <v>0.85</v>
       </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="Q27" s="65"/>
-      <c r="R27" s="65"/>
-      <c r="X27" s="65"/>
-      <c r="Y27" s="65"/>
-    </row>
-    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="O27" s="26"/>
+    </row>
+    <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28" s="23">
         <v>2045</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="26">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="26">
         <v>0.9</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="26">
         <v>0.85</v>
       </c>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="65"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
-    </row>
-    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="O28" s="26"/>
+    </row>
+    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="23" t="str">
-        <f>S17</f>
+        <f>S29</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5723,13 +5537,13 @@
       <c r="F29" s="23">
         <v>2028</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="26">
         <v>0.35</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="26">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="26">
         <v>0.6</v>
       </c>
       <c r="J29" s="23">
@@ -5738,7 +5552,7 @@
       <c r="K29" s="23">
         <v>30</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="26">
         <v>0.35</v>
       </c>
       <c r="M29" s="23">
@@ -5747,92 +5561,88 @@
       <c r="N29" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="26">
         <v>1</v>
       </c>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
-    </row>
-    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q29" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R29" s="64"/>
+      <c r="S29" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="T29" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="U29" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V29" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W29" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+    </row>
+    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E30" s="23">
         <v>2030</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="26">
         <v>0.35</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="26">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="26">
         <v>0.6</v>
       </c>
-      <c r="L30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
-    </row>
-    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="X30" s="64"/>
+      <c r="Y30" s="64"/>
+    </row>
+    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E31" s="23">
         <v>2035</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="26">
         <v>0.35</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="26">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="26">
         <v>0.6</v>
       </c>
-      <c r="L31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-    </row>
-    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="64"/>
+    </row>
+    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E32" s="23">
         <v>2040</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="26">
         <v>0.35</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="26">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="26">
         <v>0.6</v>
       </c>
-      <c r="L32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="64"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" s="23" t="str">
-        <f>S18</f>
+        <f>S33</f>
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -5844,13 +5654,13 @@
       <c r="F33" s="23">
         <v>2023</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="26">
         <v>1</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="26">
         <v>1.3301000000000001</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="26">
         <v>0.5</v>
       </c>
       <c r="J33" s="23">
@@ -5859,7 +5669,7 @@
       <c r="K33" s="23">
         <v>35</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="26">
         <v>2</v>
       </c>
       <c r="M33" s="23">
@@ -5868,112 +5678,106 @@
       <c r="N33" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O33" s="27">
+      <c r="O33" s="26">
         <v>0.35</v>
       </c>
-      <c r="Q33" s="65"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Q33" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R33" s="64"/>
+      <c r="S33" s="64" t="s">
+        <v>155</v>
+      </c>
+      <c r="T33" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="U33" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V33" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W33" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E34" s="23">
         <v>2025</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="26">
         <v>1</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="26">
         <v>1.3351</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="26">
         <v>0.5</v>
       </c>
-      <c r="L34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="Q34" s="65"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="65"/>
-      <c r="U34" s="65"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="X34" s="64"/>
+      <c r="Y34" s="64"/>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E35" s="23">
         <v>2030</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="26">
         <v>1</v>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="26">
         <v>1.9951000000000001</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="26">
         <v>0.5</v>
       </c>
-      <c r="L35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="Q35" s="65"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="64"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E36" s="23">
         <v>2035</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="26">
         <v>1</v>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="26">
         <v>2.7111000000000001</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="26">
         <v>0.5</v>
       </c>
-      <c r="L36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="Q36" s="65"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="X36" s="64"/>
+      <c r="Y36" s="64"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E37" s="23">
         <v>2040</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="26">
         <v>1</v>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="26">
         <v>2.8811</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="26">
         <v>0.5</v>
       </c>
-      <c r="L37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="Q37" s="65"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="60"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="64"/>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" s="23" t="str">
-        <f>S19</f>
+        <f>S38</f>
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
@@ -5985,13 +5789,13 @@
       <c r="F38" s="23">
         <v>2026</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="26">
         <v>1</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="26">
         <v>0.15</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="26">
         <v>0.35</v>
       </c>
       <c r="J38" s="23">
@@ -6000,29 +5804,47 @@
       <c r="K38" s="23">
         <v>26.7</v>
       </c>
-      <c r="L38" s="27"/>
+      <c r="L38" s="26"/>
       <c r="M38" s="23">
         <v>25</v>
       </c>
       <c r="N38" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O38" s="27">
+      <c r="O38" s="26">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="65"/>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Q38" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="T38" s="64" t="s">
+        <v>160</v>
+      </c>
+      <c r="U38" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V38" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E39" s="23">
         <v>2030</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="26">
         <v>1</v>
       </c>
-      <c r="H39" s="27">
+      <c r="H39" s="26">
         <v>0.9</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="26">
         <v>0.35</v>
       </c>
       <c r="J39" s="23">
@@ -6033,25 +5855,19 @@
         <f t="shared" ref="K39:K40" si="0">K38*0.95</f>
         <v>25.364999999999998</v>
       </c>
-      <c r="O39" s="27"/>
-      <c r="Q39" s="65"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="60"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="O39" s="26"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E40" s="23">
         <v>2035</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="26">
         <v>1</v>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="26">
         <v>1.05</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="26">
         <v>0.35</v>
       </c>
       <c r="J40" s="23">
@@ -6062,38 +5878,26 @@
         <f t="shared" si="0"/>
         <v>24.096749999999997</v>
       </c>
-      <c r="O40" s="27"/>
-      <c r="Q40" s="65"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="65"/>
-      <c r="W40" s="60"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="O40" s="26"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E41" s="23">
         <v>2040</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="26">
         <v>1</v>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="26">
         <v>2.1</v>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="26">
         <v>0.35</v>
       </c>
-      <c r="O41" s="27"/>
-      <c r="Q41" s="65"/>
-      <c r="S41" s="23"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="65"/>
-      <c r="V41" s="65"/>
-      <c r="W41" s="60"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="O41" s="26"/>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="str">
-        <f>S20</f>
+        <f>S42</f>
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -6105,13 +5909,13 @@
       <c r="F42" s="23">
         <v>2022</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="26">
         <v>1</v>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="26">
         <v>0.44679999999999997</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="26">
         <v>0.2</v>
       </c>
       <c r="J42" s="23">
@@ -6120,7 +5924,7 @@
       <c r="K42" s="23">
         <v>7</v>
       </c>
-      <c r="L42" s="27">
+      <c r="L42" s="26">
         <v>0</v>
       </c>
       <c r="M42" s="23">
@@ -6129,102 +5933,102 @@
       <c r="N42" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O42" s="27">
+      <c r="O42" s="26">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="65"/>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Q42" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R42" s="64"/>
+      <c r="S42" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="T42" s="64" t="s">
+        <v>161</v>
+      </c>
+      <c r="U42" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V42" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W42" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E43" s="23">
         <v>2025</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="26">
         <v>1</v>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="26">
         <v>0.93679999999999997</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="26">
         <v>0.2</v>
       </c>
-      <c r="L43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="Q43" s="65"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="60"/>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L43" s="26"/>
+      <c r="O43" s="26"/>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E44" s="23">
         <v>2030</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="26">
         <v>1</v>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="26">
         <v>2.5268000000000002</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="26">
         <v>0.2</v>
       </c>
-      <c r="L44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="Q44" s="65"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="60"/>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L44" s="26"/>
+      <c r="O44" s="26"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E45" s="23">
         <v>2035</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="26">
         <v>1</v>
       </c>
-      <c r="H45" s="27">
+      <c r="H45" s="26">
         <v>3.0908000000000002</v>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="26">
         <v>0.2</v>
       </c>
-      <c r="L45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="Q45" s="65"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="60"/>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="L45" s="26"/>
+      <c r="O45" s="26"/>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E46" s="23">
         <v>2040</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="26">
         <v>1</v>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="26">
         <v>4.2907999999999999</v>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="26">
         <v>0.2</v>
       </c>
-      <c r="L46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="Q46" s="65"/>
+      <c r="L46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="Q46" s="64"/>
       <c r="S46" s="23"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="60"/>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="T46" s="64"/>
+      <c r="U46" s="64"/>
+      <c r="V46" s="64"/>
+      <c r="W46" s="59"/>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="str">
-        <f>S22</f>
+        <f>S52</f>
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -6236,13 +6040,13 @@
       <c r="F47" s="23">
         <v>2024</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="26">
         <v>1</v>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="26">
         <v>0.06</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="26">
         <v>0.25</v>
       </c>
       <c r="J47" s="23">
@@ -6252,7 +6056,7 @@
         <f>J47*0.02</f>
         <v>21.8</v>
       </c>
-      <c r="L47" s="27">
+      <c r="L47" s="26">
         <v>0</v>
       </c>
       <c r="M47" s="23">
@@ -6261,82 +6065,98 @@
       <c r="N47" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="O47" s="27">
+      <c r="O47" s="26">
         <v>0.5</v>
       </c>
-      <c r="Q47" s="65"/>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Q47" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R47" s="64"/>
+      <c r="S47" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="T47" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="U47" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V47" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W47" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E48" s="23">
         <v>2025</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="26">
         <v>1</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="26">
         <v>0.39</v>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="26">
         <v>0.25</v>
       </c>
-      <c r="L48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="Q48" s="65"/>
-    </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L48" s="26"/>
+      <c r="O48" s="26"/>
+    </row>
+    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E49" s="23">
         <v>2030</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G49" s="26">
         <v>1</v>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="26">
         <v>0.54</v>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="26">
         <v>0.25</v>
       </c>
-      <c r="L49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="Q49" s="65"/>
-    </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L49" s="26"/>
+      <c r="O49" s="26"/>
+    </row>
+    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E50" s="23">
         <v>2035</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="26">
         <v>1</v>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="26">
         <v>0.54</v>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="26">
         <v>0.25</v>
       </c>
-      <c r="L50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="Q50" s="65"/>
-    </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="Q50" s="64"/>
+    </row>
+    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E51" s="23">
         <v>2040</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="26">
         <v>1</v>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="26">
         <v>0.54</v>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="26">
         <v>0.25</v>
       </c>
-      <c r="L51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="Q51" s="65"/>
-    </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L51" s="26"/>
+      <c r="O51" s="26"/>
+      <c r="Q51" s="64"/>
+    </row>
+    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="str">
-        <f>S23</f>
+        <f>S55</f>
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
@@ -6348,10 +6168,10 @@
       <c r="F52" s="23">
         <v>2030</v>
       </c>
-      <c r="G52" s="27">
+      <c r="G52" s="26">
         <v>1</v>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="26">
         <v>1</v>
       </c>
       <c r="I52" s="23">
@@ -6363,7 +6183,7 @@
       <c r="K52" s="23">
         <v>39.799999999999997</v>
       </c>
-      <c r="L52" s="27">
+      <c r="L52" s="26">
         <v>2</v>
       </c>
       <c r="M52" s="23">
@@ -6375,41 +6195,58 @@
       <c r="O52" s="23">
         <v>0.45</v>
       </c>
-      <c r="Q52" s="65"/>
-    </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="Q52" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R52" s="64"/>
+      <c r="S52" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="T52" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="U52" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V52" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W52" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E53" s="23">
         <v>2035</v>
       </c>
-      <c r="G53" s="27">
+      <c r="G53" s="26">
         <v>1</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="26">
         <v>1</v>
       </c>
       <c r="I53" s="23">
         <v>0.8</v>
       </c>
-      <c r="L53" s="27"/>
-      <c r="Q53" s="65"/>
-    </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L53" s="26"/>
+    </row>
+    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E54" s="23">
         <v>2040</v>
       </c>
-      <c r="G54" s="27">
+      <c r="G54" s="26">
         <v>1</v>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="26">
         <v>1.8</v>
       </c>
       <c r="I54" s="23">
         <v>0.8</v>
       </c>
-      <c r="L54" s="27"/>
-      <c r="Q54" s="65"/>
-    </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="L54" s="26"/>
+      <c r="Q54" s="64"/>
+    </row>
+    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B55" s="23" t="s">
         <v>193</v>
       </c>
@@ -6446,11 +6283,27 @@
       <c r="O55" s="23">
         <v>0.5</v>
       </c>
-      <c r="Q55" s="65"/>
-      <c r="S55" s="23"/>
-      <c r="T55" s="23"/>
-    </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="Q55" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R55" s="64"/>
+      <c r="S55" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="T55" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="U55" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V55" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W55" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E56" s="23">
         <v>2030</v>
       </c>
@@ -6464,7 +6317,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E57" s="23">
         <v>2035</v>
       </c>
@@ -6478,7 +6331,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
       <c r="E58" s="23">
         <v>2040</v>
       </c>
@@ -6503,44 +6356,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="23" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="23" customWidth="1"/>
-    <col min="16" max="16" width="66.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="23" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="66.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5546875" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.6640625" customWidth="1"/>
+    <col min="21" max="21" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-    </row>
-    <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+    </row>
+    <row r="3" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="22" t="s">
         <v>43</v>
       </c>
@@ -6563,7 +6416,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>113</v>
       </c>
@@ -6586,89 +6439,89 @@
       <c r="I4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="59"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="M5" s="61" t="s">
+      <c r="N4" s="58"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M5" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="62" t="s">
+      <c r="N5" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="61" t="s">
+      <c r="O5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="61" t="s">
+      <c r="P5" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="61" t="s">
+      <c r="Q5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="61" t="s">
+      <c r="R5" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="61" t="s">
+      <c r="S5" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="T5" s="61" t="s">
+      <c r="T5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="29"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="M6" s="63" t="s">
+    <row r="6" spans="1:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="28"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="M6" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="N6" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="63" t="s">
+      <c r="O6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="63" t="s">
+      <c r="P6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="63" t="s">
+      <c r="Q6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="63" t="s">
+      <c r="R6" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="S6" s="63" t="s">
+      <c r="S6" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="63" t="s">
+      <c r="T6" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="U6" s="63" t="s">
+      <c r="U6" s="62" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="28"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="H7" s="32"/>
+    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="27"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="H7" s="31"/>
       <c r="M7" s="2" t="s">
         <v>279</v>
       </c>
@@ -6691,7 +6544,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="M8" s="2" t="s">
         <v>280</v>
       </c>
@@ -6710,37 +6563,37 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B10"/>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>0</v>
+      </c>
       <c r="C10"/>
-      <c r="D10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6"/>
+      <c r="D10"/>
+      <c r="E10"/>
       <c r="F10"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="33"/>
+      <c r="K10" s="32"/>
       <c r="L10"/>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="59"/>
-      <c r="O10" s="65"/>
-      <c r="P10" s="65"/>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="65"/>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="N10" s="58"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -6759,7 +6612,7 @@
       <c r="G11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>185</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -6772,35 +6625,35 @@
         <v>69</v>
       </c>
       <c r="L11"/>
-      <c r="M11" s="61" t="s">
+      <c r="M11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="62" t="s">
+      <c r="N11" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="61" t="s">
+      <c r="O11" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="61" t="s">
+      <c r="P11" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="Q11" s="61" t="s">
+      <c r="Q11" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="R11" s="61" t="s">
+      <c r="R11" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="S11" s="61" t="s">
+      <c r="S11" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="T11" s="61" t="s">
+      <c r="T11" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="U11" s="60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>71</v>
       </c>
@@ -6830,35 +6683,35 @@
         <v>186</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="63" t="s">
+      <c r="M12" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="63" t="s">
+      <c r="N12" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="63" t="s">
+      <c r="O12" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="63" t="s">
+      <c r="P12" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="63" t="s">
+      <c r="Q12" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="R12" s="63" t="s">
+      <c r="R12" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="S12" s="63" t="s">
+      <c r="S12" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="T12" s="63" t="s">
+      <c r="T12" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="U12" s="63" t="s">
+      <c r="U12" s="62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>78</v>
       </c>
@@ -6866,8 +6719,8 @@
       <c r="D13" s="11"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="76" t="s">
+      <c r="G13" s="74"/>
+      <c r="H13" s="75" t="s">
         <v>132</v>
       </c>
       <c r="I13" s="17" t="s">
@@ -6880,19 +6733,19 @@
         <v>79</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="63" t="s">
+      <c r="M13" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="N13" s="63"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f t="shared" ref="B14:B20" si="0">O14</f>
         <v>IBOILNCOA</v>
@@ -6900,22 +6753,22 @@
       <c r="C14" t="s">
         <v>251</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>2022</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>0.9</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="30">
         <v>0.5</v>
       </c>
       <c r="H14" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="82">
         <v>975</v>
       </c>
       <c r="J14"/>
@@ -6923,27 +6776,27 @@
         <v>15</v>
       </c>
       <c r="L14"/>
-      <c r="M14" s="60" t="s">
+      <c r="M14" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N14" s="65"/>
-      <c r="O14" s="60" t="s">
+      <c r="N14" s="64"/>
+      <c r="O14" s="59" t="s">
         <v>245</v>
       </c>
-      <c r="P14" s="60" t="s">
+      <c r="P14" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="Q14" s="65" t="s">
+      <c r="Q14" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="64"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>IBOILNBIO</v>
@@ -6951,50 +6804,50 @@
       <c r="C15" t="s">
         <v>253</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>2022</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>0.9</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>0.5</v>
       </c>
       <c r="H15" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I15" s="83">
+      <c r="I15" s="82">
         <v>750</v>
       </c>
-      <c r="J15" s="30"/>
+      <c r="J15" s="29"/>
       <c r="K15">
         <v>15</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="60" t="s">
+      <c r="M15" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N15" s="65"/>
-      <c r="O15" s="60" t="s">
+      <c r="N15" s="64"/>
+      <c r="O15" s="59" t="s">
         <v>246</v>
       </c>
-      <c r="P15" s="60" t="s">
+      <c r="P15" s="59" t="s">
         <v>255</v>
       </c>
-      <c r="Q15" s="65" t="s">
+      <c r="Q15" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R15" s="65" t="s">
+      <c r="R15" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S15" s="65"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="65"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="64"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>IBOILNELC</v>
@@ -7002,52 +6855,52 @@
       <c r="C16" t="s">
         <v>244</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>2022</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>0.99</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <v>0.5</v>
       </c>
       <c r="H16" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I16" s="83">
+      <c r="I16" s="82">
         <v>2078.7684537684499</v>
       </c>
-      <c r="J16" s="30"/>
+      <c r="J16" s="29"/>
       <c r="K16">
         <v>15</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="60" t="s">
+      <c r="M16" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="65"/>
-      <c r="O16" s="60" t="s">
+      <c r="N16" s="64"/>
+      <c r="O16" s="59" t="s">
         <v>247</v>
       </c>
-      <c r="P16" s="60" t="s">
+      <c r="P16" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="Q16" s="65" t="s">
+      <c r="Q16" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R16" s="65" t="s">
+      <c r="R16" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S16" s="65" t="s">
+      <c r="S16" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>262</v>
       </c>
@@ -7057,19 +6910,19 @@
       <c r="D17" t="s">
         <v>261</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>2022</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>0.5</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>0.5</v>
       </c>
       <c r="H17" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="82">
         <v>500</v>
       </c>
       <c r="J17"/>
@@ -7077,27 +6930,27 @@
         <v>10</v>
       </c>
       <c r="L17"/>
-      <c r="M17" s="60" t="s">
+      <c r="M17" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="65"/>
+      <c r="N17" s="64"/>
       <c r="O17" t="s">
         <v>262</v>
       </c>
-      <c r="P17" s="60" t="s">
+      <c r="P17" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="Q17" s="65" t="s">
+      <c r="Q17" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="65" t="s">
+      <c r="R17" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="64"/>
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>ICOMPNELC</v>
@@ -7108,19 +6961,19 @@
       <c r="D18" t="s">
         <v>269</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>2022</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>1</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="30">
         <v>0.5</v>
       </c>
       <c r="H18" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="83">
+      <c r="I18" s="82">
         <v>1340</v>
       </c>
       <c r="J18"/>
@@ -7128,29 +6981,29 @@
         <v>15.5</v>
       </c>
       <c r="L18"/>
-      <c r="M18" s="60" t="s">
+      <c r="M18" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="65"/>
-      <c r="O18" s="60" t="s">
+      <c r="N18" s="64"/>
+      <c r="O18" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="P18" s="60" t="s">
+      <c r="P18" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="Q18" s="65" t="s">
+      <c r="Q18" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S18" s="65" t="s">
+      <c r="S18" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>IPUMPNELC</v>
@@ -7161,19 +7014,19 @@
       <c r="D19" t="s">
         <v>270</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>2022</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>0.7</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="30">
         <v>0.5</v>
       </c>
       <c r="H19" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="83">
+      <c r="I19" s="82">
         <v>1700</v>
       </c>
       <c r="J19"/>
@@ -7181,29 +7034,29 @@
         <v>10</v>
       </c>
       <c r="L19"/>
-      <c r="M19" s="60" t="s">
+      <c r="M19" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="65"/>
-      <c r="O19" s="60" t="s">
+      <c r="N19" s="64"/>
+      <c r="O19" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="P19" s="60" t="s">
+      <c r="P19" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="65" t="s">
+      <c r="R19" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="65" t="s">
+      <c r="S19" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>IMOTONELC</v>
@@ -7214,22 +7067,22 @@
       <c r="D20" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>2022</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>0.95</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <v>0.5</v>
       </c>
       <c r="H20" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I20" s="83">
+      <c r="I20" s="82">
         <v>120</v>
       </c>
-      <c r="J20" s="30"/>
+      <c r="J20" s="29"/>
       <c r="K20">
         <v>10</v>
       </c>
@@ -7248,11 +7101,11 @@
       <c r="R20" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="65" t="s">
+      <c r="S20" s="64" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
         <v>265</v>
       </c>
@@ -7262,7 +7115,7 @@
       <c r="D21" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>2022</v>
       </c>
       <c r="F21" s="23">
@@ -7274,7 +7127,7 @@
       <c r="H21" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="83">
+      <c r="I21" s="82">
         <v>100</v>
       </c>
       <c r="K21" s="23">
@@ -7295,11 +7148,11 @@
       <c r="R21" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="65" t="s">
+      <c r="S21" s="64" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="23" t="s">
         <v>277</v>
       </c>
@@ -7309,7 +7162,7 @@
       <c r="D22" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>2022</v>
       </c>
       <c r="F22" s="23">
@@ -7321,7 +7174,7 @@
       <c r="H22" s="23">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="83">
+      <c r="I22" s="82">
         <v>100</v>
       </c>
       <c r="K22" s="23">
@@ -7343,11 +7196,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="P23" s="2"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="D27" s="79"/>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="D27" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7357,31 +7210,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" customWidth="1"/>
+    <col min="16" max="16" width="17.5546875" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="16384" width="8.85546875" style="23"/>
+    <col min="20" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="22" t="s">
         <v>43</v>
       </c>
@@ -7399,7 +7252,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -7409,78 +7262,78 @@
       <c r="G2" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="K3" s="61" t="s">
+      <c r="L2" s="58"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="K3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="62" t="s">
+      <c r="L3" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="61" t="s">
+      <c r="M3" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="61" t="s">
+      <c r="N3" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="61" t="s">
+      <c r="O3" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="61" t="s">
+      <c r="P3" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="R3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="61" t="s">
+      <c r="S3" s="60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
-      <c r="K4" s="63" t="s">
+      <c r="K4" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="M4" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="63" t="s">
+      <c r="R4" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="62" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="K5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -7490,24 +7343,24 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="F7" s="6" t="s">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L7" s="58"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
@@ -7523,44 +7376,44 @@
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="61" t="s">
+      <c r="K8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="62" t="s">
+      <c r="L8" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="61" t="s">
+      <c r="N8" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="61" t="s">
+      <c r="O8" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="61" t="s">
+      <c r="P8" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="61" t="s">
+      <c r="Q8" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="61" t="s">
+      <c r="R8" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="61" t="s">
+      <c r="S8" s="60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>71</v>
       </c>
@@ -7581,64 +7434,64 @@
       <c r="I9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="63" t="s">
+      <c r="K9" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="63" t="s">
+      <c r="L9" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="63" t="s">
+      <c r="M9" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="N9" s="63" t="s">
+      <c r="N9" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="63" t="s">
+      <c r="O9" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="P9" s="63" t="s">
+      <c r="P9" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="63" t="s">
+      <c r="Q9" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="63" t="s">
+      <c r="R9" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="S9" s="63" t="s">
+      <c r="S9" s="62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="63" t="s">
+      <c r="K10" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>286</v>
       </c>
@@ -7650,12 +7503,12 @@
         <v>2022</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="44"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="23">
         <v>22.5</v>
       </c>
-      <c r="I11" s="43"/>
-      <c r="K11" s="65" t="str">
+      <c r="I11" s="42"/>
+      <c r="K11" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
@@ -7663,7 +7516,7 @@
         <v>286</v>
       </c>
       <c r="N11" s="21"/>
-      <c r="O11" s="65" t="str">
+      <c r="O11" s="64" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
@@ -7671,7 +7524,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>287</v>
       </c>
@@ -7683,12 +7536,12 @@
         <v>2022</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="44"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="23">
         <v>23.4</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="K12" s="65" t="str">
+      <c r="I12" s="42"/>
+      <c r="K12" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
@@ -7696,7 +7549,7 @@
         <v>287</v>
       </c>
       <c r="N12" s="21"/>
-      <c r="O12" s="65" t="str">
+      <c r="O12" s="64" t="str">
         <f t="shared" ref="O12:O21" si="0">$E$2</f>
         <v>PJ</v>
       </c>
@@ -7704,7 +7557,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>288</v>
       </c>
@@ -7716,12 +7569,12 @@
         <v>2022</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="44"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="23">
         <v>15.4</v>
       </c>
-      <c r="I13" s="43"/>
-      <c r="K13" s="65" t="str">
+      <c r="I13" s="42"/>
+      <c r="K13" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
@@ -7729,7 +7582,7 @@
         <v>288</v>
       </c>
       <c r="N13" s="21"/>
-      <c r="O13" s="65" t="str">
+      <c r="O13" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
@@ -7737,7 +7590,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>289</v>
       </c>
@@ -7753,8 +7606,8 @@
       <c r="H14" s="23">
         <v>20.8</v>
       </c>
-      <c r="I14" s="30"/>
-      <c r="K14" s="65" t="str">
+      <c r="I14" s="29"/>
+      <c r="K14" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
@@ -7762,7 +7615,7 @@
         <v>289</v>
       </c>
       <c r="N14" s="21"/>
-      <c r="O14" s="65" t="str">
+      <c r="O14" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
@@ -7770,7 +7623,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>290</v>
       </c>
@@ -7785,8 +7638,8 @@
       <c r="H15" s="23">
         <v>12.6</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="K15" s="65" t="str">
+      <c r="I15" s="29"/>
+      <c r="K15" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
@@ -7794,7 +7647,7 @@
         <v>290</v>
       </c>
       <c r="N15" s="21"/>
-      <c r="O15" s="65" t="str">
+      <c r="O15" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
@@ -7802,7 +7655,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>291</v>
       </c>
@@ -7818,15 +7671,15 @@
       <c r="H16" s="23">
         <v>13.5</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="K16" s="65" t="str">
+      <c r="I16" s="42"/>
+      <c r="K16" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="O16" s="65" t="str">
+      <c r="O16" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
@@ -7834,7 +7687,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>292</v>
       </c>
@@ -7847,14 +7700,14 @@
       <c r="H17" s="23">
         <v>14.5</v>
       </c>
-      <c r="K17" s="65" t="str">
+      <c r="K17" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="O17" s="65" t="str">
+      <c r="O17" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
@@ -7862,8 +7715,8 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="60" t="s">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="59" t="s">
         <v>301</v>
       </c>
       <c r="D18" t="s">
@@ -7872,25 +7725,25 @@
       <c r="E18" s="2">
         <v>2022</v>
       </c>
-      <c r="H18" s="82">
+      <c r="H18" s="81">
         <v>35.75</v>
       </c>
       <c r="I18">
         <v>8.91</v>
       </c>
-      <c r="K18" s="65" t="str">
+      <c r="K18" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
-      <c r="M18" s="60" t="s">
+      <c r="M18" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="O18" s="65" t="str">
+      <c r="O18" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>302</v>
       </c>
@@ -7903,22 +7756,22 @@
       <c r="H19">
         <v>22.05</v>
       </c>
-      <c r="I19" s="80">
+      <c r="I19" s="79">
         <v>2.6490239999999998</v>
       </c>
-      <c r="K19" s="65" t="str">
+      <c r="K19" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="O19" s="65" t="str">
+      <c r="O19" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>305</v>
       </c>
@@ -7934,19 +7787,19 @@
       <c r="I20">
         <v>14.19</v>
       </c>
-      <c r="K20" s="65" t="str">
+      <c r="K20" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="O20" s="65" t="str">
+      <c r="O20" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>310</v>
@@ -7963,20 +7816,20 @@
       <c r="I21">
         <v>14.19</v>
       </c>
-      <c r="K21" s="65" t="str">
+      <c r="K21" s="64" t="str">
         <f>[2]EB1!$B$6</f>
         <v>IMP</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="O21" s="65" t="str">
+      <c r="O21" s="64" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="44"/>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="43"/>
       <c r="C24" s="2"/>
       <c r="K24" s="2" t="s">
         <v>303</v>
@@ -8000,16 +7853,16 @@
         <v>309</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
-      <c r="K25" s="80">
+      <c r="K25" s="79">
         <v>168</v>
       </c>
-      <c r="L25" s="80">
+      <c r="L25" s="79">
         <f>K25*24*365*0.5</f>
         <v>735840</v>
       </c>
-      <c r="M25" s="80">
+      <c r="M25" s="79">
         <f>L25*N25</f>
         <v>2.6490239999999998</v>
       </c>
@@ -8019,24 +7872,24 @@
       <c r="O25">
         <v>7.9399999999999998E-2</v>
       </c>
-      <c r="P25" s="81">
+      <c r="P25" s="80">
         <f>L25*O25*10^3</f>
         <v>58425696</v>
       </c>
-      <c r="Q25" s="80">
+      <c r="Q25" s="79">
         <f>P25/M25</f>
         <v>22055555.555555556</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="K26" s="80">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K26" s="79">
         <v>900</v>
       </c>
-      <c r="L26" s="80">
+      <c r="L26" s="79">
         <f>K26*24*365*0.5</f>
         <v>3942000</v>
       </c>
-      <c r="M26" s="80">
+      <c r="M26" s="79">
         <f>L26*N26</f>
         <v>14.191199999999998</v>
       </c>
@@ -8046,11 +7899,11 @@
       <c r="O26">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="P26" s="81">
+      <c r="P26" s="80">
         <f>L26*O26*10^3</f>
         <v>303534000</v>
       </c>
-      <c r="Q26" s="80">
+      <c r="Q26" s="79">
         <f>P26/M26</f>
         <v>21388888.888888892</v>
       </c>
@@ -8065,37 +7918,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
     <col min="12" max="12" width="2" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.44140625" customWidth="1"/>
+    <col min="18" max="18" width="11.109375" customWidth="1"/>
+    <col min="19" max="19" width="13.5546875" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>43</v>
       </c>
@@ -8118,7 +7971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>121</v>
       </c>
@@ -8141,7 +7994,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>122</v>
       </c>
@@ -8163,19 +8016,19 @@
       <c r="I5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="59"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
-    </row>
-    <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="N5" s="58"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>86</v>
       </c>
@@ -8197,74 +8050,74 @@
       <c r="I6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="61" t="s">
+      <c r="M6" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="61" t="s">
+      <c r="O6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="61" t="s">
+      <c r="P6" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="61" t="s">
+      <c r="Q6" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="61" t="s">
+      <c r="R6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="S6" s="61" t="s">
+      <c r="S6" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="61" t="s">
+      <c r="T6" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="61" t="s">
+      <c r="U6" s="60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="M7" s="63" t="s">
+    <row r="7" spans="1:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="M7" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="N7" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="63" t="s">
+      <c r="O7" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="63" t="s">
+      <c r="P7" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="63" t="s">
+      <c r="Q7" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="63" t="s">
+      <c r="R7" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="S7" s="63" t="s">
+      <c r="S7" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="63" t="s">
+      <c r="T7" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="U7" s="63" t="s">
+      <c r="U7" s="62" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
+    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
       <c r="M8" s="2" t="s">
         <v>279</v>
       </c>
@@ -8286,12 +8139,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
       <c r="M9" s="2" t="s">
         <v>280</v>
       </c>
@@ -8309,12 +8162,12 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
       <c r="M10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -8324,29 +8177,31 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="D13" s="6" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
         <v>0</v>
       </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="7"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="33"/>
-      <c r="M13" s="59" t="s">
+      <c r="K13" s="32"/>
+      <c r="M13" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="N13" s="59"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="N13" s="58"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
         <v>1</v>
       </c>
@@ -8365,7 +8220,7 @@
       <c r="G14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>185</v>
       </c>
       <c r="I14" s="16" t="s">
@@ -8377,35 +8232,35 @@
       <c r="K14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="61" t="s">
+      <c r="M14" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="62" t="s">
+      <c r="N14" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="61" t="s">
+      <c r="O14" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="P14" s="61" t="s">
+      <c r="P14" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="Q14" s="61" t="s">
+      <c r="Q14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="61" t="s">
+      <c r="R14" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="S14" s="61" t="s">
+      <c r="S14" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="T14" s="61" t="s">
+      <c r="T14" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="U14" s="61" t="s">
+      <c r="U14" s="60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>71</v>
       </c>
@@ -8434,35 +8289,35 @@
       <c r="K15" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="M15" s="63" t="s">
+      <c r="M15" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="63" t="s">
+      <c r="N15" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="O15" s="63" t="s">
+      <c r="O15" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="63" t="s">
+      <c r="P15" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="63" t="s">
+      <c r="Q15" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="63" t="s">
+      <c r="R15" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="S15" s="63" t="s">
+      <c r="S15" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="T15" s="63" t="s">
+      <c r="T15" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="U15" s="63" t="s">
+      <c r="U15" s="62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="10" t="s">
         <v>78</v>
       </c>
@@ -8471,7 +8326,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="45" t="s">
         <v>132</v>
       </c>
       <c r="I16" s="19" t="s">
@@ -8483,19 +8338,19 @@
       <c r="K16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="63" t="s">
+      <c r="M16" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="63"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="63"/>
-      <c r="T16" s="63"/>
-      <c r="U16" s="63"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="N16" s="62"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="str">
         <f>O17</f>
         <v>CSCNSOL1</v>
@@ -8506,13 +8361,13 @@
       <c r="D17" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>2022</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>0.35</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>0.3</v>
       </c>
       <c r="H17">
@@ -8521,139 +8376,139 @@
       <c r="I17" s="23">
         <v>700</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <v>12</v>
       </c>
       <c r="K17">
         <v>15</v>
       </c>
-      <c r="M17" s="60" t="s">
+      <c r="M17" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65" t="s">
+      <c r="N17" s="64"/>
+      <c r="O17" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="P17" s="60" t="s">
+      <c r="P17" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="Q17" s="65" t="s">
+      <c r="Q17" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="65" t="s">
+      <c r="R17" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="60" t="s">
+      <c r="S17" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="str">
         <f t="shared" ref="B18:B27" si="0">O18</f>
         <v>CSCNELC1</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="54" t="s">
         <v>238</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>2022</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>1</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="30">
         <v>0.3</v>
       </c>
       <c r="H18">
         <v>31.536000000000001</v>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="46">
         <v>550</v>
       </c>
-      <c r="J18" s="52">
+      <c r="J18" s="51">
         <v>12</v>
       </c>
       <c r="K18">
         <v>20</v>
       </c>
-      <c r="M18" s="60" t="s">
+      <c r="M18" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65" t="s">
+      <c r="N18" s="64"/>
+      <c r="O18" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="P18" s="60" t="s">
+      <c r="P18" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="Q18" s="65" t="s">
+      <c r="Q18" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="S18" s="60" t="s">
+      <c r="S18" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="48" t="str">
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="47" t="str">
         <f t="shared" si="0"/>
         <v>CAPNELC1</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>2022</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="47">
         <v>1.02</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="48">
         <v>0.3</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="47">
         <v>31.536000000000001</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="48">
         <v>0.5</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48">
+      <c r="J19" s="47"/>
+      <c r="K19" s="47">
         <v>5</v>
       </c>
-      <c r="M19" s="60" t="s">
+      <c r="M19" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65" t="s">
+      <c r="N19" s="64"/>
+      <c r="O19" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="P19" s="60" t="s">
+      <c r="P19" s="59" t="s">
         <v>233</v>
       </c>
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="65" t="s">
+      <c r="R19" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="65"/>
-      <c r="T19" s="65"/>
-      <c r="U19" s="65"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="64"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>COTNOIL1</v>
@@ -8664,97 +8519,97 @@
       <c r="D20" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>2022</v>
       </c>
       <c r="F20">
         <v>1.02</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <v>0.3</v>
       </c>
       <c r="H20">
         <v>31.536000000000001</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="30">
         <v>0.3</v>
       </c>
       <c r="K20">
         <v>15</v>
       </c>
-      <c r="M20" s="60" t="s">
+      <c r="M20" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N20" s="65"/>
-      <c r="O20" s="65" t="s">
+      <c r="N20" s="64"/>
+      <c r="O20" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="P20" s="60" t="s">
+      <c r="P20" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="Q20" s="65" t="s">
+      <c r="Q20" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="65" t="s">
+      <c r="R20" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
-    </row>
-    <row r="21" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53" t="str">
+      <c r="S20" s="64"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="64"/>
+    </row>
+    <row r="21" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="52" t="str">
         <f t="shared" si="0"/>
         <v>COTNELC1</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>2022</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="52">
         <v>1.05</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="53">
         <v>0.3</v>
       </c>
-      <c r="H21" s="53">
+      <c r="H21" s="52">
         <v>31.536000000000001</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="53">
         <v>0.75</v>
       </c>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53">
+      <c r="J21" s="52"/>
+      <c r="K21" s="52">
         <v>15</v>
       </c>
-      <c r="M21" s="60" t="s">
+      <c r="M21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67" t="s">
+      <c r="N21" s="66"/>
+      <c r="O21" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="P21" s="68" t="s">
+      <c r="P21" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="Q21" s="67" t="s">
+      <c r="Q21" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="67" t="s">
+      <c r="R21" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="60" t="s">
+      <c r="S21" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f>O22</f>
         <v>RSCNSOL1</v>
@@ -8765,154 +8620,154 @@
       <c r="D22" t="s">
         <v>239</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>2022</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="30">
         <v>0.35</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="30">
         <v>0.3</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="38">
         <v>31.536000000000001</v>
       </c>
       <c r="I22" s="23">
         <v>700</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="29">
         <v>14</v>
       </c>
       <c r="K22">
         <v>15</v>
       </c>
       <c r="L22" s="2"/>
-      <c r="M22" s="60" t="s">
+      <c r="M22" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N22" s="65"/>
-      <c r="O22" s="60" t="s">
+      <c r="N22" s="64"/>
+      <c r="O22" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="P22" s="60" t="s">
+      <c r="P22" s="59" t="s">
         <v>242</v>
       </c>
-      <c r="Q22" s="65" t="s">
+      <c r="Q22" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R22" s="65" t="s">
+      <c r="R22" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="S22" s="64"/>
+      <c r="T22" s="64"/>
+      <c r="U22" s="64"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>RSCNELC1</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <v>2022</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="30">
         <v>0.96</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="30">
         <v>0.3</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="38">
         <v>31.536000000000001</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="46">
         <v>550</v>
       </c>
-      <c r="J23" s="52">
+      <c r="J23" s="51">
         <v>11</v>
       </c>
       <c r="K23">
         <v>20</v>
       </c>
       <c r="L23" s="2"/>
-      <c r="M23" s="60" t="s">
+      <c r="M23" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N23" s="65"/>
-      <c r="O23" s="60" t="s">
+      <c r="N23" s="64"/>
+      <c r="O23" s="59" t="s">
         <v>241</v>
       </c>
-      <c r="P23" s="60" t="s">
+      <c r="P23" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="Q23" s="65" t="s">
+      <c r="Q23" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R23" s="65" t="s">
+      <c r="R23" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="48" t="str">
+      <c r="S23" s="64"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="47" t="str">
         <f t="shared" si="0"/>
         <v>RAPNELC1</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="29">
         <v>2022</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="47">
         <v>1.02</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="48">
         <v>0.3</v>
       </c>
-      <c r="H24" s="77">
+      <c r="H24" s="76">
         <v>31.536000000000001</v>
       </c>
-      <c r="I24" s="49">
+      <c r="I24" s="48">
         <v>0.5</v>
       </c>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48">
+      <c r="J24" s="47"/>
+      <c r="K24" s="47">
         <v>5</v>
       </c>
-      <c r="M24" s="60" t="s">
+      <c r="M24" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="65"/>
-      <c r="O24" s="60" t="s">
+      <c r="N24" s="64"/>
+      <c r="O24" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="P24" s="60" t="s">
+      <c r="P24" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="Q24" s="65" t="s">
+      <c r="Q24" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R24" s="65" t="s">
+      <c r="R24" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S24" s="60" t="s">
+      <c r="S24" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="T24" s="65"/>
-      <c r="U24" s="65"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T24" s="64"/>
+      <c r="U24" s="64"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>ROTNOIL1</v>
@@ -8923,45 +8778,45 @@
       <c r="D25" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <v>2022</v>
       </c>
       <c r="F25">
         <v>1.02</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="30">
         <v>0.3</v>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="38">
         <v>31.536000000000001</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="30">
         <v>0.3</v>
       </c>
       <c r="K25">
         <v>15</v>
       </c>
-      <c r="M25" s="60" t="s">
+      <c r="M25" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N25" s="65"/>
-      <c r="O25" s="60" t="s">
+      <c r="N25" s="64"/>
+      <c r="O25" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="P25" s="60" t="s">
+      <c r="P25" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="Q25" s="65" t="s">
+      <c r="Q25" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R25" s="65" t="s">
+      <c r="R25" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="S25" s="64"/>
+      <c r="T25" s="64"/>
+      <c r="U25" s="64"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>ROTNBIO1</v>
@@ -8972,97 +8827,97 @@
       <c r="D26" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <v>2022</v>
       </c>
       <c r="F26">
         <v>1.02</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="30">
         <v>0.3</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="38">
         <v>31.536000000000001</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="30">
         <v>1</v>
       </c>
       <c r="K26">
         <v>15</v>
       </c>
-      <c r="M26" s="60" t="s">
+      <c r="M26" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N26" s="65"/>
-      <c r="O26" s="60" t="s">
+      <c r="N26" s="64"/>
+      <c r="O26" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="P26" s="60" t="s">
+      <c r="P26" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="Q26" s="65" t="s">
+      <c r="Q26" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R26" s="65" t="s">
+      <c r="R26" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
-    </row>
-    <row r="27" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="str">
+      <c r="S26" s="64"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="64"/>
+    </row>
+    <row r="27" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="52" t="str">
         <f t="shared" si="0"/>
         <v>ROTNELC1</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <v>2022</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="52">
         <v>1.05</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="53">
         <v>0.3</v>
       </c>
-      <c r="H27" s="78">
+      <c r="H27" s="77">
         <v>31.536000000000001</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="53">
         <v>0.75</v>
       </c>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53">
+      <c r="J27" s="52"/>
+      <c r="K27" s="52">
         <v>15</v>
       </c>
-      <c r="M27" s="60" t="s">
+      <c r="M27" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67" t="s">
+      <c r="N27" s="66"/>
+      <c r="O27" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="P27" s="68" t="s">
+      <c r="P27" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="Q27" s="67" t="s">
+      <c r="Q27" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="R27" s="67" t="s">
+      <c r="R27" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="S27" s="60" t="s">
+      <c r="S27" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>273</v>
       </c>
@@ -9072,16 +8927,16 @@
       <c r="D28" t="s">
         <v>272</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="29">
         <v>2022</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="30">
         <v>0.25</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="30">
         <v>0.35</v>
       </c>
-      <c r="H28" s="39">
+      <c r="H28" s="38">
         <v>31.536000000000001</v>
       </c>
       <c r="I28" s="23">
@@ -9090,23 +8945,23 @@
       <c r="K28">
         <v>20</v>
       </c>
-      <c r="M28" s="60" t="s">
+      <c r="M28" s="59" t="s">
         <v>90</v>
       </c>
       <c r="O28" t="s">
         <v>273</v>
       </c>
-      <c r="P28" s="60" t="s">
+      <c r="P28" s="59" t="s">
         <v>274</v>
       </c>
-      <c r="Q28" s="65" t="s">
+      <c r="Q28" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R28" s="65" t="s">
+      <c r="R28" s="64" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>276</v>
       </c>
@@ -9116,16 +8971,16 @@
       <c r="D29" t="s">
         <v>272</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>2022</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="30">
         <v>0.9</v>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="30">
         <v>0.35</v>
       </c>
-      <c r="H29" s="39">
+      <c r="H29" s="38">
         <v>31.536000000000001</v>
       </c>
       <c r="I29" s="23">
@@ -9134,51 +8989,51 @@
       <c r="K29">
         <v>4</v>
       </c>
-      <c r="M29" s="60" t="s">
+      <c r="M29" s="59" t="s">
         <v>90</v>
       </c>
       <c r="O29" t="s">
         <v>276</v>
       </c>
-      <c r="P29" s="60" t="s">
+      <c r="P29" s="59" t="s">
         <v>275</v>
       </c>
-      <c r="Q29" s="65" t="s">
+      <c r="Q29" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="R29" s="65" t="s">
+      <c r="R29" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="S29" s="60" t="s">
+      <c r="S29" s="59" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="E30" s="29"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="23"/>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="E31" s="29"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
       <c r="I31" s="23"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="E32" s="29"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="23"/>
     </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E33" s="29"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
       <c r="I33" s="23"/>
     </row>
   </sheetData>
@@ -9192,33 +9047,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:V33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="78.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="78.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>43</v>
       </c>
@@ -9237,12 +9092,12 @@
       <c r="G1" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="34"/>
       <c r="I1" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="2:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>92</v>
       </c>
@@ -9258,94 +9113,94 @@
       <c r="F2" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="32"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="N3" s="61" t="s">
+      <c r="O2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="N3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="62" t="s">
+      <c r="O3" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="61" t="s">
+      <c r="P3" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="R3" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="61" t="s">
+      <c r="S3" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="61" t="s">
+      <c r="T3" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="61" t="s">
+      <c r="U3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="61" t="s">
+      <c r="V3" s="60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="N4" s="63" t="s">
+    <row r="4" spans="2:22" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="N4" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="O4" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="63" t="s">
+      <c r="R4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="63" t="s">
+      <c r="S4" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="63" t="s">
+      <c r="T4" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="U4" s="63" t="s">
+      <c r="U4" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="63" t="s">
+      <c r="V4" s="62" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
+    <row r="5" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
       <c r="N5" s="2" t="s">
         <v>279</v>
       </c>
@@ -9367,7 +9222,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="N6" s="2" t="s">
         <v>280</v>
       </c>
@@ -9385,27 +9240,26 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="D8" s="6" t="s">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="6"/>
       <c r="G8" s="6"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="33"/>
-      <c r="N8" s="59" t="s">
+      <c r="K8" s="32"/>
+      <c r="N8" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="59"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="O8" s="58"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>1</v>
       </c>
@@ -9439,36 +9293,36 @@
       <c r="L9" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="M9" s="25"/>
-      <c r="N9" s="61" t="s">
+      <c r="M9" s="24"/>
+      <c r="N9" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="62" t="s">
+      <c r="O9" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="61" t="s">
+      <c r="P9" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="61" t="s">
+      <c r="Q9" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="R9" s="61" t="s">
+      <c r="R9" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="S9" s="61" t="s">
+      <c r="S9" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="61" t="s">
+      <c r="T9" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="61" t="s">
+      <c r="U9" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="V9" s="61" t="s">
+      <c r="V9" s="60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:22" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>71</v>
       </c>
@@ -9500,36 +9354,36 @@
       <c r="L10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="N10" s="63" t="s">
+      <c r="M10" s="36"/>
+      <c r="N10" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="63" t="s">
+      <c r="O10" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="63" t="s">
+      <c r="P10" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="63" t="s">
+      <c r="Q10" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="R10" s="63" t="s">
+      <c r="R10" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="63" t="s">
+      <c r="S10" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="T10" s="63" t="s">
+      <c r="T10" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="U10" s="63" t="s">
+      <c r="U10" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="V10" s="63" t="s">
+      <c r="V10" s="62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="10" t="s">
         <v>78</v>
       </c>
@@ -9539,7 +9393,7 @@
       <c r="F11" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="37" t="s">
         <v>103</v>
       </c>
       <c r="H11" s="20" t="s">
@@ -9557,20 +9411,20 @@
       <c r="L11" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="N11" s="69" t="s">
+      <c r="M11" s="36"/>
+      <c r="N11" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <f t="shared" ref="B12:B33" si="0">P12</f>
         <v>TCANDSL1</v>
@@ -9584,50 +9438,50 @@
       <c r="E12">
         <v>2022</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>0.31230553021919499</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="29">
         <v>12</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="30">
         <v>1.35</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="39">
         <v>30</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="30">
         <v>0.5</v>
       </c>
       <c r="K12">
         <v>20</v>
       </c>
-      <c r="L12" s="39">
+      <c r="L12" s="38">
         <v>1E-3</v>
       </c>
       <c r="N12" t="s">
         <v>90</v>
       </c>
-      <c r="O12" s="65"/>
-      <c r="P12" s="60" t="s">
+      <c r="O12" s="64"/>
+      <c r="P12" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="Q12" s="60" t="s">
+      <c r="Q12" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="R12" s="65" t="s">
+      <c r="R12" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S12" s="65" t="s">
+      <c r="S12" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T12" s="65"/>
-      <c r="U12" s="65" t="s">
+      <c r="T12" s="64"/>
+      <c r="U12" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V12" s="65"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V12" s="64"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>TCANLPG1</v>
@@ -9641,50 +9495,50 @@
       <c r="E13">
         <v>2022</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>0.39900000000000002</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <v>12</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="30">
         <v>1.25</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="39">
         <v>16.899999999999999</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="30">
         <v>0.5</v>
       </c>
       <c r="K13">
         <v>20</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="38">
         <v>1E-3</v>
       </c>
       <c r="N13" t="s">
         <v>90</v>
       </c>
-      <c r="O13" s="65"/>
-      <c r="P13" s="60" t="s">
+      <c r="O13" s="64"/>
+      <c r="P13" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="Q13" s="60" t="s">
+      <c r="Q13" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="R13" s="65" t="s">
+      <c r="R13" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S13" s="65" t="s">
+      <c r="S13" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65" t="s">
+      <c r="T13" s="64"/>
+      <c r="U13" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V13" s="65"/>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V13" s="64"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>TCANGSL1</v>
@@ -9698,107 +9552,107 @@
       <c r="E14">
         <v>2022</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>0.380510833505597</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="29">
         <v>12</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="30">
         <v>1.25</v>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="39">
         <v>25</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <v>0.5</v>
       </c>
       <c r="K14">
         <v>20</v>
       </c>
-      <c r="L14" s="39">
+      <c r="L14" s="38">
         <v>1E-3</v>
       </c>
       <c r="N14" t="s">
         <v>90</v>
       </c>
-      <c r="O14" s="65"/>
-      <c r="P14" s="60" t="s">
+      <c r="O14" s="64"/>
+      <c r="P14" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="Q14" s="60" t="s">
+      <c r="Q14" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="R14" s="65" t="s">
+      <c r="R14" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S14" s="65" t="s">
+      <c r="S14" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65" t="s">
+      <c r="T14" s="64"/>
+      <c r="U14" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V14" s="65"/>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B15" s="47" t="str">
+      <c r="V14" s="64"/>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TCANELC1</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="46">
         <v>2026</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="49">
         <v>1.5600711423474201</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="51">
         <v>12</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="49">
         <v>1.25</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="50">
         <v>20</v>
       </c>
-      <c r="J15" s="50">
+      <c r="J15" s="49">
         <v>0.15</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="46">
         <v>20</v>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="55">
         <v>1E-3</v>
       </c>
-      <c r="N15" s="47" t="s">
+      <c r="N15" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72" t="s">
+      <c r="O15" s="70"/>
+      <c r="P15" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="R15" s="71" t="s">
+      <c r="R15" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="S15" s="71" t="s">
+      <c r="S15" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71" t="s">
+      <c r="T15" s="70"/>
+      <c r="U15" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="V15" s="71"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V15" s="70"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>TPUNDSL1</v>
@@ -9812,7 +9666,7 @@
       <c r="E16">
         <v>2022</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>0.1575</v>
       </c>
       <c r="G16">
@@ -9821,10 +9675,10 @@
       <c r="H16">
         <v>15</v>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="39">
         <v>40</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="30">
         <v>0.24</v>
       </c>
       <c r="K16">
@@ -9836,26 +9690,26 @@
       <c r="N16" t="s">
         <v>90</v>
       </c>
-      <c r="O16" s="65"/>
-      <c r="P16" s="60" t="s">
+      <c r="O16" s="64"/>
+      <c r="P16" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="Q16" s="60" t="s">
+      <c r="Q16" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="R16" s="65" t="s">
+      <c r="R16" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S16" s="65" t="s">
+      <c r="S16" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="65"/>
-      <c r="U16" s="65" t="s">
+      <c r="T16" s="64"/>
+      <c r="U16" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V16" s="65"/>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V16" s="64"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>TPUNLPG1</v>
@@ -9869,7 +9723,7 @@
       <c r="E17">
         <v>2022</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>0.10500000000000001</v>
       </c>
       <c r="G17">
@@ -9878,10 +9732,10 @@
       <c r="H17">
         <v>15</v>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="39">
         <v>40</v>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="30">
         <v>0.24</v>
       </c>
       <c r="K17">
@@ -9893,26 +9747,26 @@
       <c r="N17" t="s">
         <v>90</v>
       </c>
-      <c r="O17" s="65"/>
-      <c r="P17" s="60" t="s">
+      <c r="O17" s="64"/>
+      <c r="P17" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="Q17" s="60" t="s">
+      <c r="Q17" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="R17" s="65" t="s">
+      <c r="R17" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S17" s="65" t="s">
+      <c r="S17" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65" t="s">
+      <c r="T17" s="64"/>
+      <c r="U17" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V17" s="65"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V17" s="64"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>TPUNGSL1</v>
@@ -9926,7 +9780,7 @@
       <c r="E18">
         <v>2022</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>0.1575</v>
       </c>
       <c r="G18">
@@ -9935,10 +9789,10 @@
       <c r="H18">
         <v>15</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="39">
         <v>40</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="30">
         <v>0.22499999999999998</v>
       </c>
       <c r="K18">
@@ -9950,83 +9804,83 @@
       <c r="N18" t="s">
         <v>90</v>
       </c>
-      <c r="O18" s="65"/>
-      <c r="P18" s="60" t="s">
+      <c r="O18" s="64"/>
+      <c r="P18" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="Q18" s="60" t="s">
+      <c r="Q18" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="S18" s="65" t="s">
+      <c r="S18" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65" t="s">
+      <c r="T18" s="64"/>
+      <c r="U18" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="V18" s="65"/>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B19" s="47" t="str">
+      <c r="V18" s="64"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TPUNELC1</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="46">
         <v>2026</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="49">
         <v>3.15E-2</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="46">
         <v>15</v>
       </c>
-      <c r="H19" s="47">
+      <c r="H19" s="46">
         <v>200</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="50">
         <v>40</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="49">
         <v>0.22499999999999998</v>
       </c>
-      <c r="K19" s="47">
+      <c r="K19" s="46">
         <v>30</v>
       </c>
-      <c r="L19" s="47">
+      <c r="L19" s="46">
         <v>1E-3</v>
       </c>
-      <c r="N19" s="47" t="s">
+      <c r="N19" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O19" s="71"/>
-      <c r="P19" s="72" t="s">
+      <c r="O19" s="70"/>
+      <c r="P19" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="Q19" s="72" t="s">
+      <c r="Q19" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="R19" s="71" t="s">
+      <c r="R19" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="S19" s="71" t="s">
+      <c r="S19" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71" t="s">
+      <c r="T19" s="70"/>
+      <c r="U19" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="V19" s="71"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V19" s="70"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>TMOTNGSL1</v>
@@ -10040,7 +9894,7 @@
       <c r="E20">
         <v>2022</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>1.1000000000000001</v>
       </c>
       <c r="G20">
@@ -10052,13 +9906,13 @@
       <c r="I20">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="30">
         <v>0.02</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="38">
         <v>1E-3</v>
       </c>
       <c r="N20" t="s">
@@ -10080,64 +9934,64 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B21" s="47" t="str">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TMOTNELC1</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="46">
         <v>2026</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="46">
         <v>3.2</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="46">
         <v>8</v>
       </c>
-      <c r="H21" s="47">
+      <c r="H21" s="46">
         <v>1.2</v>
       </c>
-      <c r="I21" s="47">
+      <c r="I21" s="46">
         <v>2</v>
       </c>
-      <c r="J21" s="47">
+      <c r="J21" s="46">
         <v>0.02</v>
       </c>
-      <c r="K21" s="47">
+      <c r="K21" s="46">
         <v>10</v>
       </c>
-      <c r="L21" s="56">
+      <c r="L21" s="55">
         <v>1E-3</v>
       </c>
-      <c r="N21" s="47" t="s">
+      <c r="N21" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47" t="s">
+      <c r="O21" s="46"/>
+      <c r="P21" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="Q21" s="47" t="s">
+      <c r="Q21" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R21" s="47" t="s">
+      <c r="R21" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S21" s="47" t="s">
+      <c r="S21" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47" t="s">
+      <c r="T21" s="46"/>
+      <c r="U21" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V21" s="47"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V21" s="46"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>TTRINLPG1</v>
@@ -10151,7 +10005,7 @@
       <c r="E22">
         <v>2022</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="30">
         <v>0.68</v>
       </c>
       <c r="G22">
@@ -10163,7 +10017,7 @@
       <c r="I22">
         <v>3</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="30">
         <v>0.25</v>
       </c>
       <c r="K22">
@@ -10191,7 +10045,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>TTRINGSL1</v>
@@ -10205,7 +10059,7 @@
       <c r="E23">
         <v>2022</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="30">
         <v>0.7</v>
       </c>
       <c r="G23">
@@ -10217,7 +10071,7 @@
       <c r="I23">
         <v>1.2</v>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="30">
         <v>0.25</v>
       </c>
       <c r="K23">
@@ -10245,64 +10099,64 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B24" s="47" t="str">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TTRINELC1</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="46" t="s">
         <v>207</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="46">
         <v>2026</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="46">
         <v>2.1</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="46">
         <v>12</v>
       </c>
-      <c r="H24" s="47">
+      <c r="H24" s="46">
         <v>2</v>
       </c>
-      <c r="I24" s="47">
+      <c r="I24" s="46">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J24" s="47">
+      <c r="J24" s="46">
         <v>0.12</v>
       </c>
-      <c r="K24" s="47">
+      <c r="K24" s="46">
         <v>10</v>
       </c>
-      <c r="L24" s="47">
+      <c r="L24" s="46">
         <v>1E-3</v>
       </c>
-      <c r="N24" s="47" t="s">
+      <c r="N24" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47" t="s">
+      <c r="O24" s="46"/>
+      <c r="P24" s="46" t="s">
         <v>217</v>
       </c>
-      <c r="Q24" s="47" t="s">
+      <c r="Q24" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R24" s="47" t="s">
+      <c r="R24" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S24" s="47" t="s">
+      <c r="S24" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T24" s="47"/>
-      <c r="U24" s="47" t="s">
+      <c r="T24" s="46"/>
+      <c r="U24" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V24" s="47"/>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V24" s="46"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>TFRENDSL1</v>
@@ -10310,13 +10164,13 @@
       <c r="C25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="65" t="s">
+      <c r="D25" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E25">
         <v>2022</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="30">
         <v>0.4</v>
       </c>
       <c r="G25">
@@ -10328,13 +10182,13 @@
       <c r="I25">
         <v>82</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="30">
         <v>1.1499999999999999</v>
       </c>
       <c r="K25">
         <v>30</v>
       </c>
-      <c r="L25" s="39">
+      <c r="L25" s="38">
         <v>1E-3</v>
       </c>
       <c r="N25" t="s">
@@ -10356,7 +10210,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>TFRENLPG1</v>
@@ -10364,13 +10218,13 @@
       <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E26">
         <v>2022</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="30">
         <v>0.34</v>
       </c>
       <c r="G26">
@@ -10382,13 +10236,13 @@
       <c r="I26">
         <v>86</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="30">
         <v>1.25</v>
       </c>
       <c r="K26">
         <v>30</v>
       </c>
-      <c r="L26" s="39">
+      <c r="L26" s="38">
         <v>1E-3</v>
       </c>
       <c r="N26" t="s">
@@ -10410,121 +10264,121 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B27" s="47" t="str">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B27" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TFRENELC1</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="46">
         <v>2026</v>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="46">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="46">
         <v>50</v>
       </c>
-      <c r="H27" s="47">
+      <c r="H27" s="46">
         <v>12</v>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="46">
         <v>145</v>
       </c>
-      <c r="J27" s="47">
+      <c r="J27" s="46">
         <v>0.85</v>
       </c>
-      <c r="K27" s="47">
+      <c r="K27" s="46">
         <v>30</v>
       </c>
-      <c r="L27" s="56">
+      <c r="L27" s="55">
         <v>1E-3</v>
       </c>
-      <c r="N27" s="47" t="s">
+      <c r="N27" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47" t="s">
+      <c r="O27" s="46"/>
+      <c r="P27" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="Q27" s="47" t="s">
+      <c r="Q27" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R27" s="47" t="s">
+      <c r="R27" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S27" s="47" t="s">
+      <c r="S27" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47" t="s">
+      <c r="T27" s="46"/>
+      <c r="U27" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V27" s="47"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" s="47" t="str">
+      <c r="V27" s="46"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B28" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TAVINKER1</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="47">
+      <c r="E28" s="46">
         <v>2022</v>
       </c>
-      <c r="F28" s="47">
+      <c r="F28" s="46">
         <v>0.1</v>
       </c>
-      <c r="G28" s="47">
+      <c r="G28" s="46">
         <v>65</v>
       </c>
-      <c r="H28" s="47">
+      <c r="H28" s="46">
         <v>180</v>
       </c>
-      <c r="I28" s="47">
+      <c r="I28" s="46">
         <v>50000</v>
       </c>
-      <c r="J28" s="47">
+      <c r="J28" s="46">
         <v>70</v>
       </c>
-      <c r="K28" s="47">
+      <c r="K28" s="46">
         <v>30</v>
       </c>
-      <c r="L28" s="47">
+      <c r="L28" s="46">
         <v>1E-3</v>
       </c>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O28" s="47"/>
-      <c r="P28" s="47" t="s">
+      <c r="O28" s="46"/>
+      <c r="P28" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="Q28" s="47" t="s">
+      <c r="Q28" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="R28" s="47" t="s">
+      <c r="R28" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S28" s="47" t="s">
+      <c r="S28" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T28" s="47"/>
-      <c r="U28" s="47" t="s">
+      <c r="T28" s="46"/>
+      <c r="U28" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V28" s="47"/>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V28" s="46"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>TRAINHFO1</v>
@@ -10532,7 +10386,7 @@
       <c r="C29" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="72" t="s">
         <v>211</v>
       </c>
       <c r="E29">
@@ -10556,7 +10410,7 @@
       <c r="K29">
         <v>30</v>
       </c>
-      <c r="L29" s="39">
+      <c r="L29" s="38">
         <v>1E-3</v>
       </c>
       <c r="N29" t="s">
@@ -10578,64 +10432,64 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B30" s="47" t="str">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TRAINELC1</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="74" t="s">
+      <c r="D30" s="73" t="s">
         <v>211</v>
       </c>
-      <c r="E30" s="47">
+      <c r="E30" s="46">
         <v>2040</v>
       </c>
-      <c r="F30" s="47">
+      <c r="F30" s="46">
         <v>0.78</v>
       </c>
-      <c r="G30" s="47">
+      <c r="G30" s="46">
         <v>66</v>
       </c>
-      <c r="H30" s="47">
+      <c r="H30" s="46">
         <v>500</v>
       </c>
-      <c r="I30" s="47">
+      <c r="I30" s="46">
         <v>3100</v>
       </c>
-      <c r="J30" s="47">
+      <c r="J30" s="46">
         <v>22</v>
       </c>
-      <c r="K30" s="47">
+      <c r="K30" s="46">
         <v>30</v>
       </c>
-      <c r="L30" s="56">
+      <c r="L30" s="55">
         <v>1E-3</v>
       </c>
-      <c r="N30" s="47" t="s">
+      <c r="N30" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47" t="s">
+      <c r="O30" s="46"/>
+      <c r="P30" s="46" t="s">
         <v>222</v>
       </c>
-      <c r="Q30" s="47" t="s">
+      <c r="Q30" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R30" s="47" t="s">
+      <c r="R30" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S30" s="47" t="s">
+      <c r="S30" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47" t="s">
+      <c r="T30" s="46"/>
+      <c r="U30" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V30" s="47"/>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V30" s="46"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>TMARNDSL1</v>
@@ -10643,7 +10497,7 @@
       <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="65" t="s">
+      <c r="D31" s="64" t="s">
         <v>212</v>
       </c>
       <c r="E31">
@@ -10689,7 +10543,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>TMARNLPG1</v>
@@ -10697,7 +10551,7 @@
       <c r="C32" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="64" t="s">
         <v>212</v>
       </c>
       <c r="E32">
@@ -10743,62 +10597,62 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B33" s="47" t="str">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B33" s="46" t="str">
         <f t="shared" si="0"/>
         <v>TMARNELC1</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="46">
         <v>2026</v>
       </c>
-      <c r="F33" s="47">
+      <c r="F33" s="46">
         <v>0.85</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="46">
         <v>50</v>
       </c>
-      <c r="H33" s="47">
+      <c r="H33" s="46">
         <v>400</v>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="46">
         <v>9500</v>
       </c>
-      <c r="J33" s="47">
+      <c r="J33" s="46">
         <v>70</v>
       </c>
-      <c r="K33" s="47">
+      <c r="K33" s="46">
         <v>30</v>
       </c>
-      <c r="L33" s="47">
+      <c r="L33" s="46">
         <v>1E-3</v>
       </c>
-      <c r="N33" s="47" t="s">
+      <c r="N33" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47" t="s">
+      <c r="O33" s="46"/>
+      <c r="P33" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="Q33" s="47" t="s">
+      <c r="Q33" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="R33" s="47" t="s">
+      <c r="R33" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="S33" s="47" t="s">
+      <c r="S33" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="T33" s="47"/>
-      <c r="U33" s="47" t="s">
+      <c r="T33" s="46"/>
+      <c r="U33" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="V33" s="47"/>
+      <c r="V33" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10813,26 +10667,26 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:AC2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.140625" style="57"/>
-    <col min="13" max="13" width="5" style="57" customWidth="1"/>
-    <col min="14" max="15" width="2" style="57" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.140625" style="57"/>
-    <col min="27" max="27" width="2" style="57" customWidth="1"/>
-    <col min="28" max="28" width="2.28515625" style="57" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="57"/>
+    <col min="1" max="1" width="2" style="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="9.109375" style="56"/>
+    <col min="13" max="13" width="5" style="56" customWidth="1"/>
+    <col min="14" max="15" width="2" style="56" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="9.109375" style="56"/>
+    <col min="27" max="27" width="2" style="56" customWidth="1"/>
+    <col min="28" max="28" width="2.33203125" style="56" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.109375" style="56"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B2" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="P2" s="58" t="s">
+      <c r="P2" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="AC2" s="58" t="s">
+      <c r="AC2" s="57" t="s">
         <v>168</v>
       </c>
     </row>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1206A7-DCAA-40DE-9E16-A99A308018AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E322A15-C450-4E36-BB06-11BFF77597DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1711,7 +1711,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="314">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2650,6 +2650,9 @@
   </si>
   <si>
     <t>NCAP_BND</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -5204,6 +5207,27 @@
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
       <c r="O15" s="26"/>
+      <c r="Q15" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="T15" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="U15" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W15" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E16" s="23">
@@ -5222,6 +5246,29 @@
       <c r="K16" s="26"/>
       <c r="L16" s="26"/>
       <c r="O16" s="26"/>
+      <c r="Q16" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="T16" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="U16" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V16" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W16" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="64" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E17" s="23">
@@ -5240,6 +5287,27 @@
       <c r="K17" s="26"/>
       <c r="L17" s="26"/>
       <c r="O17" s="26"/>
+      <c r="Q17" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R17" s="64"/>
+      <c r="S17" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="T17" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="U17" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W17" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E18" s="23">
@@ -5258,10 +5326,30 @@
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
       <c r="O18" s="26"/>
+      <c r="Q18" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R18" s="64"/>
+      <c r="S18" s="64" t="s">
+        <v>155</v>
+      </c>
+      <c r="T18" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="U18" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W18" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="X18" s="64"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="str">
-        <f>S19</f>
+        <f>S15</f>
         <v>ELCTNOIL01</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -5305,10 +5393,10 @@
       </c>
       <c r="R19" s="64"/>
       <c r="S19" s="64" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="T19" s="64" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="U19" s="64" t="s">
         <v>52</v>
@@ -5319,8 +5407,6 @@
       <c r="W19" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="X19" s="64"/>
-      <c r="Y19" s="64"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E20" s="23">
@@ -5338,6 +5424,25 @@
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="O20" s="26"/>
+      <c r="Q20" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R20" s="64"/>
+      <c r="S20" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="T20" s="64" t="s">
+        <v>161</v>
+      </c>
+      <c r="U20" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V20" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W20" s="59" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E21" s="23">
@@ -5355,6 +5460,25 @@
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="O21" s="26"/>
+      <c r="Q21" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="R21" s="64"/>
+      <c r="S21" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="T21" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="U21" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W21" s="59" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E22" s="23">
@@ -5372,6 +5496,25 @@
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
       <c r="O22" s="26"/>
+      <c r="Q22" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R22" s="64"/>
+      <c r="S22" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="T22" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="U22" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V22" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W22" s="59" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E23" s="23">
@@ -5389,10 +5532,29 @@
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="O23" s="26"/>
+      <c r="Q23" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R23" s="64"/>
+      <c r="S23" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="T23" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="U23" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="V23" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="W23" s="59" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" s="23" t="str">
-        <f>S24</f>
+        <f>S16</f>
         <v>ELCTNGAS01</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -5430,29 +5592,6 @@
       </c>
       <c r="O24" s="26">
         <v>1</v>
-      </c>
-      <c r="Q24" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="T24" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="U24" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V24" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W24" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
@@ -5525,7 +5664,7 @@
     </row>
     <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="23" t="str">
-        <f>S29</f>
+        <f>S17</f>
         <v>ELCRNBIO01</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -5564,27 +5703,6 @@
       <c r="O29" s="26">
         <v>1</v>
       </c>
-      <c r="Q29" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R29" s="64"/>
-      <c r="S29" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="T29" s="64" t="s">
-        <v>158</v>
-      </c>
-      <c r="U29" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V29" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W29" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="X29" s="64"/>
-      <c r="Y29" s="64"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E30" s="23">
@@ -5642,7 +5760,7 @@
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" s="23" t="str">
-        <f>S33</f>
+        <f>S18</f>
         <v>ELCRNHYD01</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -5681,26 +5799,6 @@
       <c r="O33" s="26">
         <v>0.35</v>
       </c>
-      <c r="Q33" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R33" s="64"/>
-      <c r="S33" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="T33" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="U33" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V33" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W33" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="X33" s="64"/>
       <c r="Y33" s="64"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.25">
@@ -5777,7 +5875,7 @@
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" s="23" t="str">
-        <f>S38</f>
+        <f>S19</f>
         <v>ELCRNWIN01</v>
       </c>
       <c r="C38" s="23" t="s">
@@ -5814,25 +5912,6 @@
       <c r="O38" s="26">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R38" s="64"/>
-      <c r="S38" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="T38" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="U38" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V38" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W38" s="59" t="s">
-        <v>202</v>
-      </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E39" s="23">
@@ -5897,7 +5976,7 @@
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="str">
-        <f>S42</f>
+        <f>S20</f>
         <v>ELCRNSOL01</v>
       </c>
       <c r="C42" s="23" t="s">
@@ -5935,25 +6014,6 @@
       </c>
       <c r="O42" s="26">
         <v>0.2</v>
-      </c>
-      <c r="Q42" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R42" s="64"/>
-      <c r="S42" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="T42" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="U42" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V42" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W42" s="59" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.25">
@@ -6028,7 +6088,7 @@
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="str">
-        <f>S52</f>
+        <f>S22</f>
         <v>ELCRNBSO01</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -6068,25 +6128,6 @@
       <c r="O47" s="26">
         <v>0.5</v>
       </c>
-      <c r="Q47" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R47" s="64"/>
-      <c r="S47" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="T47" s="64" t="s">
-        <v>194</v>
-      </c>
-      <c r="U47" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V47" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W47" s="59" t="s">
-        <v>202</v>
-      </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E48" s="23">
@@ -6104,7 +6145,7 @@
       <c r="L48" s="26"/>
       <c r="O48" s="26"/>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E49" s="23">
         <v>2030</v>
       </c>
@@ -6120,7 +6161,7 @@
       <c r="L49" s="26"/>
       <c r="O49" s="26"/>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E50" s="23">
         <v>2035</v>
       </c>
@@ -6137,7 +6178,7 @@
       <c r="O50" s="26"/>
       <c r="Q50" s="64"/>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E51" s="23">
         <v>2040</v>
       </c>
@@ -6154,9 +6195,9 @@
       <c r="O51" s="26"/>
       <c r="Q51" s="64"/>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="str">
-        <f>S55</f>
+        <f>S23</f>
         <v>ELCRNPHY01</v>
       </c>
       <c r="C52" s="23" t="s">
@@ -6195,27 +6236,8 @@
       <c r="O52" s="23">
         <v>0.45</v>
       </c>
-      <c r="Q52" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R52" s="64"/>
-      <c r="S52" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="T52" s="64" t="s">
-        <v>196</v>
-      </c>
-      <c r="U52" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V52" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W52" s="59" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E53" s="23">
         <v>2035</v>
       </c>
@@ -6230,7 +6252,7 @@
       </c>
       <c r="L53" s="26"/>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E54" s="23">
         <v>2040</v>
       </c>
@@ -6246,7 +6268,7 @@
       <c r="L54" s="26"/>
       <c r="Q54" s="64"/>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="23" t="s">
         <v>193</v>
       </c>
@@ -6283,27 +6305,8 @@
       <c r="O55" s="23">
         <v>0.5</v>
       </c>
-      <c r="Q55" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="R55" s="64"/>
-      <c r="S55" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="T55" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="U55" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="V55" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="W55" s="59" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E56" s="23">
         <v>2030</v>
       </c>
@@ -6317,7 +6320,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E57" s="23">
         <v>2035</v>
       </c>
@@ -6331,7 +6334,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E58" s="23">
         <v>2040</v>
       </c>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E322A15-C450-4E36-BB06-11BFF77597DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454DD9D6-91AB-47E3-AB04-CA449CF99F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="12" r:id="rId1"/>
@@ -2649,10 +2649,10 @@
     <t>PDP Installed Capacity</t>
   </si>
   <si>
-    <t>NCAP_BND</t>
-  </si>
-  <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>NCAP_BND~FX</t>
   </si>
 </sst>
 </file>
@@ -2666,7 +2666,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2873,8 +2873,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2935,6 +2940,11 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -3148,7 +3158,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3306,6 +3316,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="59" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="1" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -4722,7 +4735,7 @@
     <col min="5" max="5" width="11.88671875" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="23" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" style="23" customWidth="1"/>
     <col min="11" max="11" width="7.6640625" style="23" customWidth="1"/>
@@ -4844,7 +4857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="32.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="28" t="s">
         <v>56</v>
       </c>
@@ -4968,8 +4981,8 @@
       <c r="G11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>312</v>
+      <c r="H11" s="83" t="s">
+        <v>313</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -5461,7 +5474,7 @@
       <c r="L21" s="26"/>
       <c r="O21" s="26"/>
       <c r="Q21" s="64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R21" s="64"/>
       <c r="S21" s="23" t="s">
@@ -9100,7 +9113,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="2:22" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>92</v>
       </c>

--- a/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_04_PDP_with_no_policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454DD9D6-91AB-47E3-AB04-CA449CF99F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1587C4-7A9B-45F5-A7C3-EAA1EAAB54D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC" sheetId="12" r:id="rId1"/>
@@ -1711,7 +1711,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="315">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2652,7 +2652,10 @@
     <t>STG</t>
   </si>
   <si>
-    <t>NCAP_BND~FX</t>
+    <t>NCAP_START</t>
+  </si>
+  <si>
+    <t>CAP_BND</t>
   </si>
 </sst>
 </file>
@@ -3401,13 +3404,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>21166</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4725,7 +4728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A4B651-1072-492F-9C98-6FB421C5AC2C}">
-  <dimension ref="A1:Y58"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="23" customWidth="1"/>
@@ -4962,7 +4965,7 @@
       <c r="X10" s="59"/>
       <c r="Y10" s="59"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>1</v>
       </c>
@@ -4976,13 +4979,13 @@
         <v>98</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>35</v>
@@ -5607,164 +5610,193 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="E25" s="23">
+    <row r="25" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="23" t="str">
+        <f>S17</f>
+        <v>ELCRNBIO01</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="23">
+        <v>2028</v>
+      </c>
+      <c r="G25" s="26">
+        <v>0.35</v>
+      </c>
+      <c r="H25" s="26">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="I25" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="J25" s="23">
+        <v>2500</v>
+      </c>
+      <c r="K25" s="23">
+        <v>30</v>
+      </c>
+      <c r="L25" s="26">
+        <v>0.35</v>
+      </c>
+      <c r="M25" s="23">
+        <v>25</v>
+      </c>
+      <c r="N25" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O25" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="23">
         <v>2030</v>
       </c>
-      <c r="G25" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="H25" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="I25" s="26">
-        <v>0.85</v>
-      </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="O25" s="26"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="E26" s="23">
-        <v>2035</v>
-      </c>
       <c r="G26" s="26">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="H26" s="26">
-        <v>0.9</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="I26" s="26">
-        <v>0.85</v>
-      </c>
-      <c r="K26" s="26"/>
+        <v>0.6</v>
+      </c>
       <c r="L26" s="26"/>
       <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
+    </row>
+    <row r="27" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E27" s="23">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="G27" s="26">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H27" s="26">
-        <v>0.9</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="I27" s="26">
-        <v>0.85</v>
-      </c>
-      <c r="K27" s="26"/>
+        <v>0.6</v>
+      </c>
       <c r="L27" s="26"/>
       <c r="O27" s="26"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="64"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28" s="23">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="G28" s="26">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="H28" s="26">
-        <v>0.9</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="I28" s="26">
-        <v>0.85</v>
-      </c>
-      <c r="K28" s="26"/>
+        <v>0.6</v>
+      </c>
       <c r="L28" s="26"/>
       <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" s="23" t="str">
-        <f>S17</f>
-        <v>ELCRNBIO01</v>
+        <f>S18</f>
+        <v>ELCRNHYD01</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>49</v>
       </c>
       <c r="F29" s="23">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="G29" s="26">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="H29" s="26">
-        <v>2.1999999999999999E-2</v>
+        <v>1.3301000000000001</v>
       </c>
       <c r="I29" s="26">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="23">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="K29" s="23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L29" s="26">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="M29" s="23">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N29" s="23">
         <v>31.536000000000001</v>
       </c>
       <c r="O29" s="26">
+        <v>0.35</v>
+      </c>
+      <c r="Y29" s="64"/>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="E30" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G30" s="26">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G30" s="26">
-        <v>0.35</v>
-      </c>
       <c r="H30" s="26">
-        <v>7.1999999999999995E-2</v>
+        <v>1.3351</v>
       </c>
       <c r="I30" s="26">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="26"/>
       <c r="O30" s="26"/>
       <c r="X30" s="64"/>
       <c r="Y30" s="64"/>
     </row>
-    <row r="31" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E31" s="23">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="G31" s="26">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="H31" s="26">
-        <v>7.1999999999999995E-2</v>
+        <v>1.9951000000000001</v>
       </c>
       <c r="I31" s="26">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="26"/>
       <c r="O31" s="26"/>
       <c r="X31" s="64"/>
       <c r="Y31" s="64"/>
     </row>
-    <row r="32" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E32" s="23">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="G32" s="26">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="H32" s="26">
-        <v>7.1999999999999995E-2</v>
+        <v>2.7111000000000001</v>
       </c>
       <c r="I32" s="26">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L32" s="26"/>
       <c r="O32" s="26"/>
@@ -5772,65 +5804,62 @@
       <c r="Y32" s="64"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B33" s="23" t="str">
-        <f>S18</f>
-        <v>ELCRNHYD01</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="23">
-        <v>2023</v>
+      <c r="E33" s="23">
+        <v>2040</v>
       </c>
       <c r="G33" s="26">
         <v>1</v>
       </c>
       <c r="H33" s="26">
-        <v>1.3301000000000001</v>
+        <v>2.8811</v>
       </c>
       <c r="I33" s="26">
         <v>0.5</v>
       </c>
-      <c r="J33" s="23">
-        <v>3000</v>
-      </c>
-      <c r="K33" s="23">
-        <v>35</v>
-      </c>
-      <c r="L33" s="26">
-        <v>2</v>
-      </c>
-      <c r="M33" s="23">
-        <v>50</v>
-      </c>
-      <c r="N33" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O33" s="26">
-        <v>0.35</v>
-      </c>
+      <c r="L33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="X33" s="64"/>
       <c r="Y33" s="64"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="E34" s="23">
-        <v>2025</v>
+      <c r="B34" s="23" t="str">
+        <f>S19</f>
+        <v>ELCRNWIN01</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="23">
+        <v>2026</v>
       </c>
       <c r="G34" s="26">
         <v>1</v>
       </c>
       <c r="H34" s="26">
-        <v>1.3351</v>
+        <v>0.15</v>
       </c>
       <c r="I34" s="26">
-        <v>0.5</v>
+        <v>0.35</v>
+      </c>
+      <c r="J34" s="23">
+        <v>1340</v>
+      </c>
+      <c r="K34" s="23">
+        <v>26.7</v>
       </c>
       <c r="L34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="X34" s="64"/>
-      <c r="Y34" s="64"/>
+      <c r="M34" s="23">
+        <v>25</v>
+      </c>
+      <c r="N34" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O34" s="26">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E35" s="23">
@@ -5840,15 +5869,20 @@
         <v>1</v>
       </c>
       <c r="H35" s="26">
-        <v>1.9951000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I35" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="L35" s="26"/>
+        <v>0.35</v>
+      </c>
+      <c r="J35" s="23">
+        <f>J34*0.95</f>
+        <v>1273</v>
+      </c>
+      <c r="K35" s="23">
+        <f t="shared" ref="K35:K36" si="0">K34*0.95</f>
+        <v>25.364999999999998</v>
+      </c>
       <c r="O35" s="26"/>
-      <c r="X35" s="64"/>
-      <c r="Y35" s="64"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E36" s="23">
@@ -5858,15 +5892,20 @@
         <v>1</v>
       </c>
       <c r="H36" s="26">
-        <v>2.7111000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="I36" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="L36" s="26"/>
+        <v>0.35</v>
+      </c>
+      <c r="J36" s="23">
+        <f>J35*0.95</f>
+        <v>1209.3499999999999</v>
+      </c>
+      <c r="K36" s="23">
+        <f t="shared" si="0"/>
+        <v>24.096749999999997</v>
+      </c>
       <c r="O36" s="26"/>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E37" s="23">
@@ -5876,46 +5915,45 @@
         <v>1</v>
       </c>
       <c r="H37" s="26">
-        <v>2.8811</v>
+        <v>2.1</v>
       </c>
       <c r="I37" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="L37" s="26"/>
+        <v>0.35</v>
+      </c>
       <c r="O37" s="26"/>
-      <c r="X37" s="64"/>
-      <c r="Y37" s="64"/>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" s="23" t="str">
-        <f>S19</f>
-        <v>ELCRNWIN01</v>
+        <f>S20</f>
+        <v>ELCRNSOL01</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>49</v>
       </c>
       <c r="F38" s="23">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G38" s="26">
         <v>1</v>
       </c>
       <c r="H38" s="26">
-        <v>0.15</v>
+        <v>0.44679999999999997</v>
       </c>
       <c r="I38" s="26">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="J38" s="23">
-        <v>1340</v>
+        <v>550</v>
       </c>
       <c r="K38" s="23">
-        <v>26.7</v>
-      </c>
-      <c r="L38" s="26"/>
+        <v>7</v>
+      </c>
+      <c r="L38" s="26">
+        <v>0</v>
+      </c>
       <c r="M38" s="23">
         <v>25</v>
       </c>
@@ -5923,441 +5961,338 @@
         <v>31.536000000000001</v>
       </c>
       <c r="O38" s="26">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E39" s="23">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="G39" s="26">
         <v>1</v>
       </c>
       <c r="H39" s="26">
-        <v>0.9</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="I39" s="26">
-        <v>0.35</v>
-      </c>
-      <c r="J39" s="23">
-        <f>J38*0.95</f>
-        <v>1273</v>
-      </c>
-      <c r="K39" s="23">
-        <f t="shared" ref="K39:K40" si="0">K38*0.95</f>
-        <v>25.364999999999998</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L39" s="26"/>
       <c r="O39" s="26"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E40" s="23">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="G40" s="26">
         <v>1</v>
       </c>
       <c r="H40" s="26">
-        <v>1.05</v>
+        <v>2.5268000000000002</v>
       </c>
       <c r="I40" s="26">
-        <v>0.35</v>
-      </c>
-      <c r="J40" s="23">
-        <f>J39*0.95</f>
-        <v>1209.3499999999999</v>
-      </c>
-      <c r="K40" s="23">
-        <f t="shared" si="0"/>
-        <v>24.096749999999997</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L40" s="26"/>
       <c r="O40" s="26"/>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E41" s="23">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="G41" s="26">
         <v>1</v>
       </c>
       <c r="H41" s="26">
-        <v>2.1</v>
+        <v>3.0908000000000002</v>
       </c>
       <c r="I41" s="26">
-        <v>0.35</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L41" s="26"/>
       <c r="O41" s="26"/>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B42" s="23" t="str">
-        <f>S20</f>
-        <v>ELCRNSOL01</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F42" s="23">
-        <v>2022</v>
+      <c r="E42" s="23">
+        <v>2040</v>
       </c>
       <c r="G42" s="26">
         <v>1</v>
       </c>
       <c r="H42" s="26">
-        <v>0.44679999999999997</v>
+        <v>4.2907999999999999</v>
       </c>
       <c r="I42" s="26">
         <v>0.2</v>
       </c>
-      <c r="J42" s="23">
-        <v>550</v>
-      </c>
-      <c r="K42" s="23">
-        <v>7</v>
-      </c>
-      <c r="L42" s="26">
-        <v>0</v>
-      </c>
-      <c r="M42" s="23">
-        <v>25</v>
-      </c>
-      <c r="N42" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O42" s="26">
-        <v>0.2</v>
-      </c>
+      <c r="L42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="Q42" s="64"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="64"/>
+      <c r="U42" s="64"/>
+      <c r="V42" s="64"/>
+      <c r="W42" s="59"/>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="E43" s="23">
-        <v>2025</v>
+      <c r="B43" s="23" t="str">
+        <f>S22</f>
+        <v>ELCRNBSO01</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" s="23">
+        <v>2024</v>
       </c>
       <c r="G43" s="26">
         <v>1</v>
       </c>
       <c r="H43" s="26">
-        <v>0.93679999999999997</v>
+        <v>0.06</v>
       </c>
       <c r="I43" s="26">
-        <v>0.2</v>
-      </c>
-      <c r="L43" s="26"/>
-      <c r="O43" s="26"/>
+        <v>0.25</v>
+      </c>
+      <c r="J43" s="23">
+        <v>1090</v>
+      </c>
+      <c r="K43" s="23">
+        <f>J43*0.02</f>
+        <v>21.8</v>
+      </c>
+      <c r="L43" s="26">
+        <v>0</v>
+      </c>
+      <c r="M43" s="23">
+        <v>25</v>
+      </c>
+      <c r="N43" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O43" s="26">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E44" s="23">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="G44" s="26">
         <v>1</v>
       </c>
       <c r="H44" s="26">
-        <v>2.5268000000000002</v>
+        <v>0.39</v>
       </c>
       <c r="I44" s="26">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="26"/>
       <c r="O44" s="26"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E45" s="23">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="G45" s="26">
         <v>1</v>
       </c>
       <c r="H45" s="26">
-        <v>3.0908000000000002</v>
+        <v>0.54</v>
       </c>
       <c r="I45" s="26">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="26"/>
       <c r="O45" s="26"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="E46" s="23">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="G46" s="26">
         <v>1</v>
       </c>
       <c r="H46" s="26">
-        <v>4.2907999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="I46" s="26">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="26"/>
       <c r="O46" s="26"/>
       <c r="Q46" s="64"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="64"/>
-      <c r="U46" s="64"/>
-      <c r="V46" s="64"/>
-      <c r="W46" s="59"/>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B47" s="23" t="str">
-        <f>S22</f>
-        <v>ELCRNBSO01</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F47" s="23">
-        <v>2024</v>
+      <c r="E47" s="23">
+        <v>2040</v>
       </c>
       <c r="G47" s="26">
         <v>1</v>
       </c>
       <c r="H47" s="26">
-        <v>0.06</v>
+        <v>0.54</v>
       </c>
       <c r="I47" s="26">
         <v>0.25</v>
       </c>
-      <c r="J47" s="23">
-        <v>1090</v>
-      </c>
-      <c r="K47" s="23">
-        <f>J47*0.02</f>
-        <v>21.8</v>
-      </c>
-      <c r="L47" s="26">
-        <v>0</v>
-      </c>
-      <c r="M47" s="23">
-        <v>25</v>
-      </c>
-      <c r="N47" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O47" s="26">
-        <v>0.5</v>
-      </c>
+      <c r="L47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="Q47" s="64"/>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="E48" s="23">
-        <v>2025</v>
+      <c r="B48" s="23" t="str">
+        <f>S23</f>
+        <v>ELCRNPHY01</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" s="23">
+        <v>2030</v>
       </c>
       <c r="G48" s="26">
         <v>1</v>
       </c>
       <c r="H48" s="26">
-        <v>0.39</v>
-      </c>
-      <c r="I48" s="26">
-        <v>0.25</v>
-      </c>
-      <c r="L48" s="26"/>
-      <c r="O48" s="26"/>
+        <v>1</v>
+      </c>
+      <c r="I48" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="J48" s="23">
+        <v>1990</v>
+      </c>
+      <c r="K48" s="23">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="L48" s="26">
+        <v>2</v>
+      </c>
+      <c r="M48" s="23">
+        <v>40</v>
+      </c>
+      <c r="N48" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O48" s="23">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E49" s="23">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="G49" s="26">
         <v>1</v>
       </c>
       <c r="H49" s="26">
-        <v>0.54</v>
-      </c>
-      <c r="I49" s="26">
-        <v>0.25</v>
+        <v>1</v>
+      </c>
+      <c r="I49" s="23">
+        <v>0.8</v>
       </c>
       <c r="L49" s="26"/>
-      <c r="O49" s="26"/>
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E50" s="23">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="G50" s="26">
         <v>1</v>
       </c>
       <c r="H50" s="26">
-        <v>0.54</v>
-      </c>
-      <c r="I50" s="26">
-        <v>0.25</v>
+        <v>1.8</v>
+      </c>
+      <c r="I50" s="23">
+        <v>0.8</v>
       </c>
       <c r="L50" s="26"/>
-      <c r="O50" s="26"/>
       <c r="Q50" s="64"/>
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="E51" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G51" s="26">
-        <v>1</v>
-      </c>
-      <c r="H51" s="26">
-        <v>0.54</v>
-      </c>
-      <c r="I51" s="26">
-        <v>0.25</v>
-      </c>
-      <c r="L51" s="26"/>
-      <c r="O51" s="26"/>
-      <c r="Q51" s="64"/>
+      <c r="B51" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" s="23">
+        <v>2025</v>
+      </c>
+      <c r="G51" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H51" s="23">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="I51" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="J51" s="23">
+        <v>490</v>
+      </c>
+      <c r="K51" s="23">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M51" s="23">
+        <v>15</v>
+      </c>
+      <c r="N51" s="23">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="O51" s="23">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B52" s="23" t="str">
-        <f>S23</f>
-        <v>ELCRNPHY01</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F52" s="23">
+      <c r="E52" s="23">
         <v>2030</v>
       </c>
-      <c r="G52" s="26">
-        <v>1</v>
-      </c>
-      <c r="H52" s="26">
-        <v>1</v>
+      <c r="G52" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H52" s="23">
+        <v>1.754</v>
       </c>
       <c r="I52" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="J52" s="23">
-        <v>1990</v>
-      </c>
-      <c r="K52" s="23">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="L52" s="26">
-        <v>2</v>
-      </c>
-      <c r="M52" s="23">
-        <v>40</v>
-      </c>
-      <c r="N52" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O52" s="23">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E53" s="23">
         <v>2035</v>
       </c>
-      <c r="G53" s="26">
-        <v>1</v>
-      </c>
-      <c r="H53" s="26">
-        <v>1</v>
+      <c r="G53" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H53" s="23">
+        <v>1.754</v>
       </c>
       <c r="I53" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="L53" s="26"/>
+        <v>0.15</v>
+      </c>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E54" s="23">
         <v>2040</v>
       </c>
-      <c r="G54" s="26">
-        <v>1</v>
-      </c>
-      <c r="H54" s="26">
-        <v>1.8</v>
+      <c r="G54" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H54" s="23">
+        <v>2.254</v>
       </c>
       <c r="I54" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="L54" s="26"/>
-      <c r="Q54" s="64"/>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B55" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F55" s="23">
-        <v>2025</v>
-      </c>
-      <c r="G55" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H55" s="23">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="I55" s="23">
-        <v>0.15</v>
-      </c>
-      <c r="J55" s="23">
-        <v>490</v>
-      </c>
-      <c r="K55" s="23">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="M55" s="23">
-        <v>15</v>
-      </c>
-      <c r="N55" s="23">
-        <v>31.536000000000001</v>
-      </c>
-      <c r="O55" s="23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="E56" s="23">
-        <v>2030</v>
-      </c>
-      <c r="G56" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H56" s="23">
-        <v>1.754</v>
-      </c>
-      <c r="I56" s="23">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="E57" s="23">
-        <v>2035</v>
-      </c>
-      <c r="G57" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H57" s="23">
-        <v>1.754</v>
-      </c>
-      <c r="I57" s="23">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="E58" s="23">
-        <v>2040</v>
-      </c>
-      <c r="G58" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="H58" s="23">
-        <v>2.254</v>
-      </c>
-      <c r="I58" s="23">
         <v>0.15</v>
       </c>
     </row>
